--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_1.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_1.xlsx
@@ -618,1641 +618,1641 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.0103</t>
+          <t>X ≈ -0.01029</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>6</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-53.30634469643234</v>
+        <v>-53.27373987298473</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.57576731486389</v>
+        <v>12.60931146728728</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.14892455231046</v>
+        <v>11.18413415735737</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>27.00976658246542</v>
+        <v>27.04593095798985</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.08225993627823</v>
+        <v>10.14762051504819</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.27103369754713</v>
+        <v>10.3362152999258</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.077783521853064</v>
+        <v>-7.011776612957917</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.357231906294139</v>
+        <v>-7.290862235945262</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.274018916824147</v>
+        <v>9.340471638469481</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.506254985680037</v>
+        <v>8.573636386286879</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>25.38431520928424</v>
+        <v>25.45149344533183</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.100335468814471</v>
+        <v>-8.032945724951823</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.388547141141338</v>
+        <v>7.457345441790416</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.169530325971969</v>
+        <v>7.238624463994299</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-10.10726031781666</v>
+        <v>-10.03741773518378</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-9.516559674225874</v>
+        <v>-9.447362230807329</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-9.65311563960271</v>
+        <v>-9.583718140364006</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-26.397424662886</v>
+        <v>-26.3278964154084</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-9.547781469394089</v>
+        <v>-9.478423869941132</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-9.36377924609436</v>
+        <v>-9.294594678771894</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>23.39409035901318</v>
+        <v>23.46398824715811</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.668469282087692</v>
+        <v>6.738477197103684</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>6.945198778023034</v>
+        <v>7.014925285582265</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376943253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.009573</t>
+          <t>X ≈ -0.009562</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.647159582543466</v>
+        <v>-3.614152334797048</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-23.85092288345135</v>
+        <v>-23.81766503089773</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.35115490591184</v>
+        <v>-15.31614436783351</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.125566080072787</v>
+        <v>-6.08963769983189</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.490232818461628</v>
+        <v>-6.42498594087364</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.25269615335839</v>
+        <v>-16.1876863135857</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.871657139348393</v>
+        <v>2.937722490879224</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.357064337385644</v>
+        <v>-7.290696610858113</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.318198527586695</v>
+        <v>-7.251835831379324</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-18.04907329318491</v>
+        <v>-17.98182592265827</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.820020971095488</v>
+        <v>-7.752997423338464</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-8.10019662765054</v>
+        <v>-8.032808392756309</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.223427384874704</v>
+        <v>-9.154695372014821</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.5226949941611423</v>
+        <v>0.5917645598459629</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1340535474590681</v>
+        <v>-0.06418001229010173</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-9.516451809831501</v>
+        <v>-9.447255429908601</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-19.6320677238831</v>
+        <v>-19.56269621645986</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.760471007167126</v>
+        <v>-9.69090809772095</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.4373123303202817</v>
+        <v>0.5066871779037072</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.6242913147411855</v>
+        <v>0.6934896919858176</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>10.07264294684234</v>
+        <v>10.14252641912412</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>19.99378962459027</v>
+        <v>20.06380695492734</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>10.27752259568873</v>
+        <v>10.34725022273058</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>10.2046783625731</v>
+        <v>10.27453271028038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.008841</t>
+          <t>X ≈ -0.008831</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.476128183535224</v>
+        <v>-10.49705419702738</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.832012422058938</v>
+        <v>-10.85207640665586</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.93206760922851</v>
+        <v>7.499819281805387</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.081473072569416</v>
+        <v>0.1249821480785016</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.7932229317188</v>
+        <v>6.395337664446686</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.891732061606533</v>
+        <v>-0.03500103446524605</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.031265727375335</v>
+        <v>-7.481284754442228</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.330060994705889</v>
+        <v>-7.779393285894834</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.283000116825718</v>
+        <v>-7.733884263942286</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.113490024345531</v>
+        <v>-8.560521161599205</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.93676428092614</v>
+        <v>-14.91217077581012</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.995615845025455</v>
+        <v>-1.927862537583103</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>15.03789307170224</v>
+        <v>10.17049902001424</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.81982995899326</v>
+        <v>9.951336366904243</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.989065373936874</v>
+        <v>2.598476644089168</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.624340109493211</v>
+        <v>3.229102247931252</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>11.73067466340852</v>
+        <v>3.08340846961179</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.62957164036139</v>
+        <v>2.966657905736206</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>18.9808092939768</v>
+        <v>9.862406945941807</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.03910483291436</v>
+        <v>3.402189506773112</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>11.49985853017838</v>
+        <v>6.812130474597545</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>18.56599117164368</v>
+        <v>13.40105946147386</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>11.70564147924647</v>
+        <v>7.014896271111184</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>4.49039264828739</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.008109</t>
+          <t>X ≈ -0.0081</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>13</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>15.45585943234401</v>
+        <v>23.13062035592474</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1604989154239007</v>
+        <v>7.516865530866419</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.053938340797401</v>
+        <v>6.089204602458807</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.345428067829516</v>
+        <v>5.381531657679865</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.983940933939579</v>
+        <v>5.049362685340377</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.171582031944716</v>
+        <v>5.236820947903787</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-10.90704580799979</v>
+        <v>-3.185645183825358</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.530019805130983</v>
+        <v>4.194073620888574</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.490008568593559</v>
+        <v>4.236376839636236</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.26164612590722</v>
+        <v>3.467974618396774</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.989599259089573</v>
+        <v>3.742046991023635</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.39785965035297</v>
+        <v>11.13219626535626</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.277607702907716</v>
+        <v>10.01559169195429</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.614433422994466</v>
+        <v>2.126135559457701</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9.074357469513991</v>
+        <v>16.81807413922332</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.994966588647905</v>
+        <v>9.740324721482295</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>9.537313430712771</v>
+        <v>17.28811372073581</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>17.11395654344361</v>
+        <v>24.86949434253793</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.654018237945941</v>
+        <v>17.40942705259014</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>17.52685447720523</v>
+        <v>25.28676188304037</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>9.303962546687082</v>
+        <v>17.05920029693791</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>16.91854375146854</v>
+        <v>24.67622889026085</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>9.508474699107374</v>
+        <v>17.26819079199815</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>17.12775528565003</v>
+        <v>24.88991732566499</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.007377</t>
+          <t>X ≈ -0.007369</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.629941135123893</v>
+        <v>0.9001431350142965</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>20.85940132007172</v>
+        <v>18.6345717903762</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.15093615439773</v>
+        <v>17.21033547816869</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18.72955998136464</v>
+        <v>25.54490393411255</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>26.66019842294543</v>
+        <v>34.26041641464266</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>26.85438788133268</v>
+        <v>34.4566873622324</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.213984698619718</v>
+        <v>-2.489606960870525</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.9369469577503367</v>
+        <v>-2.7674174552998</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.978296769708912</v>
+        <v>-2.727209590055345</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2080265798927883</v>
+        <v>-3.497681637233974</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.821686901231708</v>
+        <v>-12.2836740310337</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-8.102295083674896</v>
+        <v>-12.56528022930167</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.917875575639215</v>
+        <v>-4.625562954937799</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.171267402765942</v>
+        <v>4.218283616213846</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.516296768544386</v>
+        <v>3.563205924434854</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>7.112266942948416</v>
+        <v>4.15761389362725</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.978493092993517</v>
+        <v>4.0252938989059</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>6.875954231908338</v>
+        <v>3.92194934832245</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>15.41439633027674</v>
+        <v>13.21855084413209</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>15.60594843819749</v>
+        <v>13.40928434167449</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.583625821696629</v>
+        <v>-5.298204588562371</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>6.668276466802631</v>
+        <v>3.709809225548099</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>6.945127974419471</v>
+        <v>3.98546559226223</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.461988304091676</v>
+        <v>-5.180012744267145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.006645</t>
+          <t>X ≈ -0.006637</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>31</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.158331196907504</v>
+        <v>1.191380299384825</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.585092471311135</v>
+        <v>-5.551689155109635</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.018182497708004</v>
+        <v>-6.983105329242328</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.304953292508024</v>
+        <v>8.340988782798306</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>7.944295607859289</v>
+        <v>8.009648469045089</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.714687946288493</v>
+        <v>1.779821719315564</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.366547179129363</v>
+        <v>7.432646747269551</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.541743683057007</v>
+        <v>-2.475339610083559</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7105720894065968</v>
+        <v>0.7769870334659643</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.059733016548698</v>
+        <v>0.007614294128977406</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.214316482582987</v>
+        <v>-6.147274065038566</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.279482065183927</v>
+        <v>-3.212060532147447</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.246070434642995</v>
+        <v>5.314871968796218</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.841366766794643</v>
+        <v>-7.772310975667096</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-14.93671235343019</v>
+        <v>-14.8668675462229</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-14.34728876226357</v>
+        <v>-14.2780868104683</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-14.48105840760165</v>
+        <v>-14.41601725745862</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-14.59012767713864</v>
+        <v>-14.52497698454999</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-11.15811183846624</v>
+        <v>-11.09207680553675</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-10.97463153309726</v>
+        <v>-10.90872555952802</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-8.29786839808061</v>
+        <v>-8.228007192401513</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-14.82398638705751</v>
+        <v>-14.75399574853002</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-17.77850861244051</v>
+        <v>-17.70879201545643</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-11.40822486323482</v>
+        <v>-11.33837051552607</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005913</t>
+          <t>X ≈ -0.005905</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.284693956385404</v>
+        <v>5.582010156386062</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.994825116042144</v>
+        <v>-2.108584369804767</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-7.402152499949949</v>
+        <v>-7.219815825188533</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.139015859683958</v>
+        <v>-4.250341846438261</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.503414929512445</v>
+        <v>-4.585466517791502</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11.59814373515218</v>
+        <v>10.33692179610236</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.108336952103386</v>
+        <v>-1.484551027795284</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.385602411115684</v>
+        <v>-1.761590730079341</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.34511305524417</v>
+        <v>-1.721243517010137</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.115989498245717</v>
+        <v>-2.491320847687568</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.843016068987396</v>
+        <v>1.471281341015526</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.108391181337268</v>
+        <v>-2.497444480910751</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-15.20719178556858</v>
+        <v>-11.00305389261842</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-11.44389768522979</v>
+        <v>-7.53365416711901</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-12.10437330520414</v>
+        <v>-8.192138821788006</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-15.50554839013848</v>
+        <v>-11.29712475283864</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-15.63931244498588</v>
+        <v>-11.43420882160976</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-15.74880916038663</v>
+        <v>-11.54232353789195</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-23.52582567365973</v>
+        <v>-18.72876811312469</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-11.36102167704303</v>
+        <v>-7.446997713266221</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-11.90730008728945</v>
+        <v>-7.989148070194076</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-15.98440667233022</v>
+        <v>-11.76882214816762</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-15.71453655701968</v>
+        <v>-11.49794816812793</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-11.79532163742599</v>
+        <v>-7.873615437866931</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.005181</t>
+          <t>X ≈ -0.005174</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8.015267531481364</v>
+        <v>8.697323848736438</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.443766489257428</v>
+        <v>2.835204033641212</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1831771355373846</v>
+        <v>-1.394422939704533</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.510698460514817</v>
+        <v>-4.879313957181736</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.358842076212795</v>
+        <v>0.3017107832991357</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-6.307959591416868</v>
+        <v>-7.797286707886343</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.078389243639684</v>
+        <v>-7.012367843511221</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-12.59609539126941</v>
+        <v>-12.8207769720651</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-9.938993582873941</v>
+        <v>-10.01819093529475</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-15.95435536707224</v>
+        <v>-16.32390334590229</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.198714285013899</v>
+        <v>-7.753537642258159</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.101130376472433</v>
+        <v>-10.80210407594575</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.978195013542376</v>
+        <v>-6.387164772057062</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.200489073892122</v>
+        <v>-6.609920510982569</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.858737796823981</v>
+        <v>-7.268124360123892</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>3.611201661139496</v>
+        <v>1.638066720583467</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.477444079880087</v>
+        <v>1.50494891614413</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.7471641428213474</v>
+        <v>-1.372650187312907</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.664523623359223</v>
+        <v>-3.93196726558763</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.106653797043691</v>
+        <v>-6.521802800540698</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.650728570024853</v>
+        <v>-7.063945384372275</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.5317815936800727</v>
+        <v>-1.589848557883997</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-7.085557991680986</v>
+        <v>-9.646604398768964</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-9.795321637427499</v>
+        <v>-12.5032450674974</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004449</t>
+          <t>X ≈ -0.004443</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>35</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6.284731452607971</v>
+        <v>6.3178226807022</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.115323921147571</v>
+        <v>3.148792436371671</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>18.72002684616135</v>
+        <v>18.76119607344672</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.33453274197415</v>
+        <v>12.37457288588784</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>20.49796800884727</v>
+        <v>20.56995488166679</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12.16503670310304</v>
+        <v>12.23415868000137</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.55769208343991</v>
+        <v>8.623781203535735</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8.283791796459809</v>
+        <v>8.350237905138002</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.327099087852105</v>
+        <v>8.3935372760143</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.559614965956889</v>
+        <v>7.626982488910969</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.83505173735368</v>
+        <v>7.902142436070129</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.712144985244521</v>
+        <v>4.779584676249229</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.288460564227513</v>
+        <v>9.357265189195793</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9.07032342872116</v>
+        <v>9.139424635147492</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>11.26621299245944</v>
+        <v>11.33612572720541</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.16177802388291</v>
+        <v>6.231024172641185</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>11.72970752351634</v>
+        <v>11.80286084689992</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>5.925298096076673</v>
+        <v>5.996733910072777</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.4374840527665569</v>
+        <v>0.5069888692847186</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>9.184943587467515</v>
+        <v>9.257052776454316</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>8.645042928977411</v>
+        <v>8.714919223341859</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.716467557877174</v>
+        <v>5.786470775508938</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.575652550527998</v>
+        <v>-2.505931955333438</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.2046783625737518</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.003717</t>
+          <t>X ≈ -0.003711</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.590916589444355</v>
+        <v>-6.720342234674071</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.19379374107389</v>
+        <v>-2.396445863177746</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-12.51093465503993</v>
+        <v>-11.59237359737546</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.182095411954869</v>
+        <v>-2.985082285264426</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.765941236327407</v>
+        <v>2.895313430579094</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.375331919344603</v>
+        <v>1.528407508730254</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.550271104180567</v>
+        <v>-2.347860932924625</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.332063956736334</v>
+        <v>0.4852091952570419</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.787147147267952</v>
+        <v>-2.584932338352871</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.184360597417161</v>
+        <v>1.313157394706124</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7042678991601292</v>
+        <v>-1.526645741809709</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.564141741342866</v>
+        <v>-3.361730918478912</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.104314747843731</v>
+        <v>-2.925551886430576</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.743300347909944</v>
+        <v>-1.589247086758348</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.400434079195001</v>
+        <v>-2.245867103978036</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.8070518733109822</v>
+        <v>-1.653424693789859</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.226525006502307</v>
+        <v>1.331313479236528</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.70702341604914</v>
+        <v>2.7873247069397</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.339166781087236</v>
+        <v>1.443268829925493</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-3.814534847253434</v>
+        <v>-4.613754332654707</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.18697975947773</v>
+        <v>-2.033890185904021</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.3230027752236921</v>
+        <v>-0.5488536267960953</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.358326008188023</v>
+        <v>4.411510742503779</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.109440267335003</v>
+        <v>1.212032710280376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.002986</t>
+          <t>X ≈ -0.002979</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.459149598201087</v>
+        <v>4.063788195360615</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.100935773916312</v>
+        <v>1.684921872712891</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.356349552172411</v>
+        <v>-1.792194977046371</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.001217634678021</v>
+        <v>3.644954548154573</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4053409021588905</v>
+        <v>0.2354462475254735</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.884225047178028</v>
+        <v>7.600680726711417</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.044050441835864</v>
+        <v>1.706609058825052</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7676781893383833</v>
+        <v>1.430790563737062</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.824577956955963</v>
+        <v>2.498355022133737</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.071018779028577</v>
+        <v>2.756405712802263</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.41034699490271</v>
+        <v>7.137591905526428</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.084633059326237</v>
+        <v>3.780994679568707</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.032232292953204</v>
+        <v>6.772098873988575</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.778398791554508</v>
+        <v>4.497796553474963</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.15825947086072</v>
+        <v>5.899663776266458</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.735692815554934</v>
+        <v>5.466168059406101</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.601673849289469</v>
+        <v>5.334147724194509</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.443600789405394</v>
+        <v>2.143838257872737</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.6411216045075676</v>
+        <v>1.330571677025027</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.90428118108639</v>
+        <v>5.63721777770931</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>4.363091854040597</v>
+        <v>5.095056048187367</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.288601225542074</v>
+        <v>5.020911614946705</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>6.60498780587448</v>
+        <v>7.358268247146242</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.449576321757007</v>
+        <v>3.161130648424468</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002254</t>
+          <t>X ≈ -0.002249</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.316428272505362</v>
+        <v>0.8359471266808498</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.270743682235903</v>
+        <v>-2.919353267942249</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.862107985869741</v>
+        <v>-1.607449159117301</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.100963347633034</v>
+        <v>3.162635126647331</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.287327277588339</v>
+        <v>6.942608955817583</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.08449951737689787</v>
+        <v>0.2723194634804713</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.290771809254188</v>
+        <v>4.307748633362621</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.594576288718258</v>
+        <v>1.974848857279767</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.057873705367697</v>
+        <v>3.388882297997277</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.578221385370078</v>
+        <v>1.93443737467765</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.838712088524304</v>
+        <v>-2.600006356915465</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.116917343603156</v>
+        <v>-1.503750148686379</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.742907926459111</v>
+        <v>2.186145682571244</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.946447921026831</v>
+        <v>1.966370923729656</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.714963179981218</v>
+        <v>3.374291297754475</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.4595183188377305</v>
+        <v>1.216692212530525</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.750595079624539</v>
+        <v>1.771564547692861</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.9342373128136572</v>
+        <v>0.9795705674340169</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.002526104943314</v>
+        <v>3.950310617131962</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.6240084353653117</v>
+        <v>0.6934763961023762</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.222109233509173</v>
+        <v>2.218147689072012</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.574568271525678</v>
+        <v>3.52149093519072</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.278740464271173</v>
+        <v>5.176103804785484</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.204678362572785</v>
+        <v>5.102118917177073</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001522</t>
+          <t>X ≈ -0.001517</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.609928432963478</v>
+        <v>2.247707539605948</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.634726609067194</v>
+        <v>4.861903376045539</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.035839624501214</v>
+        <v>7.355433976711687</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.404904122850795</v>
+        <v>4.677147339584081</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>6.441612560843573</v>
+        <v>5.820132955660227</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.190861083302529</v>
+        <v>5.2970014779971</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8.744371698896664</v>
+        <v>8.956218454565381</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>7.988817220266299</v>
+        <v>8.681599634490382</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>8.514063127524139</v>
+        <v>9.218996048051082</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>9.185967345708953</v>
+        <v>9.927677987459234</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.577293400745901</v>
+        <v>6.754536314410878</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>6.300103573480712</v>
+        <v>5.491385741093943</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.214063829674494</v>
+        <v>3.382485184490626</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.439135931994507</v>
+        <v>5.63031138172488</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>7.475294723247963</v>
+        <v>6.947843153234935</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>5.181201301930123</v>
+        <v>4.582510349985611</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.565193272469841</v>
+        <v>4.450318296909259</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.980944476721113</v>
+        <v>3.851561722010132</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.644504694995554</v>
+        <v>5.845018221320238</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>4.386333041295117</v>
+        <v>4.550410814278479</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.362656371639083</v>
+        <v>3.513725797825138</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.805297787011284</v>
+        <v>2.944586920579198</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.564164348235515</v>
+        <v>3.715162235196772</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>5.42206966692104</v>
+        <v>5.62106736374573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007899</t>
+          <t>X ≈ -0.0007853</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4373981914640339</v>
+        <v>-0.4038087371073118</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4007548783140678</v>
+        <v>0.4329159680047425</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.431041951600605</v>
+        <v>0.4648878756398958</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.160970483383785</v>
+        <v>-1.124015990522672</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3550682717754512</v>
+        <v>-0.2918735923357545</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1670607352481142</v>
+        <v>-0.1041881139069218</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.989750758786556</v>
+        <v>-2.916950516569379</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.68107094395026</v>
+        <v>-2.60803735027212</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.641039634718851</v>
+        <v>-2.568925632443253</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.826864762558195</v>
+        <v>-2.752810335114837</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.9713213611149953</v>
+        <v>1.033461226765326</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1881896597788284</v>
+        <v>-0.1208743595571633</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7243749791547955</v>
+        <v>-0.6552071893236899</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.416285156160392</v>
+        <v>-2.341905200280912</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-4.545665388372761</v>
+        <v>-4.465111159375788</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.069411486314387</v>
+        <v>-2.992794426426535</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.263073169805779</v>
+        <v>-5.182113974352298</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.487348441376959</v>
+        <v>-4.407250772952885</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.683495499464513</v>
+        <v>-3.604974239268863</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8462063025068431</v>
+        <v>-0.7759092597768529</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.5062047213629768</v>
+        <v>-0.4367568329141633</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.007737427492024551</v>
+        <v>0.07516663584008398</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.312025792649074</v>
+        <v>-1.414030643140769</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.0866842622781121</v>
+        <v>-0.01958493677845041</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -5.785e-05</t>
+          <t>X ≈ -5.4e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1231</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9168837035338342</v>
+        <v>0.8274133627952835</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6245470827715636</v>
+        <v>0.6153948259389708</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.199877322958699</v>
+        <v>1.236542134289117</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.095199993914413</v>
+        <v>1.089973769241759</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3545859131018716</v>
+        <v>-0.375163980737149</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2033288675463751</v>
+        <v>-0.2695143893213228</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.03901818825444536</v>
+        <v>-0.07516481524886842</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3722742266816184</v>
+        <v>0.2568173509666352</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1715611779043229</v>
+        <v>0.1023588696620692</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.04611625116864815</v>
+        <v>0.02112422992021123</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4418586734023435</v>
+        <v>-0.4667985394412284</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1877019132965501</v>
+        <v>-0.2138034986338226</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.553164004705565</v>
+        <v>-1.580076191880963</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.483879708438586</v>
+        <v>-1.559287611397387</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5230050308186946</v>
+        <v>-0.5499976054665296</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8192165680196766</v>
+        <v>-0.7985188968347856</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.9526947861724935</v>
+        <v>-0.9331882179697857</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.331964835449185</v>
+        <v>-1.313956466679109</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.6648081442925147</v>
+        <v>-0.6927686736097201</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.289734663902564</v>
+        <v>-1.317703851447448</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.076392707691177</v>
+        <v>-2.103944150112703</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.153807674574267</v>
+        <v>-2.131772404313125</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.879032508092138</v>
+        <v>-1.809360461264951</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.199870784461829</v>
+        <v>-2.130016436754552</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.000674</t>
+          <t>X ≈ 0.0006774</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.531988047747902</v>
+        <v>1.556832209410373</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2807372734287696</v>
+        <v>-0.2492689716880676</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.49690915754735</v>
+        <v>-3.456887908182019</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.916329726831904</v>
+        <v>-3.878502759036834</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.49830478743619</v>
+        <v>-2.432636918138101</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8256298461119016</v>
+        <v>-0.7605419193292065</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9966724902730348</v>
+        <v>-0.9304060443817903</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.08579537747951349</v>
+        <v>-0.01943537473019319</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.530012454099911</v>
+        <v>-1.463676485657814</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5147681146887777</v>
+        <v>-0.449521849367656</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.138691728218561</v>
+        <v>2.196307740164549</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.863230968598259</v>
+        <v>1.924152618155702</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.937044546630553</v>
+        <v>2.001441804430875</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.418076814725978</v>
+        <v>1.485536366578955</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.056966819744083</v>
+        <v>1.12472066029094</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.952055345445103</v>
+        <v>2.016796468697393</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.415019745249545</v>
+        <v>2.48216289514248</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>4.398706695536063</v>
+        <v>4.464499323977975</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.911248069123637</v>
+        <v>4.973282511575128</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>3.312500909315744</v>
+        <v>3.377155413434409</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>3.668327246548223</v>
+        <v>3.730158355493309</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>4.073110364928489</v>
+        <v>3.951941642994051</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.151866972501921</v>
+        <v>3.033963822894592</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.378331057183878</v>
+        <v>3.259607337146065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001406</t>
+          <t>X ≈ 0.001409</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.057234438865237</v>
+        <v>1.587880147831001</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.067456204132547</v>
+        <v>3.461243580888201</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.635244651662489</v>
+        <v>2.030790974683313</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8063189118320579</v>
+        <v>0.2195073470650399</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1149568965905488</v>
+        <v>0.1813981269104374</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4844223829503136</v>
+        <v>-0.1835410746399404</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1371634806230944</v>
+        <v>0.1607604874319435</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.364936066819297</v>
+        <v>2.637552537039248</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.299704114589083</v>
+        <v>1.577490665597672</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.205883119240788</v>
+        <v>2.464814596383427</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.2469872059790106</v>
+        <v>0.5255983831055744</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.03019753971521766</v>
+        <v>0.2592884503241919</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.5948785445727438</v>
+        <v>-0.2946620805891982</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.493003531988215</v>
+        <v>-2.172329420371668</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.710767891893518</v>
+        <v>-3.383832401746666</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8815526144700883</v>
+        <v>-0.5787373623598313</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.222356583609795</v>
+        <v>1.503743627665557</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.115678321638413</v>
+        <v>1.401641874461149</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.581243266499776</v>
+        <v>-2.267485597724608</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.837705228269051</v>
+        <v>-1.526423727128901</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.950420068198774</v>
+        <v>-3.176552732574777</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-3.584452361731159</v>
+        <v>-3.253543411456192</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.750855854375402</v>
+        <v>-2.978152924996301</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.491950850910051</v>
+        <v>-3.058800623052996</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.002138</t>
+          <t>X ≈ 0.002141</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9843819154846187</v>
+        <v>-1.604242374456952</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7051642833461713</v>
+        <v>0.7679717557311179</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.637527643126809</v>
+        <v>2.714065575759101</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.283436327507836</v>
+        <v>5.756970367856695</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.556816301403934</v>
+        <v>1.349467250905704</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.618193448421984</v>
+        <v>-1.856660433333403</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.997484739337551</v>
+        <v>2.804942525113489</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.646540756025054</v>
+        <v>-0.8680360444483171</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5986686697047006</v>
+        <v>-0.8257122352974662</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.009659104338184</v>
+        <v>1.796139213474824</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4183365168619204</v>
+        <v>-0.6463678087227862</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6540239545165036</v>
+        <v>0.4367217857627068</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.59127404259479</v>
+        <v>3.399736078082661</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.336730996244938</v>
+        <v>1.139241094833721</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.032030544650183</v>
+        <v>1.844618852555016</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.7593426553131408</v>
+        <v>-0.9682853089055854</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.8942082040315924</v>
+        <v>-1.105561745065899</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.425697897923826</v>
+        <v>4.251651238164591</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.937866702094382</v>
+        <v>1.745104982394345</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.201926462011997</v>
+        <v>2.619450348868504</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.306289386920412</v>
+        <v>1.381289167013911</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.490754104096347</v>
+        <v>-2.113279046953316</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.5357068287707136</v>
+        <v>-0.473689546123353</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.06862394080442158</v>
+        <v>0.548505313020101</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.00287</t>
+          <t>X ≈ 0.002871</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>101</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.719870125867416</v>
+        <v>-1.677827814444747</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.09557202950060173</v>
+        <v>-0.05137190077198284</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.402893456704355</v>
+        <v>1.452815435623705</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.663092384776327</v>
+        <v>1.722443017853486</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.169976635432292</v>
+        <v>7.272494585731394</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.381582307835664</v>
+        <v>6.477415146245754</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2587377618834736</v>
+        <v>-0.1819835063380566</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.419570038045137</v>
+        <v>1.50193105441366</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4861184887663086</v>
+        <v>-0.419243745265895</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7164981204003169</v>
+        <v>0.7703239015954964</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9764643446576144</v>
+        <v>-0.9177424617475225</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.672959603652743</v>
+        <v>2.726509534938934</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.065484239883268</v>
+        <v>4.562501694656234</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.807672043171088</v>
+        <v>7.306647331399816</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.177731638252062</v>
+        <v>4.677473597442336</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.791193939949189</v>
+        <v>5.270277027702761</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>6.644896699864304</v>
+        <v>6.714098871119816</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.564320375641017</v>
+        <v>4.633654574456813</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.1620730499772947</v>
+        <v>-0.09297845947335759</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.013474063353179</v>
+        <v>1.090321984357125</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.46793820486343</v>
+        <v>1.537874826292082</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.39198314922082</v>
+        <v>1.462028864882981</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.666758315703007</v>
+        <v>1.736503577365035</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.571014996236407</v>
+        <v>3.640869343943741</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.003602</t>
+          <t>X ≈ 0.003603</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>51</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-19.17663566446626</v>
+        <v>-19.19280283547973</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-11.76316955378581</v>
+        <v>-11.75531410111053</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.394004302911277</v>
+        <v>-7.367846328907014</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.084258079807981</v>
+        <v>-8.047389393606402</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-10.3893037751962</v>
+        <v>-10.3299585776383</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-14.09738400711522</v>
+        <v>-14.05882378433895</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-16.83356558582994</v>
+        <v>-16.81096213445729</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-22.92883245840798</v>
+        <v>-22.92579738535929</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-17.98234322951201</v>
+        <v>-19.00560209369466</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-18.81209246794389</v>
+        <v>-19.76738078481679</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-12.69537540401144</v>
+        <v>-13.65669733650583</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-7.123422469722342</v>
+        <v>-8.113672247024127</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-12.12833715117569</v>
+        <v>-12.06079154573744</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.445375636639227</v>
+        <v>-8.400823004501611</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-7.157578363483118</v>
+        <v>-7.105209889122754</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-8.532157150232656</v>
+        <v>-8.463493250020747</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.8513263134181273</v>
+        <v>-0.7823847351604911</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-8.771234260476859</v>
+        <v>-8.702251090819402</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-6.606846716023206</v>
+        <v>-6.538033947527623</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-8.372440702899887</v>
+        <v>-8.325325462740587</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-6.977023938409715</v>
+        <v>-6.907087316981062</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-10.97454762150337</v>
+        <v>-10.90450190584115</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-10.69977245502118</v>
+        <v>-10.6300271933591</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-10.77571379428965</v>
+        <v>-10.70585944658237</v>
       </c>
     </row>
     <row r="26">
@@ -2265,76 +2265,76 @@
         <v>42</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.314177428159844</v>
+        <v>-1.273900334720537</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-11.05311444740602</v>
+        <v>-11.05245464407479</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-7.78643235847094</v>
+        <v>-7.765583737123372</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-10.89168225429708</v>
+        <v>-10.86649293863883</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-13.60339061475123</v>
+        <v>-13.56022658845698</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-11.0292712198318</v>
+        <v>-10.98830642076707</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-16.45900009698383</v>
+        <v>-16.45213185535764</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-19.07949151721228</v>
+        <v>-19.08528527690143</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-19.02897185074903</v>
+        <v>-19.03779569402634</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-19.88507811278349</v>
+        <v>-19.81971497150344</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-14.89504826637984</v>
+        <v>-14.82976897479969</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-8.085512970159726</v>
+        <v>-8.019682844033973</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-11.54666681522373</v>
+        <v>-11.47977968479965</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-11.75894962780065</v>
+        <v>-11.73828226898986</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-10.0600455771938</v>
+        <v>-10.02703173127208</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-7.127072730767225</v>
+        <v>-7.058713974802274</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-4.896399642700224</v>
+        <v>-4.82777427571002</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.99528624133432</v>
+        <v>-4.926565647226298</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-7.159171904271552</v>
+        <v>-7.090654433133892</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-4.598216100243256</v>
+        <v>-4.54381285769837</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.3943908851884288</v>
+        <v>-0.324454263759776</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.470345940830974</v>
+        <v>-0.400300225168877</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.1955707743489086</v>
+        <v>-0.1258255126868235</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2715121136173124</v>
+        <v>-0.2016577659100989</v>
       </c>
     </row>
     <row r="27">
@@ -2344,79 +2344,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>15.65197569975808</v>
+        <v>15.17427893698821</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>9.7045219404826</v>
+        <v>9.424330664643428</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.285946593109848</v>
+        <v>7.995509889516633</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-11.60606800859878</v>
+        <v>-11.46818226301732</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-14.77747691593846</v>
+        <v>-14.51155847256207</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-6.446521453258391</v>
+        <v>-6.321412636226121</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.709000096983786</v>
+        <v>-4.514551417777255</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.287041203753461</v>
+        <v>-2.131168495053537</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4761135167313029</v>
+        <v>0.5811113282419811</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.35951644308138</v>
+        <v>-10.92096628283876</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.99139252523928</v>
+        <v>-10.6101135450602</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.469267488254907</v>
+        <v>-8.190475485414836</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.084159718011925</v>
+        <v>4.049523928537539</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.763076136623098</v>
+        <v>-1.600033421063664</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-5.152902828074794</v>
+        <v>-4.938071803602611</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1228939914342249</v>
+        <v>-1.652385987828957</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.1981364614777306</v>
+        <v>-1.729284080445694</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.427576920920536</v>
+        <v>0.8229626829471712</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.702551307957727</v>
+        <v>1.095873108232269</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.677730696798541</v>
+        <v>-2.548960862846592</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.970688479890931</v>
+        <v>2.31389837459286</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.894733424248322</v>
+        <v>2.238052413183759</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.169508590730452</v>
+        <v>2.512527125665812</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.315789473684127</v>
+        <v>-0.2660078302601647</v>
       </c>
     </row>
     <row r="28">
@@ -2429,568 +2429,568 @@
         <v>31</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-5.29523230477735</v>
+        <v>-5.261958012458521</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-5.612656340131736</v>
+        <v>-5.578983331518394</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6418777051531848</v>
+        <v>-0.6065232814846979</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.77206727717433</v>
+        <v>-7.735873559755426</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-11.33518016202654</v>
+        <v>-11.26950713213086</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.722743550546795</v>
+        <v>-4.657268947560524</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.46306530390266</v>
+        <v>-5.396673252752713</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-8.942421629131005</v>
+        <v>-8.875686377215573</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.897946984226749</v>
+        <v>-8.831240615419247</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-9.73753921881756</v>
+        <v>-9.601197711574066</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.237373500089319</v>
+        <v>-6.132253549465652</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.516467403564135</v>
+        <v>-6.416920112676998</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.189345718825507</v>
+        <v>-1.114810181060051</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.49252327659179</v>
+        <v>11.56180134142451</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>7.607785585941592</v>
+        <v>7.677851592231058</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>11.42865208717583</v>
+        <v>11.4980449657869</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>11.2945583930269</v>
+        <v>11.36412782880943</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>17.64118788015739</v>
+        <v>17.71090002821401</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.954085236637631</v>
+        <v>5.023565602686766</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>8.366935483870961</v>
+        <v>8.436217864267689</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>11.04954152648592</v>
+        <v>11.11947814791457</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.747780019230397</v>
+        <v>7.817825734892558</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>8.022555185712527</v>
+        <v>8.092300447374612</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>11.17242029805697</v>
+        <v>11.24227464576425</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.00653</t>
+          <t>X ≈ 0.006529</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.331245985952286</v>
+        <v>-1.297971693633457</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.5467561741196</v>
+        <v>12.58042918273294</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.094127721919207</v>
+        <v>-3.058773298250721</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>19.84472569445743</v>
+        <v>19.88091941187633</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>19.49544823311795</v>
+        <v>19.56112126301363</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>14.96087927823729</v>
+        <v>15.02635388122356</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.772532576856584</v>
+        <v>4.838924628006531</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.235701903831242</v>
+        <v>9.302437155746674</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.281216049774969</v>
+        <v>9.347922418582471</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.579004823467216</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>8.833074061023318</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.537296037296031</v>
+        <v>8.546328495733007</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.431162590719204</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.33236151603505</v>
+        <v>-2.263083451202327</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.770612006832415</v>
+        <v>1.840678013121881</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>11.88948158026339</v>
+        <v>11.95887445887446</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.231578362305008</v>
+        <v>2.301147798087534</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.88849970811448</v>
+        <v>6.958211856171104</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.104622871046296</v>
+        <v>7.17410323709543</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>11.51037101957348</v>
+        <v>11.58030764100213</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>11.43441596393087</v>
+        <v>11.50446167959303</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>11.709191130413</v>
+        <v>11.77893639207508</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.007261</t>
+          <t>X ≈ 0.00726</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.703498609040949</v>
+        <v>-3.67022431672212</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.9515217539244</v>
+        <v>-13.91784874531106</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-15.39122221801054</v>
+        <v>-15.35586779434205</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.197064101513</v>
+        <v>-6.160870384094096</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.31232337942444</v>
+        <v>13.37799640932012</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-16.26843210157574</v>
+        <v>-16.20295749858947</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.877424837267164</v>
+        <v>2.943816888417111</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.608662592845178</v>
+        <v>2.67539784476061</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.272461373467465</v>
+        <v>-7.205755004659963</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.124635993011061</v>
+        <v>-7.973774480148371</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.850276725895867</v>
+        <v>-7.724195840728243</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-8.129370629370484</v>
+        <v>-8.012737645272964</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.253861847857912</v>
+        <v>-9.126107311032357</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.134149897929575</v>
+        <v>-0.06408389164010941</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.4609101516920973</v>
+        <v>0.5303030303031733</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-9.778166958552248</v>
+        <v>-9.708454810495624</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-19.56204379562043</v>
+        <v>-19.4925634295713</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-19.37499999999986</v>
+        <v>-19.30571761960313</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-19.9182004089981</v>
+        <v>-19.84826378756944</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-19.99415546464056</v>
+        <v>-19.9241097489784</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-19.71938029815843</v>
+        <v>-19.64963503649635</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-29.7953216374269</v>
+        <v>-29.72546728971962</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.007993</t>
+          <t>X ≈ 0.007992</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.687781659110207</v>
+        <v>8.721055951429037</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.376364756962893</v>
+        <v>8.410037765576234</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.737893801073497</v>
+        <v>0.7732482247419838</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.204368269544261</v>
+        <v>-6.168174552125357</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.358988256516497</v>
+        <v>-0.2933152266208197</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.26135525884243</v>
+        <v>12.3268298618287</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.55382531115522</v>
+        <v>11.62021736230516</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.110391011721319</v>
+        <v>-1.043655759805887</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.141774851352956</v>
+        <v>5.208481220160458</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.441505197248333</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.649723274104275</v>
+        <v>4.685866573788964</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.370629370629288</v>
+        <v>4.395237864092508</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.24613815214223</v>
+        <v>3.28395510348485</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>28.02478134110788</v>
+        <v>28.0940594059406</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>27.36585010207066</v>
+        <v>27.43591610836013</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>27.96091015169187</v>
+        <v>28.03030303030295</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>21.57681645754295</v>
+        <v>21.64638589332547</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>21.47183304144767</v>
+        <v>21.54154518950429</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>21.68795620437948</v>
+        <v>21.75743657042862</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>21.875</v>
+        <v>21.94428238039673</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>15.08179959100213</v>
+        <v>15.15173621243078</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>15.00584453535944</v>
+        <v>15.0758902510216</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>21.53061970184157</v>
+        <v>21.60036496350365</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>21.45467836257318</v>
+        <v>21.52453271028046</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.008725</t>
+          <t>X ≈ 0.008724</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.341881716809624</v>
+        <v>3.375156009128453</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.1137840059645</v>
+        <v>10.14745701457784</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-12.54848563151044</v>
+        <v>-12.51313120784195</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-13.29263717178322</v>
+        <v>-13.25644345436432</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-13.65031740003735</v>
+        <v>-13.58464437014167</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.797364170207686</v>
+        <v>7.862838773193957</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.10798316262251</v>
+        <v>7.174375213772457</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.859786744183324</v>
+        <v>6.926521996098757</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.908892365975873</v>
+        <v>6.975598734783375</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.16107829270333</v>
+        <v>6.2102726155168</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.435437559818709</v>
+        <v>6.446384473829333</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9865134865134308</v>
+        <v>-0.924263619878019</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.253861847857614</v>
+        <v>-9.108966149913876</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-9.475218658892068</v>
+        <v>-9.405940594059345</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-10.13414989792937</v>
+        <v>-10.0640838916399</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-9.539089848307988</v>
+        <v>-9.469696969696912</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-24.06388124426648</v>
+        <v>-23.99416909620986</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-23.84775808133467</v>
+        <v>-23.77827771528553</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-9.37500000000005</v>
+        <v>-9.305717619603321</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-9.918200408997897</v>
+        <v>-9.848263787569245</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-9.994155464640464</v>
+        <v>-9.924109748978303</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-9.719380298158434</v>
+        <v>-9.649635036496349</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-16.9381787802841</v>
+        <v>-16.86832443257682</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.009457</t>
+          <t>X ≈ 0.009455</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>20</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-20.75745473908408</v>
+        <v>-20.72418044676525</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-11.23151914261737</v>
+        <v>-11.19784613400403</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-17.85640479188874</v>
+        <v>-17.82105036822025</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-18.3850129198966</v>
+        <v>-18.34881920247769</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-13.79657900121694</v>
+        <v>-13.73090597132126</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.655710684506452</v>
+        <v>-8.590236081520182</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.062163924180176</v>
+        <v>5.128555975330123</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.401575906523505</v>
+        <v>-5.334840654608072</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4063561377971325</v>
+        <v>-0.3396497689896307</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.875364006988868</v>
+        <v>-1.158861741322454</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.850276725895796</v>
+        <v>-10.65332061767911</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-13.1293706293707</v>
+        <v>-15.88577372483085</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-19.25386184785781</v>
+        <v>-22.14782468057582</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.475218658892196</v>
+        <v>-9.405940594059473</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-10.13414989792943</v>
+        <v>-10.06408389163996</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-14.53908984830808</v>
+        <v>-14.469696969697</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.778166958552291</v>
+        <v>-4.708454810495667</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.562043795620475</v>
+        <v>-4.492563429571341</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.375000000000043</v>
+        <v>-4.305717619603314</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.08179959100201017</v>
+        <v>0.1517362124306629</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.005844535359365466</v>
+        <v>0.07589025102152647</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-4.795321637426945</v>
+        <v>-4.725467289719667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.01019</t>
+          <t>X ≈ 0.01018</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-25.89634362797302</v>
+        <v>-25.86306933565419</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-20.67596358706175</v>
+        <v>-20.64229057844841</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-27.67121960670344</v>
+        <v>-27.63586518303496</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-39.49612403100782</v>
+        <v>-39.45993031358893</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-23.19472714936521</v>
+        <v>-23.12905411946954</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-23.00756253635843</v>
+        <v>-22.94208793337216</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.558206446190148</v>
+        <v>-1.491814395040201</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.274350019402362</v>
+        <v>9.341085271317795</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.315866084424997</v>
+        <v>9.382572453232498</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.816389940770989</v>
+        <v>8.883716419358016</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.537296037296088</v>
+        <v>8.60496701591002</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.52391592991996</v>
+        <v>18.59291606016492</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-3.919663103336568</v>
+        <v>-3.850385038503845</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-4.578594342373911</v>
+        <v>-4.508528336084446</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-9.539089848308045</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-9.778166958552248</v>
+        <v>-9.708454810495624</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-9.562043795620433</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-14.93055555555556</v>
+        <v>-14.86127317515883</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-9.848263787569302</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-4.438599909085006</v>
+        <v>-4.368554193422845</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-4.163824742602841</v>
+        <v>-4.094079480940756</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-4.239766081871345</v>
+        <v>-4.169911734164067</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1723 +3180,1723 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01067</t>
+          <t>X &gt; -0.01066</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3350</v>
+        <v>3354</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1651907792477232</v>
+        <v>0.1643053887889394</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1721977415265812</v>
+        <v>0.1712955194978321</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2021447098527673</v>
+        <v>0.2011718540020411</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1280104892692009</v>
+        <v>0.1271078211671295</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1653203424722065</v>
+        <v>0.1637613761328751</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1020970044175868</v>
+        <v>0.100616692962447</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0006048885885974187</v>
+        <v>-0.001982825113707065</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02452104417454137</v>
+        <v>-0.02587813125387584</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.05510964613465319</v>
+        <v>-0.05643021818330851</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03902362678038429</v>
+        <v>-0.04038281108581998</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01501059446545128</v>
+        <v>-0.01639248075093036</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.009204061851285417</v>
+        <v>-0.01060042318687948</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.01421312982744638</v>
+        <v>0.0127608678255271</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.159742468415935</v>
+        <v>-0.1609941017882903</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1162874388642265</v>
+        <v>-0.1176075312474509</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.0989469060805277</v>
+        <v>-0.1002740071746544</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.06639176408341996</v>
+        <v>-0.0677616818008957</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.02517034776479221</v>
+        <v>0.02368804664723001</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.009137685337279322</v>
+        <v>-0.01057474246204038</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.01677101967799643</v>
+        <v>0.01530679969392423</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.06135579223684573</v>
+        <v>-0.06274099936555189</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.08962085843531042</v>
+        <v>-0.09097506483060869</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.03570378368514326</v>
+        <v>-0.03711640758427848</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.06397835384480999</v>
+        <v>-0.06535995519369209</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.009939</t>
+          <t>X &gt; -0.009928</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3344</v>
+        <v>3348</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2611325295031364</v>
+        <v>0.2600724949928335</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1499425329619797</v>
+        <v>0.1490051683369131</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1825033584607922</v>
+        <v>0.1814891258598337</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.07977767331250618</v>
+        <v>0.07886620264235233</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1475267905694508</v>
+        <v>0.1458691554538234</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08385130460933965</v>
+        <v>0.08227332628329975</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01209339843281043</v>
+        <v>0.01057952934480255</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.01136426631188669</v>
+        <v>-0.01285844647844669</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.07184851317345675</v>
+        <v>-0.07327054409128664</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.05435606448217101</v>
+        <v>-0.05582012147537796</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.06058354746260619</v>
+        <v>-0.06203385337831691</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.005313518424365782</v>
+        <v>0.003776539719503091</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.0009816692808328753</v>
+        <v>-0.000580681590186316</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1728930774967736</v>
+        <v>-0.1742550669599368</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.09836105211969937</v>
+        <v>-0.09983009360599482</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.0820492755156792</v>
+        <v>-0.08352295301043711</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.04919070449815166</v>
+        <v>-0.05070799639128865</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.07257931010447294</v>
+        <v>0.07091310840718279</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.00797710614128988</v>
+        <v>0.006392729092588922</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.03360215053763937</v>
+        <v>0.03199121094565527</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1034409228909965</v>
+        <v>-0.1049035965815435</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1017466182568256</v>
+        <v>-0.1032142265903389</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.04822932655902434</v>
+        <v>-0.04975447513475473</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.07642211589580228</v>
+        <v>-0.07791651313658576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.009207</t>
+          <t>X &gt; -0.009197</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3334</v>
+        <v>3338</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2728550613329119</v>
+        <v>0.271678920486508</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2219307315715042</v>
+        <v>0.2208046596467881</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2290950149226205</v>
+        <v>0.2279170272789202</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0983899821109091</v>
+        <v>0.09734584285348546</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1674360875371477</v>
+        <v>0.1655541617340077</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1328511470147618</v>
+        <v>0.1310149669060365</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.003516422605230218</v>
+        <v>0.001810377273095298</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.01066842736260298</v>
+        <v>0.008944543828270923</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.05011381007084026</v>
+        <v>-0.05176495605267917</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0003827074674589426</v>
+        <v>-0.002117288038633092</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.03730988992321471</v>
+        <v>-0.03899321955578472</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.02962518652896051</v>
+        <v>0.02785258804927793</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.02864936290456654</v>
+        <v>0.02684326895033706</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1749794244423626</v>
+        <v>-0.1765499130558226</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.09825399604488894</v>
+        <v>-0.09993689432892694</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.05375172742234469</v>
+        <v>-0.05547102827437556</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.009546179183260506</v>
+        <v>0.007746132488485102</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1020725624058301</v>
+        <v>0.1001576296957651</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.006689358018377334</v>
+        <v>0.004893944045214482</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.03183043738766145</v>
+        <v>0.03000948991198271</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1339630700707701</v>
+        <v>-0.1356029075932454</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1620211720746099</v>
+        <v>-0.1636307070622323</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.0792003881134562</v>
+        <v>-0.08090188285753896</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1072592499044021</v>
+        <v>-0.1089304413074004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.008475</t>
+          <t>X &gt; -0.008466</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3320</v>
+        <v>3323</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3055314967028266</v>
+        <v>0.3202889104843223</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2558931424603088</v>
+        <v>0.2707875714718071</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1797451304888043</v>
+        <v>0.1950917086457977</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.08159384859692409</v>
+        <v>0.09722109275466551</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1226285526520456</v>
+        <v>0.137432960247196</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1170004443628656</v>
+        <v>0.1317643620371101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.02053056420153609</v>
+        <v>0.03558901915565826</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0289727080580704</v>
+        <v>0.04410104922876457</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.03226428950018345</v>
+        <v>-0.01708792035651641</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.02117858844708564</v>
+        <v>0.03651529038550194</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.01286853220751993</v>
+        <v>0.02814420546491903</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.02133486447506527</v>
+        <v>0.03668067317852319</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.03464262863855083</v>
+        <v>-0.01894512595364972</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2382105483484125</v>
+        <v>-0.2222671246716459</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1281402825448126</v>
+        <v>-0.1121175151764291</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.08612922312018867</v>
+        <v>-0.07029757029756922</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.0398802662321458</v>
+        <v>-0.006137386938789291</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.05346262653493739</v>
+        <v>0.08721826642744901</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.07332199110915383</v>
+        <v>-0.03960280438344199</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.01880264741275539</v>
+        <v>0.01478749164146365</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1830213539272378</v>
+        <v>-0.1669649300828269</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2409947181023355</v>
+        <v>-0.224861628677651</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1288955044215996</v>
+        <v>-0.1129322687466541</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1266469386317226</v>
+        <v>-0.1106613914349381</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007743</t>
+          <t>X &gt; -0.007734</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3307</v>
+        <v>3310</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2459747192116524</v>
+        <v>0.2307015060158193</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2575300026818041</v>
+        <v>0.2423286550149726</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1566533519178961</v>
+        <v>0.1719426247728109</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.06090142499545692</v>
+        <v>0.07646700292262665</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1035184646699605</v>
+        <v>0.1181413933510598</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.09713060443587551</v>
+        <v>0.1117142908539535</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.06348747162173396</v>
+        <v>0.04824039215829856</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.04296330457196973</v>
+        <v>0.02780206329777712</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.01867170539730978</v>
+        <v>-0.03379337107552516</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.03801460939858003</v>
+        <v>0.02303825979210217</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.02860245458032296</v>
+        <v>0.01355788032526561</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.008061558694471671</v>
+        <v>-0.006896880506772618</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.04373221264523153</v>
+        <v>-0.05835569351643244</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2170763187232509</v>
+        <v>-0.2314904584763866</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1643158104482794</v>
+        <v>-0.1786107150275456</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.09431012591818444</v>
+        <v>-0.1088287152501834</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.07752874462956783</v>
+        <v>-0.07406042754295328</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.01360311913177981</v>
+        <v>-0.01011393568415997</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1115607038329927</v>
+        <v>-0.1081337373564537</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.08777559649652744</v>
+        <v>-0.08446799690481299</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2203152126233334</v>
+        <v>-0.2346205639049543</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.3084498133864102</v>
+        <v>-0.3226604736160823</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1667805399964024</v>
+        <v>-0.1811964982903689</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.1944749485850537</v>
+        <v>-0.2088509755202281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.007011</t>
+          <t>X &gt; -0.007003</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3295</v>
+        <v>3299</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2300088324162175</v>
+        <v>0.2284693575105194</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1825004258051237</v>
+        <v>0.1810025942423152</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1166134752472487</v>
+        <v>0.11513076621344</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.007087619822875979</v>
+        <v>-0.008453520339898546</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.006802179541196551</v>
+        <v>0.004299312346446982</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.0003161595467560119</v>
+        <v>-0.002803655125184434</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.0592974968951907</v>
+        <v>0.056702447594283</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.03970752192002891</v>
+        <v>0.0371222860030116</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.02230254658130804</v>
+        <v>-0.02481259556513749</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.03739544592485089</v>
+        <v>0.03477755014290551</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.05719227924488735</v>
+        <v>0.05456107857472148</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.03759851763481947</v>
+        <v>0.03497708640342978</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.04054868598182537</v>
+        <v>-0.04312705457262211</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2439837920640358</v>
+        <v>-0.2463275348090974</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1886458107359701</v>
+        <v>-0.1910872179175485</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1205556266242169</v>
+        <v>-0.1230545014574034</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.1032259410033092</v>
+        <v>-0.0877290839815501</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.0386940715483064</v>
+        <v>-0.02322478628254743</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1681044016810347</v>
+        <v>-0.1525694846727248</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.144930281903612</v>
+        <v>-0.129460805551183</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2153501967481048</v>
+        <v>-0.217736834207706</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.3338582247254891</v>
+        <v>-0.3361061137163617</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1926812690322137</v>
+        <v>-0.1950895819508887</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1898588149686375</v>
+        <v>-0.1922754133934603</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.006279</t>
+          <t>X &gt; -0.006271</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3264</v>
+        <v>3268</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2211920452534599</v>
+        <v>0.2193352573886997</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2372784220706308</v>
+        <v>0.2353824731376406</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1843765497452878</v>
+        <v>0.1824640951483048</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.08603163584072604</v>
+        <v>-0.0876556964100601</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.06858455338706904</v>
+        <v>-0.07163882224892149</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.01660449511075512</v>
+        <v>-0.01971350414833495</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.01010346516034133</v>
+        <v>-0.01326520029125078</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06422498128102205</v>
+        <v>0.06095530888510581</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.02926305936182416</v>
+        <v>-0.03241840599964263</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.03831792825839386</v>
+        <v>0.03503521872809756</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1167562411372458</v>
+        <v>0.1133912161059385</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.06910265307212882</v>
+        <v>0.06577823884379086</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.09075861022795806</v>
+        <v>-0.09395262670371807</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1718272748407941</v>
+        <v>-0.1749366270163719</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.04857532580228252</v>
+        <v>-0.05187387942994803</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.01456346872038949</v>
+        <v>0.01121906083737656</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.03332822764392063</v>
+        <v>0.04818797029562205</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.09950888242634903</v>
+        <v>0.1143377345700571</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.06372626732431286</v>
+        <v>-0.04879814839770091</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.04207466340269406</v>
+        <v>-0.02720951810525207</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1385860839290771</v>
+        <v>-0.1417520174684128</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.196237522203333</v>
+        <v>-0.19933910677657</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.02565901178783747</v>
+        <v>-0.02895592973587213</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.08331183350532712</v>
+        <v>-0.08654440110272787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.005547</t>
+          <t>X &gt; -0.00554</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3239</v>
+        <v>3241</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1743913204068193</v>
+        <v>0.1746600885294214</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.254506760586473</v>
+        <v>0.2549095033009934</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2429326554082749</v>
+        <v>0.2441307282396608</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.05474895427355619</v>
+        <v>-0.05297734835367152</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.03435461840616938</v>
+        <v>-0.03403519750975192</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1062521350479457</v>
+        <v>-0.1059921690995154</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.001626825094405149</v>
+        <v>-0.001008268065824325</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.07541537486235228</v>
+        <v>0.07613850637107333</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.01910676115340948</v>
+        <v>-0.01834920575363697</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.05494580280689831</v>
+        <v>0.05608169012372599</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1318826096933208</v>
+        <v>0.1020789565031706</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1167832167832188</v>
+        <v>0.08713183755818221</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.02591654549402733</v>
+        <v>-0.003071499218471274</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.0848245702221746</v>
+        <v>-0.1136329017517141</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.04447652646231859</v>
+        <v>0.01594073132095275</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1343543907554192</v>
+        <v>0.1054261830123977</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1542964328973113</v>
+        <v>0.1438450864268859</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>0.211446606633146</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.117364342480677</v>
+        <v>0.1068202376089715</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.04528985507246119</v>
+        <v>0.03460297225862519</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.0477500697012232</v>
+        <v>-0.07637722776659217</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.07437761829683609</v>
+        <v>-0.1029564958177502</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.09543451665637548</v>
+        <v>0.06658951624887521</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.007086513236885139</v>
+        <v>-0.02167216475819345</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.004815</t>
+          <t>X &gt; -0.004808</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3201</v>
+        <v>3205</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.08131000331189853</v>
+        <v>0.07892969995922527</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2285174229765019</v>
+        <v>0.2259264758151147</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.247991128402937</v>
+        <v>0.2625356992368495</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.01372237469305304</v>
+        <v>0.001234232899932408</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.05089366070405532</v>
+        <v>-0.03780644721619097</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03262986596265449</v>
+        <v>-0.01960009315681788</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.08238347540692104</v>
+        <v>0.07774647287521219</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2258425567158326</v>
+        <v>0.2210024555828412</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.09865509427469021</v>
+        <v>0.09397350946117911</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2449968632428323</v>
+        <v>0.2400690415424265</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1951636724858474</v>
+        <v>0.190316771653066</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2143404540664875</v>
+        <v>0.2094446278502744</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.07345051589183527</v>
+        <v>0.06863750478220965</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.03596632244352094</v>
+        <v>-0.04066368055598701</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1026840067137655</v>
+        <v>0.09775862314373285</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.09307972775179962</v>
+        <v>0.08821087588211185</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1148463827300645</v>
+        <v>0.1285565566703113</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.2155966834808041</v>
+        <v>0.2292398935542224</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1385176516659072</v>
+        <v>0.1521857134639149</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.09457878315132007</v>
+        <v>0.1082474676785239</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.006893223960851458</v>
+        <v>0.002110277268606353</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.08157351022283166</v>
+        <v>-0.08625505611902895</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1806821628034641</v>
+        <v>0.1756924744206785</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.123453745266012</v>
+        <v>0.1185264700307656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.004083</t>
+          <t>X &gt; -0.004077</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3166</v>
+        <v>3170</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.01273143391033216</v>
+        <v>0.01004602351569872</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1966038956751817</v>
+        <v>0.1936550850834209</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.04378353202847052</v>
+        <v>0.05829181497901459</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1502318279726964</v>
+        <v>-0.1353799162655491</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2780604826984643</v>
+        <v>-0.2653369350745152</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1674745690319241</v>
+        <v>-0.1548939597374286</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.01131071324790156</v>
+        <v>-0.01661037746330862</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1367622587401414</v>
+        <v>0.1312474900514786</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.007689983796105082</v>
+        <v>0.002337947369895232</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1641340604648747</v>
+        <v>0.1585100602623299</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1107050236322848</v>
+        <v>0.1051704315096558</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.164617409659904</v>
+        <v>0.1589856683253643</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.02842104181243599</v>
+        <v>-0.03391832138639472</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1366359817267693</v>
+        <v>-0.1420211225274812</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.02072834783491118</v>
+        <v>-0.02632429440899386</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.02599051727657553</v>
+        <v>0.02038801613871755</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.01355543026030404</v>
+        <v>-0.0003395474804861465</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1524761688121856</v>
+        <v>0.1655609375358722</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1352125903776766</v>
+        <v>0.1482683284627342</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.00591482649841879</v>
+        <v>0.007235421682580068</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.08860116633465509</v>
+        <v>-0.0940879287606009</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1456706161557122</v>
+        <v>-0.1510958776038791</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.211153329880716</v>
+        <v>0.2053003151277437</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.1225558104568591</v>
+        <v>0.1168040036557656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003352</t>
+          <t>X &gt; -0.003345</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3103</v>
+        <v>3106</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1671077875910711</v>
+        <v>0.1487275587778143</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2654389105366732</v>
+        <v>0.2470248406174491</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2986811297678642</v>
+        <v>0.2983570391872234</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1089790384815998</v>
+        <v>-0.07666100074207094</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3601655772194547</v>
+        <v>-0.3304630211665369</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2191009978968026</v>
+        <v>-0.1895788579930482</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.01993469591380403</v>
+        <v>0.03142569322231026</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1124941288742818</v>
+        <v>0.123954009969971</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.04413044117832499</v>
+        <v>0.05564937630945366</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1231175371558209</v>
+        <v>0.1347182285159079</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1272513639919168</v>
+        <v>0.138794460837552</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.2200192229093929</v>
+        <v>0.231531019759835</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.0137256882810064</v>
+        <v>0.0256645981766539</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1243189159615312</v>
+        <v>-0.112200626162128</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.007283724699952643</v>
+        <v>0.01941000688283623</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.04290372082378724</v>
+        <v>0.05487739586679652</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.05903563248912747</v>
+        <v>-0.02777863109603373</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.08030843546512756</v>
+        <v>0.1115387607033469</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.09046585688922448</v>
+        <v>0.1215844803965425</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.07141132925652016</v>
+        <v>0.1024522099239107</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.06630085973845468</v>
+        <v>-0.05411775990766898</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1551860604537723</v>
+        <v>-0.1428999677686278</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.106650629676615</v>
+        <v>0.1186301710993973</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.08221622915382909</v>
+        <v>0.09423650937889505</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.00262</t>
+          <t>X &gt; -0.002614</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3005</v>
+        <v>3009</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.02713437746136549</v>
+        <v>0.02251922320169797</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2055791126627255</v>
+        <v>0.2006718954153115</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3526555080807228</v>
+        <v>0.3657493773642386</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.210409745293461</v>
+        <v>-0.1966333198656898</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3586923053911519</v>
+        <v>-0.3487060251755594</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4507568888842641</v>
+        <v>-0.4407105229037569</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.01346408714788794</v>
+        <v>-0.02257656216600878</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.0911270613450057</v>
+        <v>0.08182601205857054</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.01393407015152803</v>
+        <v>-0.02309520582578983</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.05959197252902726</v>
+        <v>0.05020387624745126</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.07765491615094078</v>
+        <v>-0.08682313708029454</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1265975403906481</v>
+        <v>0.1171082962631758</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1825517317715324</v>
+        <v>-0.1918176632901947</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2515955666558938</v>
+        <v>-0.2608113694073211</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1607015076207645</v>
+        <v>-0.1701495197473477</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1101389850942311</v>
+        <v>-0.1195643437022653</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2110321480346542</v>
+        <v>-0.2006290320475728</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.03584831876425199</v>
+        <v>0.04602428704916406</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.07250769939617641</v>
+        <v>0.0826108153673033</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.08619973413094328</v>
+        <v>-0.07596994364045173</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2107536004873225</v>
+        <v>-0.2201097371044938</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3001082414945699</v>
+        <v>-0.3093638173942139</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1052751750712773</v>
+        <v>-0.1147513155661173</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.005011141275254261</v>
+        <v>-0.004629802182229525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001888</t>
+          <t>X &gt; -0.001883</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0358677674971517</v>
+        <v>-0.01866340459314841</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3754517797781887</v>
+        <v>0.358634063252893</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4608812983610235</v>
+        <v>0.4656494429333193</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3722220430280956</v>
+        <v>-0.3667080142596717</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.683454169829929</v>
+        <v>-0.7178543045903609</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4769125247923114</v>
+        <v>-0.4768101555943005</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2237932408987717</v>
+        <v>-0.2418143950402012</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.03120553615315913</v>
+        <v>-0.01401487919738997</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2129054797755003</v>
+        <v>-0.1958384802861133</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.06348241413684974</v>
+        <v>-0.04519202363815822</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.05726585317970034</v>
+        <v>0.04041553850493074</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2850939047044818</v>
+        <v>0.1991699144606969</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2277748913360327</v>
+        <v>-0.3122103606190763</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.3590043234711118</v>
+        <v>-0.373570249471868</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.3012226441876962</v>
+        <v>-0.3495992119742226</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1379756421799101</v>
+        <v>-0.1872169975618192</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3068882778330106</v>
+        <v>-0.3004782181726995</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.008052016023505359</v>
+        <v>-0.001239752984290021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.1195350848190415</v>
+        <v>-0.1132049916354489</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.120904496340188</v>
+        <v>-0.1149258512042479</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.3296369501416052</v>
+        <v>-0.3435550327733452</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.4894467098446071</v>
+        <v>-0.5033142151333223</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3683684349344318</v>
+        <v>-0.3826193296900655</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2490738189277693</v>
+        <v>-0.26317678692633</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001156</t>
+          <t>X &gt; -0.001151</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1640392548919465</v>
+        <v>-0.1906419660988803</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.04374753235048701</v>
+        <v>0.0169134016510526</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.05116398888917928</v>
+        <v>-0.05716666368698498</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7442555706191172</v>
+        <v>-0.7494498555355733</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.238340856530243</v>
+        <v>-1.213975050860313</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9183079863708059</v>
+        <v>-0.9149431195257236</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9222169213117368</v>
+        <v>-0.939786835168043</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6557897011564862</v>
+        <v>-0.6738624117912835</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8925452471611308</v>
+        <v>-0.9102624377331949</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7838120229736063</v>
+        <v>-0.8019612731654604</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4505015291928416</v>
+        <v>-0.4690707112069461</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1833436428638748</v>
+        <v>-0.202418213630942</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5736968684801909</v>
+        <v>-0.5925741848535395</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8105524923504888</v>
+        <v>-0.8291615678421707</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9068430712227524</v>
+        <v>-0.903349534202718</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.5522230565632071</v>
+        <v>-0.5491572395620352</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6863167507121304</v>
+        <v>-0.6609819356958155</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.3187074990927883</v>
+        <v>-0.2936010970672598</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5684275733147643</v>
+        <v>-0.5653316216193147</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4719196093163092</v>
+        <v>-0.4689446364888212</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6171857528536506</v>
+        <v>-0.6362562828788683</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7460351638886777</v>
+        <v>-0.764950589819243</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.674626631366408</v>
+        <v>-0.6935704476867386</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.690731720195906</v>
+        <v>-0.7096896789006948</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0004238</t>
+          <t>X &gt; -0.0004197</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1240786341511395</v>
+        <v>-0.1594289160804081</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.008441122363457509</v>
+        <v>-0.04399998015784945</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1216546373695735</v>
+        <v>-0.1336087581620617</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.683338642879896</v>
+        <v>-0.6946038237114536</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.367460910963992</v>
+        <v>-1.348994213607234</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.028128089057567</v>
+        <v>-1.033658322760182</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.619977175341937</v>
+        <v>-0.6502796639034187</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3597265958062934</v>
+        <v>-0.3906498884995173</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6369438683849182</v>
+        <v>-0.6673918579737403</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4851510144702971</v>
+        <v>-0.516307233086728</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6583488598587977</v>
+        <v>-0.6890796943725661</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1826352341816175</v>
+        <v>-0.2143583128493205</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5516701847722558</v>
+        <v>-0.5834031161542086</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5758205505516329</v>
+        <v>-0.6076573322568279</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3749065617299365</v>
+        <v>-0.3818168242290483</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.1842511386306285</v>
+        <v>-0.1913464542330487</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.01726956396234414</v>
+        <v>0.001027062212529017</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.2906798572825195</v>
+        <v>0.3087420940615573</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1130554185218529</v>
+        <v>-0.1202504459083542</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.4172049956933677</v>
+        <v>-0.4239971894957364</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.6334093706524158</v>
+        <v>-0.6654680886445732</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.8562244301578019</v>
+        <v>-0.8879651706651472</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.5814492636756725</v>
+        <v>-0.5880767067503285</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.8043772648525191</v>
+        <v>-0.8107386075490766</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003081</t>
+          <t>X &gt; 0.0003117</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.301858632028164</v>
+        <v>-1.272905401227966</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.7246253875484072</v>
+        <v>-0.7880100684302391</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.616880596160087</v>
+        <v>-1.679581030029532</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.695637413002885</v>
+        <v>-2.708183124284687</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.513461942552482</v>
+        <v>-2.447788912656804</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.961333825896062</v>
+        <v>-1.895859222909792</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.365586819263953</v>
+        <v>-1.299194768114006</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.187937085220476</v>
+        <v>-1.121201833305044</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.551713824250761</v>
+        <v>-1.535919030952378</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.086244768148177</v>
+        <v>-1.122703320127556</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.9032931792778101</v>
+        <v>-0.9398845538780378</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1769026220580088</v>
+        <v>-0.2149843222895385</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5814537971559517</v>
+        <v>0.5411656796474631</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4515882944473049</v>
+        <v>0.4660886563976376</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.2073429445899961</v>
+        <v>-0.1920546411829207</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.5341702249520281</v>
+        <v>0.4937399590050404</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.04110217182874</v>
+        <v>1.055123313270663</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.126594946209657</v>
+        <v>2.139669617683694</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5112162776396403</v>
+        <v>0.5257348320938391</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.5700045829514195</v>
+        <v>0.5843922705066191</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.9992307836625969</v>
+        <v>0.9575970182915015</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.6119051414200456</v>
+        <v>0.5154506905820355</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.886680307902175</v>
+        <v>0.789925403064089</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.7745313037495691</v>
+        <v>0.6778324353032943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.00104</t>
+          <t>X &gt; 0.001043</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.557170025987332</v>
+        <v>-2.526823522344159</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9212548704608281</v>
+        <v>-1.026737935372871</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.7840827984103029</v>
+        <v>-0.892017796985769</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.15490633499374</v>
+        <v>-2.189589106239758</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.520176120017787</v>
+        <v>-2.45450309012211</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.464417551689046</v>
+        <v>-2.398942948702775</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.529005102928359</v>
+        <v>-1.462613051778412</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.676153703768868</v>
+        <v>-1.609418451853436</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.561326898031112</v>
+        <v>-1.567931269938732</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.339392251245584</v>
+        <v>-1.42100463322884</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.250803735118382</v>
+        <v>-2.329599393169403</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.080622276274447</v>
+        <v>-1.162882305158796</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.01903335181555832</v>
+        <v>-0.1059143491917567</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.02346207989415205</v>
+        <v>0.01434926101305933</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.7673952805151742</v>
+        <v>-0.7755463422328432</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.09391151277303322</v>
+        <v>-0.1811594202898519</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.4324967745839885</v>
+        <v>0.4227711175999644</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.120115736295837</v>
+        <v>1.10948714201097</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.437869423097311</v>
+        <v>-1.445070025877371</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6448412698412653</v>
+        <v>-0.6531416618754022</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.1831010712496095</v>
+        <v>-0.2709850557331066</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9213077825213603</v>
+        <v>-1.00733299864816</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.1167312915359133</v>
+        <v>-0.2044567009613374</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.3788760140847316</v>
+        <v>-0.466208030460372</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001772</t>
+          <t>X &gt; 0.001775</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>576</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.812668419273891</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.462905167817809</v>
+        <v>-2.429232159204467</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.840749961800846</v>
+        <v>-1.805395538132359</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.070007192519775</v>
+        <v>-2.942431747897508</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.263455671701898</v>
+        <v>-3.278222220444782</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.076291058695112</v>
+        <v>-3.091256034347403</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.95912282648797</v>
+        <v>-1.969917282781651</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.924962695374234</v>
+        <v>-2.936596885882395</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.44546495401444</v>
+        <v>-2.550875624793854</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.434980820597275</v>
+        <v>-2.635323142482669</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.022690518999177</v>
+        <v>-3.221848698255336</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.40523269833615</v>
+        <v>-1.60731066624723</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1589188084462094</v>
+        <v>-0.04693068313005</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8011198557883574</v>
+        <v>0.6976863489457799</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.1421886167510564</v>
+        <v>0.03954305136522152</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.1494914665708507</v>
+        <v>-0.05691631339298908</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.1884081530447546</v>
+        <v>0.08496720820445347</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.121487020686509</v>
+        <v>1.018188788120291</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.084535145101405</v>
+        <v>-1.188065159675098</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.276213171577119</v>
+        <v>-0.3802410164836871</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.6720773687798243</v>
+        <v>0.637004843279918</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.09832213130722778</v>
+        <v>-0.3053922446456525</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.6972863685082302</v>
+        <v>0.6623233690495809</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.274122807017541</v>
+        <v>0.3439771547248185</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002504</t>
+          <t>X &gt; 0.002506</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.595780391925913</v>
+        <v>-4.562506099607084</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.548467427307564</v>
+        <v>-3.514794418694223</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.375264665587252</v>
+        <v>-3.339910241918766</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.932375951130631</v>
+        <v>-5.896182233711727</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.915157256892016</v>
+        <v>-4.849484226996339</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.575918911166333</v>
+        <v>-3.510444308180062</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.657540803589022</v>
+        <v>-3.591148752439075</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.705680702563811</v>
+        <v>-3.638945450648379</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.078283261225465</v>
+        <v>-3.136628775646109</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.957969326344397</v>
+        <v>-4.139959198226379</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.915091540710542</v>
+        <v>-4.096314302608242</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.1108521108521</v>
+        <v>-2.301330987162224</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.017202915143159</v>
+        <v>-1.217194281123199</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.6175887657018393</v>
+        <v>0.5477631096443076</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.5053795963052892</v>
+        <v>-0.5733431508992126</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.2525252525252526</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.5593745970779196</v>
+        <v>0.489193317919522</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.01072509808712852</v>
+        <v>-0.07968450887148748</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.120183330504155</v>
+        <v>-2.183978742796356</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.468023255813954</v>
+        <v>-1.398740875417225</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.4547599639624167</v>
+        <v>0.3842943519655861</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.3788049083198075</v>
+        <v>0.3084483905564852</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.119780541002413</v>
+        <v>1.0480393821083</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.344538502433231</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003236</t>
+          <t>X &gt; 0.003237</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.481350321413444</v>
+        <v>-5.448076029094615</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.611706558949344</v>
+        <v>-4.578033550336002</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.846587745927046</v>
+        <v>-4.811233322258559</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.271224432614176</v>
+        <v>-8.235030715195272</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-8.636494217638223</v>
+        <v>-8.570821187742546</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.642100688968782</v>
+        <v>-6.576626085982511</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.704123447528843</v>
+        <v>-4.637731396378896</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.283882912324501</v>
+        <v>-5.217147660409069</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.87648034054979</v>
+        <v>-3.970841201385937</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-5.397363265738342</v>
+        <v>-5.647371335253759</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.819973695592694</v>
+        <v>-5.072106873814718</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.583916083916087</v>
+        <v>-3.844832180877177</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.890225484221411</v>
+        <v>-2.991508243292571</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.596430780104249</v>
+        <v>-1.527152715271527</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.25536201914155</v>
+        <v>-2.185296012852085</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.180427234326288</v>
+        <v>-1.287878787878789</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.314520928475211</v>
+        <v>-1.421795924856262</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.419504344570491</v>
+        <v>-1.526636628677444</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-2.723138020544447</v>
+        <v>-2.825896762904634</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-2.162860476746133</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.1427752007581446</v>
+        <v>0.03015566531824021</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.06682014511553547</v>
+        <v>-0.04569029609086073</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.9513514091586401</v>
+        <v>0.8366871519534982</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.6489801740122729</v>
+        <v>-0.7589019401755479</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.003968</t>
+          <t>X &gt; 0.003969</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.959835691465088</v>
+        <v>-2.926561399146259</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.295011206109415</v>
+        <v>-3.261338197496073</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.37756881305269</v>
+        <v>-4.342214389384203</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-8.305647840531556</v>
+        <v>-8.269454123112652</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-8.313774768412749</v>
+        <v>-8.248101738517072</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.269467298263109</v>
+        <v>-5.203992695276838</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.470904858888566</v>
+        <v>-2.40451280773862</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.035173790121405</v>
+        <v>-1.968438538205973</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.279372010813063</v>
+        <v>-1.212665642005561</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.92750337652361</v>
+        <v>-3.057009889470613</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.369989987544464</v>
+        <v>-3.497235961594413</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.932238012883175</v>
+        <v>-3.061699650756687</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.189345718825507</v>
+        <v>-1.32771886046995</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3354337126555649</v>
+        <v>-0.266155647822842</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.352787890760965</v>
+        <v>-1.282721884471499</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.173140367519288</v>
+        <v>0.02851091560768282</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.399802247492936</v>
+        <v>-1.539097977642179</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.06593674272491512</v>
+        <v>-0.2102469251909724</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.008086961088061</v>
+        <v>-2.144893178675247</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.101618705035968</v>
+        <v>-1.032336324639239</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.453640746236701</v>
+        <v>1.302815349121346</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.099707351243921</v>
+        <v>1.946393848143906</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.096504178375866</v>
+        <v>2.940293021057606</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.215508687482846</v>
+        <v>1.065899616755196</v>
       </c>
     </row>
     <row r="27">
@@ -4906,79 +4906,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.253953338523907</v>
+        <v>-3.220679046205078</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.908456584260662</v>
+        <v>-1.874783575647321</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.768325115573688</v>
+        <v>-3.732970691905201</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.843462966581981</v>
+        <v>-7.807269249163078</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.36839661715225</v>
+        <v>-7.302723587256573</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.240055533557218</v>
+        <v>-4.174580930570947</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.011044697273555</v>
+        <v>1.077779949188987</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.892896896749967</v>
+        <v>1.959603265557469</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.103212108254759</v>
+        <v>-0.07381661215968904</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.31019233771007</v>
+        <v>-1.480429238905337</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.011227169455012</v>
+        <v>-2.179346709580223</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6617499664882232</v>
+        <v>0.479003828605677</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.706215940263988</v>
+        <v>1.775494005096711</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.2034028446866003</v>
+        <v>0.2734688509760659</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.477859304234329</v>
+        <v>1.289796701189111</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.7748784577112104</v>
+        <v>-0.9538250771385748</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.8150533804308111</v>
+        <v>0.629097932120402</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.08746752443399</v>
+        <v>-1.264715328305478</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.4766949152542423</v>
+        <v>-0.4074125348575137</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.783927250576511</v>
+        <v>1.592414178532394</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.559036024721138</v>
+        <v>2.364025844241937</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.684875020990503</v>
+        <v>3.485958183842634</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.481274107253945</v>
+        <v>1.291481862822749</v>
       </c>
     </row>
     <row r="28">
@@ -4991,158 +4991,158 @@
         <v>199</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-6.674121405750796</v>
+        <v>-6.640847113431967</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.94899738448126</v>
+        <v>-5.913642960812773</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.162790697674417</v>
+        <v>-7.126596980255513</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.028060482698464</v>
+        <v>-5.962387452802787</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.840895869691678</v>
+        <v>-3.775421266705408</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.8862379982542876</v>
+        <v>0.9526300494042346</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.607683352735734</v>
+        <v>1.674418604651166</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.149199417758368</v>
+        <v>2.21590578656587</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.176871544677375</v>
+        <v>1.942990110529379</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4411805605364307</v>
+        <v>0.2170497526912953</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8429384685666008</v>
+        <v>-1.061699650756701</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.04262056420252947</v>
+        <v>-0.1848617176128116</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.333826567238532</v>
+        <v>2.403104632071255</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.172382765387155</v>
+        <v>1.242448771676621</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.767442815008536</v>
+        <v>1.836835693619612</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8792136932107368</v>
+        <v>-0.8096442574282108</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.5233405791361889</v>
+        <v>0.5930527271928128</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.773099072002346</v>
+        <v>-1.703618705953211</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.07851758793970021</v>
+        <v>-0.00923520754297158</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.388332254318627</v>
+        <v>1.458268875747279</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.317402324304162</v>
+        <v>2.387448039966323</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.597202616414428</v>
+        <v>3.666947878076513</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.511211025889679</v>
+        <v>1.581065373596957</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006164</t>
+          <t>X &gt; 0.006163</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>168</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.928559275573278</v>
+        <v>-6.895284983254449</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.713438932229444</v>
+        <v>-3.679765923616102</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.928287325309661</v>
+        <v>-6.892932901641174</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.050364662171461</v>
+        <v>-7.014170944752557</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-5.048770541870063</v>
+        <v>-4.983097511974385</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.678173976200554</v>
+        <v>-3.612699373214284</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.05783563139039</v>
+        <v>2.124227682540337</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.554428914865909</v>
+        <v>3.621164166781341</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.073167625322277</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.673532797913801</v>
+        <v>1.388647385827397</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2039627039627092</v>
+        <v>-0.07353397028332154</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.2699476759517552</v>
+        <v>-0.01326408447671668</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.6438289601554885</v>
+        <v>0.7131070249882114</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.01510227888181248</v>
+        <v>0.0549637274076531</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.01528032449851935</v>
+        <v>0.05411255411255667</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.125564494837924</v>
+        <v>-3.055995059055398</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-2.635309815695109</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-3.014424748001389</v>
+        <v>-2.944944381952254</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.636904761904766</v>
+        <v>-1.567622381508038</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3943908851884288</v>
+        <v>-0.324454263759776</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.315368344883247</v>
+        <v>1.385414060545408</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.780619701841566</v>
+        <v>2.850364963503651</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.2715121136173764</v>
+        <v>-0.2016577659100989</v>
       </c>
     </row>
     <row r="30">
@@ -5155,486 +5155,486 @@
         <v>147</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-7.728175459804845</v>
+        <v>-7.694901167486016</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-6.036323947422154</v>
+        <v>-6.002650938808813</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.476024411508291</v>
+        <v>-7.440669987839804</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-10.89252042740415</v>
+        <v>-10.85632670998525</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-8.555087509725496</v>
+        <v>-8.489414479829819</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-6.275421266705408</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.670021782038077</v>
+        <v>1.736413833188024</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.742818487870863</v>
+        <v>2.809553739786296</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.460010228569182</v>
+        <v>3.526716597376684</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.780125911750844</v>
+        <v>3.429476597015871</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.653124634648492</v>
+        <v>0.3251578607994077</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-1.304942893999936</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7504604873135534</v>
+        <v>-1.076753609504706</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.068999028182709</v>
+        <v>1.138277093015432</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.2702043196981307</v>
+        <v>-0.2001383134086652</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.715960596607367</v>
+        <v>-1.646567717996291</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-3.890870617286907</v>
+        <v>-3.821301181504381</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.995854033382187</v>
+        <v>-3.926141885325563</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-4.460002979293911</v>
+        <v>-4.390522613244777</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-2.9124149659864</v>
+        <v>-2.843132585589672</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-2.095071157297276</v>
+        <v>-2.025134535868624</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.1302098864092684</v>
+        <v>-0.06016417074710745</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.505109497759932</v>
+        <v>1.574854759422017</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.291920276882685</v>
+        <v>-1.222065929175407</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.007627</t>
+          <t>X &gt; 0.007626</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>137</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-8.021947492707319</v>
+        <v>-7.98867320038849</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.458572282713966</v>
+        <v>-5.424899274100625</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.898272746800103</v>
+        <v>-6.862918323131616</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.23525446579036</v>
+        <v>-11.19906074837146</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-10.15124888849557</v>
+        <v>-10.08557585859989</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-5.616258188532257</v>
+        <v>-5.550783585545986</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.581890172167341</v>
+        <v>1.648282223317288</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.752610888967617</v>
+        <v>2.819346140883049</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.243402316309087</v>
+        <v>4.310108685116589</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.649086634726167</v>
+        <v>4.26183069023952</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.273810865345155</v>
+        <v>0.912701926604349</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.465137052728295</v>
+        <v>-0.8153228391624907</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1297742566168907</v>
+        <v>-0.489209543699765</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.108722946947296</v>
+        <v>1.178001011780019</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.2801352993892721</v>
+        <v>-0.2100692930998065</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.874856271665713</v>
+        <v>-1.805463393054637</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-3.468803980413178</v>
+        <v>-3.399234544630652</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.573787396508457</v>
+        <v>-3.504075248451834</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-3.357664233576642</v>
+        <v>-3.288183867527508</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.710766423357668</v>
+        <v>-1.64148404296094</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.7941128177570747</v>
+        <v>-0.7241761963284219</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.319713148498124</v>
+        <v>1.389758864160285</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.054342329578795</v>
+        <v>3.12408759124088</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.7886199684125188</v>
+        <v>0.8584743161197963</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.008359</t>
+          <t>X &gt; 0.008358</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>121</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-10.23149845493113</v>
+        <v>-10.1982241626123</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-7.287985444985281</v>
+        <v>-7.25431243637194</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-7.908013777923884</v>
+        <v>-7.872659354255397</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-11.90049561570721</v>
+        <v>-11.8643018982883</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-11.44609326958371</v>
+        <v>-11.38042023968804</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.980240131986761</v>
+        <v>-7.914765529000491</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2632871785821607</v>
+        <v>0.3296792297321076</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.263421057653765</v>
+        <v>3.330156309569198</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.124609253823941</v>
+        <v>4.191315622631443</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.68528136236084</v>
+        <v>4.238072077742494</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.8274092245175027</v>
+        <v>0.4137710641667098</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.104577240940877</v>
+        <v>-1.504322601576369</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5761758974445428</v>
+        <v>-0.9881404061374042</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.450425270462375</v>
+        <v>-2.381147205629652</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-3.935802790491408</v>
+        <v>-3.865736784201943</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.820081583845237</v>
+        <v>-5.750688705234161</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-6.780621558985892</v>
+        <v>-6.711052123203366</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-6.885604975081172</v>
+        <v>-6.815892827024548</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-6.669481812149357</v>
+        <v>-6.600001446100222</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-4.82954545454546</v>
+        <v>-4.760263074148732</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.893407020568205</v>
+        <v>-2.823470399139552</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.490023233235604</v>
+        <v>-0.419977517573443</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.6111982142382573</v>
+        <v>0.6809434759003423</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-1.94408196800542</v>
+        <v>-1.874227620298143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.009091</t>
+          <t>X &gt; 0.009089</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>107</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-12.00745473908412</v>
+        <v>-11.9741804467653</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-9.56485247595068</v>
+        <v>-9.531179467337338</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-7.300849236333114</v>
+        <v>-7.265494812664627</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.71834625322997</v>
+        <v>-11.68215253581107</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.15769011232809</v>
+        <v>-11.09201708243241</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-10.04459957339538</v>
+        <v>-9.97912497040911</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.6322805202642314</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.792868537920917</v>
+        <v>2.859603789836349</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.760310528869482</v>
+        <v>3.827016897676984</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.492186436895473</v>
+        <v>3.980027147566418</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.09364850774912981</v>
+        <v>-0.3755428399012928</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.120024834978111</v>
+        <v>-1.58021816927522</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.5592222642917548</v>
+        <v>0.07439754164644086</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.53129342524727</v>
+        <v>-1.462015360414547</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-3.12480410353691</v>
+        <v>-3.054738097247444</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.333482371672538</v>
+        <v>-5.264089493061462</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-6.402155505073793</v>
+        <v>-6.332586069291267</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.637980042664402</v>
+        <v>-4.568267894607779</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.421856879732587</v>
+        <v>-4.352376513683453</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.234813084112155</v>
+        <v>-4.165530703715426</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-1.9742751753531</v>
+        <v>-1.904338553924447</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.7535080867613004</v>
+        <v>0.8235538024234614</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>1.962862692495769</v>
+        <v>2.032607954157854</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.01776247472262327</v>
+        <v>0.08761682242990076</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.009823</t>
+          <t>X &gt; 0.00982</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>87</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-9.995960486210564</v>
+        <v>-9.962686193891734</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-9.181710713498568</v>
+        <v>-9.148037704885226</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.874284740803091</v>
+        <v>-4.838930317134604</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-10.18577920342155</v>
+        <v>-10.14958548600264</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.55104898844559</v>
+        <v>-10.48537595854992</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.36388437543881</v>
+        <v>-10.29840977245254</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.94134820864226</v>
+        <v>-1.874956157492313</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.676648869977114</v>
+        <v>4.743384121892547</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.718164934999749</v>
+        <v>4.78487130380725</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.093754811586642</v>
+        <v>5.161380915127083</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.919838216633018</v>
+        <v>1.987164695220045</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.640744313158116</v>
+        <v>1.708415291772049</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.113954244096256</v>
+        <v>5.182954374341215</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2948962836366178</v>
+        <v>0.3641743484693407</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-1.51346024275702</v>
+        <v>-1.443394236467554</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-3.217250767848277</v>
+        <v>-3.147857889237201</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-5.650195036709839</v>
+        <v>-5.580625600927313</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-4.605753165448803</v>
+        <v>-4.536041017392179</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.389630002516988</v>
+        <v>-4.320149636467853</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.202586206896555</v>
+        <v>-4.133303826499827</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-2.446936041181864</v>
+        <v>-2.376999419753211</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.9253847652444946</v>
+        <v>0.9954304809066556</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>2.349585219082947</v>
+        <v>2.419330480745032</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.124218592458156</v>
+        <v>1.194072940165434</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01056</t>
+          <t>X &gt; 0.01055</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-5.848034449229054</v>
+        <v>-5.814760156910225</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.539602291877308</v>
+        <v>-2.503408574458405</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.252698163857879</v>
+        <v>-7.187025133962202</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.065533550851093</v>
+        <v>-7.000058947864822</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.04129823362976</v>
+        <v>-1.974906182479813</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.477248570127045</v>
+        <v>3.543983822042478</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3.51876463514968</v>
+        <v>3.585471003957181</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4.19420458669908</v>
+        <v>4.26183069023952</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>0.1880642454449273</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1583561366170017</v>
+        <v>-0.09068515800306898</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.615703369533541</v>
+        <v>1.6847034997785</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.394346558499187</v>
+        <v>1.46362462333191</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.7138600428569646</v>
+        <v>-0.643794036567499</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-1.56807535555442</v>
+        <v>-1.498682476943344</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-4.600719774341023</v>
+        <v>-4.531150338558497</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.256427828117467</v>
+        <v>-3.186715680060843</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-3.040304665185651</v>
+        <v>-2.970824299136517</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-1.403985507246375</v>
+        <v>-1.334703126849647</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4979105539254931</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>2.324685115069578</v>
+        <v>2.394730830731739</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.048735643870543</v>
+        <v>4.118480905532628</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>2.523518942283239</v>
+        <v>2.593373289990517</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1723 +5824,1723 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01067</t>
+          <t>X &lt; -0.01066</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.746585173866741</v>
+        <v>-8.713310881547912</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.081760688511068</v>
+        <v>-9.048087679897726</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.5214611525972</v>
+        <v>-10.48610672892872</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.887428378833832</v>
+        <v>-6.851234661414928</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.701973526176722</v>
+        <v>-8.636300496281045</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-5.616258188532257</v>
+        <v>-5.550783585545986</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5786978454893585</v>
+        <v>0.6454330974047906</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.069489272830829</v>
+        <v>2.136195641638331</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.2956538620614</v>
+        <v>1.363279965601841</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>0.1880642454449273</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1583561366170017</v>
+        <v>-0.09068515800306898</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.282847355104145</v>
+        <v>-1.213847224859187</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.083241406418402</v>
+        <v>5.153307412707868</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.229026093720933</v>
+        <v>4.298418972332009</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.645657037253173</v>
+        <v>2.715226473035699</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.807152465798623</v>
+        <v>-1.737440317741999</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1417539405479715</v>
+        <v>-0.07227357449883698</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.403985507246375</v>
+        <v>-1.334703126849647</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>2.400640170712187</v>
+        <v>2.470576792140839</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>3.773960477388414</v>
+        <v>3.844006193050575</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>1.150184919232878</v>
+        <v>1.219930180894963</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.523518942283239</v>
+        <v>2.593373289990517</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.009939</t>
+          <t>X &lt; -0.009928</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>75</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-12.34078807241746</v>
+        <v>-12.30751378009863</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.342630253728458</v>
+        <v>-7.308957245115117</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.782330717814595</v>
+        <v>-8.746976294146108</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.162790697674417</v>
+        <v>-4.126596980255513</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.194727149365129</v>
+        <v>-7.129054119469451</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.340895869691678</v>
+        <v>-4.275421266705408</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.113762001745698</v>
+        <v>-1.047369950595751</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05898331393093059</v>
+        <v>0.007751937984501467</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.875364006988939</v>
+        <v>1.942990110529379</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.149723274104275</v>
+        <v>2.217049752691302</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.7960372960372908</v>
+        <v>-0.7283663174233581</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.587195181191106</v>
+        <v>-0.5181950509461473</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.865850102070574</v>
+        <v>3.93591610836004</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>3.127576818358627</v>
+        <v>3.196969696969703</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.66014979087636</v>
+        <v>1.729719226658887</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-3.778166958552241</v>
+        <v>-3.708454810495617</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.8953771289537684</v>
+        <v>-0.8258967629046339</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-2.041666666666664</v>
+        <v>-1.972384286269936</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.081799591002046</v>
+        <v>4.151736212430698</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>4.005844535359437</v>
+        <v>4.075890251021598</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.613953035174895</v>
+        <v>1.68369829683698</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>2.87134502923977</v>
+        <v>2.941199376947047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.009207</t>
+          <t>X &lt; -0.009197</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>85</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-11.32118022928021</v>
+        <v>-11.28790593696138</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-9.303414567453942</v>
+        <v>-9.2697415588406</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.566644443304789</v>
+        <v>-9.531290019636302</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.398084815321468</v>
+        <v>-4.361891097902564</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.116295776816109</v>
+        <v>-7.050622746920432</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.752660575574033</v>
+        <v>-5.687185972587763</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6431737664515893</v>
+        <v>-0.5767817153016424</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9217284119701503</v>
+        <v>-0.8549931600547183</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.472728829523078</v>
+        <v>1.53943519833058</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.4775771694816555</v>
+        <v>-0.4099510659412147</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.9732526858689852</v>
+        <v>1.040579164456013</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.658782394076511</v>
+        <v>-1.591111415462578</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.606803024328364</v>
+        <v>-1.537802894083406</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.407134282284339</v>
+        <v>6.476412347117062</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3.395261866776451</v>
+        <v>3.465327873065917</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.637380739927252</v>
+        <v>1.706773618538328</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.849654130692258</v>
+        <v>-0.780084694909732</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.484049311493422</v>
+        <v>-4.414337163436798</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7385143838557227</v>
+        <v>-0.6690340178065881</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.727941176470594</v>
+        <v>-1.658658796073865</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>4.78768194394322</v>
+        <v>4.857618565371872</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.8881974765359</v>
+        <v>5.958243192198061</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.633560878312153</v>
+        <v>2.703306139974238</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.734090127278975</v>
+        <v>3.803944474986253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.008475</t>
+          <t>X &lt; -0.008466</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-10.6741214057508</v>
+        <v>-11.06658968768939</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-9.009296920395123</v>
+        <v>-9.421168466237226</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.44899738448126</v>
+        <v>-6.898791475664261</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.162790697674417</v>
+        <v>-3.651349455503038</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.528060482698464</v>
+        <v>-4.977238937951299</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.340895869691678</v>
+        <v>-4.790272751853919</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.113762001745698</v>
+        <v>-1.601825396140306</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.392316647264259</v>
+        <v>-1.880036840893382</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.6491994177583607</v>
+        <v>0.1416483608232895</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.124635993011069</v>
+        <v>-1.621366325114188</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.850276725895732</v>
+        <v>-1.347306682952265</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.129370629370634</v>
+        <v>-1.626056086400261</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>0.2210788764465903</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.524781341107875</v>
+        <v>6.93069306930694</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>3.865850102070574</v>
+        <v>3.302252742023406</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.460910151691955</v>
+        <v>1.916441644164415</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.932877063603641</v>
+        <v>-0.1976735126150402</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.20240938279467</v>
+        <v>-3.272811246139192</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.05411782054118</v>
+        <v>0.9034761743890982</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.2209595959595916</v>
+        <v>-0.8898760354448569</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>5.738365247567707</v>
+        <v>5.151736212430698</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7.682612212127118</v>
+        <v>7.075890251021598</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.916983338205199</v>
+        <v>3.350364963503651</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>3.841041998936731</v>
+        <v>3.274532710280376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007743</t>
+          <t>X &lt; -0.007734</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.656422290706551</v>
+        <v>-7.149619043256529</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.991597805350878</v>
+        <v>-7.484395841606343</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.006519508375064</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.180489812718669</v>
+        <v>-2.617825050430952</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.430715349955094</v>
+        <v>-3.830808505434369</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.243550736948308</v>
+        <v>-3.64384231933699</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.246505364577565</v>
+        <v>-1.784212055858909</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.640104257883735</v>
+        <v>-1.185230518155855</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1713233115636754</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.487467851418138</v>
+        <v>-1.039466029821497</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.213108584302802</v>
+        <v>-0.7654063876595742</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6072467355653188</v>
+        <v>-0.1669628086514265</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.9231293025847123</v>
+        <v>1.341454071860873</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.011507004824686</v>
+        <v>6.383533090151133</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.467620013574994</v>
+        <v>4.848196810114423</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>2.407812806559207</v>
+        <v>2.811004784689004</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.933959314685893</v>
+        <v>1.799894665255387</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.04326161287632146</v>
+        <v>-0.0593320034780831</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>2.788138324814675</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.232142857142861</v>
+        <v>2.097791152326558</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>6.153228162430615</v>
+        <v>6.523417628359901</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>8.755844535359437</v>
+        <v>9.102438923587961</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>4.566333987555858</v>
+        <v>4.95213487500807</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>5.383249791144529</v>
+        <v>5.761258373997187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.007011</t>
+          <t>X &lt; -0.007003</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>124</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.4741214057508</v>
+        <v>-6.440847113431971</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.209296920395126</v>
+        <v>-5.175623911781784</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.44899738448126</v>
+        <v>-3.413642960812773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.16279069767441</v>
+        <v>-0.1265969802555063</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5280604826984572</v>
+        <v>-0.4623874528027798</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3408958696916713</v>
+        <v>-0.2754212667054006</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.913762001745702</v>
+        <v>-1.847369950595755</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.392316647264259</v>
+        <v>-1.325581395348827</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2491994177583621</v>
+        <v>0.3159057865658639</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.324635993011064</v>
+        <v>-1.257009889470623</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.850276725895718</v>
+        <v>-1.78295024730869</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.329370629370629</v>
+        <v>-1.261699650756697</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>6.124781341107884</v>
+        <v>6.194059405940607</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>4.665850102070571</v>
+        <v>4.735916108360037</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.860910151691954</v>
+        <v>2.93030303030303</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.423590651091416</v>
+        <v>1.996385893325559</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.705704009189688</v>
+        <v>0.2915451895043759</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.147633623734407</v>
+        <v>3.707436570428705</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.528225806451616</v>
+        <v>3.094282380396727</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.404380236163327</v>
+        <v>5.47431685759198</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>8.554231632133629</v>
+        <v>8.62427734779579</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.79674873409963</v>
+        <v>4.866493995761715</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.720807394831162</v>
+        <v>4.79066174253844</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.006279</t>
+          <t>X &lt; -0.006271</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>155</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.956172687802081</v>
+        <v>-4.922898395483251</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.291348202446407</v>
+        <v>-5.257675193833066</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.166946102429982</v>
+        <v>-4.131591678761495</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.529516994633269</v>
+        <v>1.565710712052173</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.164247209609222</v>
+        <v>1.229920239504899</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0693605405647304</v>
+        <v>0.1348351435510011</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06247995046365418</v>
+        <v>0.003912100686292774</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.623085878033493</v>
+        <v>-1.556350626118061</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3415071100660541</v>
+        <v>0.4082134788735559</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.07335394172901</v>
+        <v>-1.005727838188569</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.722071597690594</v>
+        <v>-2.654745119103566</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.719114219114218</v>
+        <v>-1.651443240500285</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.64357404957812</v>
+        <v>1.712574179823079</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.345294161620693</v>
+        <v>3.414572226453416</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.7632859995064649</v>
+        <v>0.8333520057959305</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.5647308739490668</v>
+        <v>-0.4953379953379908</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.9635061231021353</v>
+        <v>-1.270280773341106</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.358812119842568</v>
+        <v>-2.657172759213573</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.083117494702144</v>
+        <v>0.7638468268389573</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.625</v>
+        <v>0.3096669957813418</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.662444752292373</v>
+        <v>2.732381373721026</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.876812277294917</v>
+        <v>3.946857992957078</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.495000943218258</v>
+        <v>1.564855290925536</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.005547</t>
+          <t>X &lt; -0.00554</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.397878311828137</v>
+        <v>-3.367623069716117</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.838026202163078</v>
+        <v>-4.795296042929323</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.620268102713297</v>
+        <v>-4.593970829665231</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7432866503918802</v>
+        <v>0.7040041126406607</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3780168653678331</v>
+        <v>0.3682136400933871</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.670153854065227</v>
+        <v>1.64807600105415</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2076846536794079</v>
+        <v>-0.2167688576995843</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.591211674888577</v>
+        <v>-1.587876477316051</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1077629536699689</v>
+        <v>0.0929549668937355</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.218558644944764</v>
+        <v>-1.226408796574447</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.601657941365332</v>
+        <v>-2.045245329275915</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.328265656994937</v>
+        <v>-1.777546645292219</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6903259362555687</v>
+        <v>-0.1684682749898627</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.298262004091299</v>
+        <v>1.796245198290329</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.018127798481906</v>
+        <v>-0.5012423615853194</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.633012500241747</v>
+        <v>-2.092647789369103</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.006516875790304</v>
+        <v>-2.773013013778268</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.222611402996691</v>
+        <v>-3.970749892462841</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.339821573398211</v>
+        <v>-2.115514249243432</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.041666666666664</v>
+        <v>-0.8357722644120145</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.6373551465575957</v>
+        <v>1.140747201441691</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.116955646470551</v>
+        <v>1.614351789483138</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.941602520380663</v>
+        <v>-1.407876794738101</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.350877192982459</v>
+        <v>0.1646426003902661</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.004815</t>
+          <t>X &lt; -0.004808</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>218</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.401394133023523</v>
+        <v>-1.368119840704694</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.55475146584967</v>
+        <v>-3.521078457236328</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.850823868499525</v>
+        <v>-4.050006597176406</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.001592863969420932</v>
+        <v>-0.2175060711646069</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5495650880777916</v>
+        <v>0.3557943653790332</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2801086965183615</v>
+        <v>0.08821509693095209</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.405999444668083</v>
+        <v>-1.339607393518136</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.511038108451487</v>
+        <v>-3.444302856536055</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.64303802516401</v>
+        <v>-1.576331656356508</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.786736449632066</v>
+        <v>-3.719110346091625</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.055756177950521</v>
+        <v>-2.988429699363493</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.334850081425422</v>
+        <v>-3.26717910281149</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.26299426794909</v>
+        <v>-1.193994137704131</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3421329392813917</v>
+        <v>0.4114110041141146</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.686661313454543</v>
+        <v>-1.616595307165078</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.548222268399364</v>
+        <v>-1.478829389788288</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.875018404842294</v>
+        <v>-2.069367531331977</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.356148609928397</v>
+        <v>-3.544071248851786</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.22259425433603</v>
+        <v>-2.414937858795042</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.576834862385326</v>
+        <v>-1.771471044260807</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2851728860621776</v>
+        <v>-0.2152362646335249</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.015018847286044</v>
+        <v>1.085064562948205</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.838646353204304</v>
+        <v>-2.768901091542219</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.997156499812228</v>
+        <v>-1.92730215210495</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.004083</t>
+          <t>X &lt; -0.004077</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>253</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.3407880724174603</v>
+        <v>-0.3075137800986312</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.636747900787284</v>
+        <v>-2.603074892173943</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7245879356623561</v>
+        <v>-0.9038390392441471</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.711225050357079</v>
+        <v>1.520461843273893</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.314459202340913</v>
+        <v>3.145455684452116</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.926820665741388</v>
+        <v>1.763794419569109</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.0271478285173572</v>
+        <v>0.03924422263258975</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.880505623642215</v>
+        <v>-1.813770371726783</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2641864090132842</v>
+        <v>-0.1974800402057824</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.219124181987439</v>
+        <v>-2.151498078446998</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.551064127470525</v>
+        <v>-1.483737648883498</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.223858818347004</v>
+        <v>-2.156187839733072</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1949570497800295</v>
+        <v>0.2639571800249882</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.548403388351971</v>
+        <v>1.617681453184694</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1020705745115222</v>
+        <v>0.1721365808009878</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.4839717380718298</v>
+        <v>-0.4145788594607538</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.01061092394619578</v>
+        <v>-0.1547952090366422</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.070657077129326</v>
+        <v>-2.228139849865705</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.854533914197511</v>
+        <v>-2.01224846894138</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.08646245059288304</v>
+        <v>-0.2505995093670563</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.9513648083933575</v>
+        <v>1.02130142982201</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.665923586742835</v>
+        <v>1.735969302404996</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.802384250727599</v>
+        <v>-2.732638989065514</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.692554839007933</v>
+        <v>-1.622700491300655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003352</t>
+          <t>X &lt; -0.003345</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.78732895292061</v>
+        <v>-1.603229558573027</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.751435285174999</v>
+        <v>-2.564965604571746</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.08306678511218</v>
+        <v>-3.062545782129391</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9350011004328351</v>
+        <v>0.6132149319701909</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.408848034651697</v>
+        <v>3.09874107384298</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.018725581412426</v>
+        <v>1.718309140818107</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3314276168876589</v>
+        <v>-0.4435963656900981</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.240897088904653</v>
+        <v>-1.350738628053236</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5684661973835858</v>
+        <v>-0.6803206285284702</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.342301608153015</v>
+        <v>-1.45323630456496</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.383399754286884</v>
+        <v>-1.493642071208072</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.293408484260219</v>
+        <v>-2.40132229226613</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2633255702552475</v>
+        <v>-0.3798302710719312</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.092604684956456</v>
+        <v>0.9714178965066367</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1972413805792641</v>
+        <v>-0.3156562186839906</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.548553570705522</v>
+        <v>-0.6646655231560885</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.4533987360240417</v>
+        <v>0.1448135662815275</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.9174074648813573</v>
+        <v>-1.217888772759778</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.017739998152074</v>
+        <v>-1.31646280064048</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.8306962025316409</v>
+        <v>-1.129616990672453</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.524837565685587</v>
+        <v>0.4041021430300731</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.39824959865058</v>
+        <v>1.274628421368597</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.175076500690075</v>
+        <v>-1.290013585392245</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.9345621437560112</v>
+        <v>-1.050388425366307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.00262</t>
+          <t>X &lt; -0.002614</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>414</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3087367903661828</v>
+        <v>-0.2754624980473537</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.605450766548969</v>
+        <v>-1.571777757935628</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.677913047131867</v>
+        <v>-2.769412191581999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.427570748108714</v>
+        <v>1.32532609666756</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.508084095614791</v>
+        <v>2.431843316427987</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.177176419464956</v>
+        <v>3.099578733294592</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.005328266805946669</v>
+        <v>0.06106378434400028</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.765810623167873</v>
+        <v>-0.6990753712524409</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.00140299188018389</v>
+        <v>0.06530337692731791</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5342745472279304</v>
+        <v>-0.4666484436874896</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4629762861524682</v>
+        <v>0.5303027647394956</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.020936894430868</v>
+        <v>-0.9532659158169352</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.228065862985602</v>
+        <v>1.297065993230561</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.72960061821631</v>
+        <v>1.798878683049033</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.070669379179009</v>
+        <v>1.140735385468474</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7018740071136449</v>
+        <v>0.7712668857247209</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.437927568654146</v>
+        <v>1.36024131501231</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.4313463767606862</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.6248457279875836</v>
+        <v>-0.6973827066797256</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.5283816425120733</v>
+        <v>0.453318524975046</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.434456595832955</v>
+        <v>1.504393217261608</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.083139221349775</v>
+        <v>2.153184937011936</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.6670931317932585</v>
+        <v>0.7368383934553435</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1334858886346311</v>
+        <v>-0.06363154092735357</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001888</t>
+          <t>X &lt; -0.001883</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.1028570115153897</v>
+        <v>0.01334183487462326</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.030879654208071</v>
+        <v>-1.925713038341499</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.476024411508284</v>
+        <v>-2.472466490224534</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.855227320343594</v>
+        <v>1.805666834361247</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.608913794969048</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.397842869047061</v>
+        <v>2.369855025629704</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.084436196452501</v>
+        <v>1.166915763689957</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.08516083021321208</v>
+        <v>-0.004152823920264836</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.027577796136747</v>
+        <v>0.9301915008515849</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2537423853673175</v>
+        <v>0.1572758248150947</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3727992484182465</v>
+        <v>-0.2829502473087047</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.552794052794049</v>
+        <v>-1.097413936470986</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.106498512502597</v>
+        <v>1.529423996672897</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.786042602369129</v>
+        <v>1.844059405940605</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.487471723692202</v>
+        <v>1.721630394074332</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6410903318721282</v>
+        <v>0.8874458874458853</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.518152197615237</v>
+        <v>1.467814464754134</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.03087453977968124</v>
+        <v>-0.06559766763848529</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.5462594534770417</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.552797833935017</v>
+        <v>0.515710951825298</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.634146161399158</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.460718181568822</v>
+        <v>2.508806172309612</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.832966272238679</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.215508687482846</v>
+        <v>1.27632161904603</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001156</t>
+          <t>X &lt; -0.001151</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>761</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5143602696418768</v>
+        <v>0.6075188996399277</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.2134854020705106</v>
+        <v>-0.1194147614549834</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1211205709577996</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.552805632600815</v>
+        <v>2.566213477260831</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.284521430800879</v>
+        <v>4.191207318439041</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.161070054292587</v>
+        <v>3.148662502928097</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.174573515947607</v>
+        <v>3.240965567097554</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.24071087567151</v>
+        <v>2.307446127586942</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.068596534403191</v>
+        <v>3.135302903210693</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.687945920488282</v>
+        <v>2.755572024028723</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.520627599137043</v>
+        <v>1.587954077724071</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5862257009046061</v>
+        <v>0.6538966795185388</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.9519048624961</v>
+        <v>2.020904992741059</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.779040843073801</v>
+        <v>2.848318907906524</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>3.120443277923584</v>
+        <v>3.10760680298651</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.878232986337629</v>
+        <v>1.867131339608399</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.350469545585085</v>
+        <v>2.257460598436964</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.062831727387305</v>
+        <v>0.973065504052208</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.935985113709393</v>
+        <v>1.924759405074376</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.597404730617612</v>
+        <v>1.586670831840294</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.105452679044099</v>
+        <v>2.175389300472752</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.555121802113703</v>
+        <v>2.625167517775864</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.304272789883619</v>
+        <v>2.374018051545704</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.359737495293203</v>
+        <v>2.42959184300048</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0004238</t>
+          <t>X &lt; -0.0004197</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2208061304810869</v>
+        <v>0.2958044702784406</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.02378967401831744</v>
+        <v>0.05152540948518691</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2173670760808406</v>
+        <v>0.2424656364722964</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.407472221636546</v>
+        <v>1.429964105717332</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.855439063992378</v>
+        <v>2.813630646744727</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.135985363309231</v>
+        <v>2.14849177677285</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.272457399886207</v>
+        <v>1.338849451036154</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7219172602606676</v>
+        <v>0.7886525121760997</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.307404313497265</v>
+        <v>1.374110682304767</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9868780595727955</v>
+        <v>1.054504163113236</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.35189915805713</v>
+        <v>1.419225636644157</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3475106036302833</v>
+        <v>0.415181582244216</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.126917843892002</v>
+        <v>1.195917974136961</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.177546526964626</v>
+        <v>1.246824591797349</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.7551422980778355</v>
+        <v>0.7700049569547787</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3520172297318851</v>
+        <v>0.367111733838847</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.0001590192961984371</v>
+        <v>-0.03879089724561169</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6501015634568859</v>
+        <v>-0.6876025892807576</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.2018072488845704</v>
+        <v>0.2170554452018436</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.8429836512261559</v>
+        <v>0.8576217633368373</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.298874977014769</v>
+        <v>1.368811598443422</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.767879049437546</v>
+        <v>1.837924765099707</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.18971061093248</v>
+        <v>1.204134264139434</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.659223817118551</v>
+        <v>1.673261138981552</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003081</t>
+          <t>X &lt; 0.0003117</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5884531893046159</v>
+        <v>0.5755072306906825</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3190612885600927</v>
+        <v>0.34904587944105</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7370094414573032</v>
+        <v>0.7670902020175845</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.242245580601292</v>
+        <v>1.247657069190346</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.157678202186247</v>
+        <v>1.124995326395847</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.8995996450456119</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6212807332970272</v>
+        <v>0.5891488207352964</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5384229850572382</v>
+        <v>0.5062581266315291</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7081989902252275</v>
+        <v>0.7005343091961009</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4901566534190422</v>
+        <v>0.50770604389119</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4046420080649256</v>
+        <v>0.4221779578195139</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.06489552381722064</v>
+        <v>0.08280654847374791</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2893774661718496</v>
+        <v>-0.2707958775102099</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2286433164263642</v>
+        <v>-0.2353548736660684</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.07998286438320434</v>
+        <v>0.07278522726508641</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2671412401709929</v>
+        <v>-0.2484731785116878</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5043746307174644</v>
+        <v>-0.5107600202388412</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.012629024561676</v>
+        <v>-1.018386317344941</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.2567264714351865</v>
+        <v>-0.2634413738967751</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.2840909090909065</v>
+        <v>-0.2907283262413856</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4842381448470121</v>
+        <v>-0.4652303685461661</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.3029033205582365</v>
+        <v>-0.2584432251892821</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.4315210102991429</v>
+        <v>-0.3871993589663347</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.3787622208674932</v>
+        <v>-0.3343866722239071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.00104</t>
+          <t>X &lt; 0.001043</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7085716192398834</v>
+        <v>0.7013071914506313</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2444344228884603</v>
+        <v>0.2749353723345465</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2060978002891858</v>
+        <v>0.2372335777922245</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5959845077027239</v>
+        <v>0.6059654964322831</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7001800851013087</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6845151915938246</v>
+        <v>0.6648772407572778</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4189482786281289</v>
+        <v>0.3994385600425474</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4610864940969961</v>
+        <v>0.4414088959132982</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4278082434876183</v>
+        <v>0.4297645837268718</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3645188312222984</v>
+        <v>0.3884310671810951</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6233484143960837</v>
+        <v>0.6469562947473761</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.291288053264104</v>
+        <v>0.3152637000286447</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.00984987180986252</v>
+        <v>0.01483910512465769</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.02183041478878778</v>
+        <v>-0.01925398224189223</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2029287537559696</v>
+        <v>0.2052763777203097</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.01147194944476837</v>
+        <v>0.03629105425512336</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1377770231613482</v>
+        <v>-0.1350512324229456</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.3328895972329136</v>
+        <v>-0.3299448891178614</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.3929618286765333</v>
+        <v>0.3950770198669105</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.1675571803524534</v>
+        <v>0.1699378111083476</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.03680521529901171</v>
+        <v>0.06181489358468895</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.2459045503631856</v>
+        <v>0.2707927997472339</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.01795553673837702</v>
+        <v>0.04290339619956995</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.09210800610029679</v>
+        <v>0.1170523953197531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001772</t>
+          <t>X &lt; 0.001775</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.7314729998436107</v>
+        <v>0.7585942273501516</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4852816035643031</v>
+        <v>0.4777466785081259</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3592601382619165</v>
+        <v>0.3515562006127979</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6100479442576798</v>
+        <v>0.5819984075851536</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6498106657609171</v>
+        <v>0.6505101354530609</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6118186662102474</v>
+        <v>0.612690621406486</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3844860711344609</v>
+        <v>0.3852988147067933</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5817457432019069</v>
+        <v>0.5820463163376601</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.4830585134471121</v>
+        <v>0.5037951810355992</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4803412239535305</v>
+        <v>0.5214214830783988</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5999336527859001</v>
+        <v>0.6408676160888547</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2711905772235568</v>
+        <v>0.3125119820393891</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.04656616213346609</v>
+        <v>-0.004763609694101945</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1769730448570428</v>
+        <v>-0.1557654013474163</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.04288980666933639</v>
+        <v>-0.02202290320672518</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.04453035374854863</v>
+        <v>-0.002656296485191945</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.05239702560303527</v>
+        <v>-0.03138409264920483</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.241812901650249</v>
+        <v>-0.2205558276825741</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.206051777113224</v>
+        <v>0.2267348160427431</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.04172522839071746</v>
+        <v>0.06270343302831094</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.1501048362642976</v>
+        <v>-0.1431040824096002</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>0.04780036338114968</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.155385924037482</v>
+        <v>-0.1484056722532898</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.06967970988556971</v>
+        <v>-0.0837391548407993</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002504</t>
+          <t>X &lt; 0.002506</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2990</v>
+        <v>2993</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6476871048875097</v>
+        <v>0.6420214124644446</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4968553908785722</v>
+        <v>0.4913305883842725</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4724929681468168</v>
+        <v>0.4667557102835715</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8422009828580315</v>
+        <v>0.8358490150917746</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6956412483268366</v>
+        <v>0.6852189301759353</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5022609734651624</v>
+        <v>0.4921211343587757</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5144858330311095</v>
+        <v>0.5041935889917326</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5217120098500274</v>
+        <v>0.511357040591264</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4299391711738991</v>
+        <v>0.4389417386297865</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5558038603711424</v>
+        <v>0.5843487518880224</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5497232741042737</v>
+        <v>0.5781423576213456</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2901025283486121</v>
+        <v>0.318840169303293</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1326003061935879</v>
+        <v>0.1620226542632324</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.102303382040887</v>
+        <v>-0.09237844810805029</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.05937696226409628</v>
+        <v>0.06924944169337977</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.0796303888485852</v>
+        <v>-0.04989036749623921</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.09374429012051877</v>
+        <v>-0.08377416002556259</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.01188983000466237</v>
+        <v>-0.001983829841854856</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.2909956165372165</v>
+        <v>0.3005630302218236</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1973354493818888</v>
+        <v>0.1871085398895573</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.07857461547973799</v>
+        <v>-0.06855751253592501</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.06768487640527354</v>
+        <v>-0.05766567552264235</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.1740777237685975</v>
+        <v>-0.1639970939445732</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.06288016585499889</v>
+        <v>-0.05289796128661095</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003236</t>
+          <t>X &lt; 0.003237</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3091</v>
+        <v>3094</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5702515846029002</v>
+        <v>0.5659608506014351</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.477676382917835</v>
+        <v>0.4734605726383947</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5033835678996965</v>
+        <v>0.4989534402155087</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8697165440378427</v>
+        <v>0.8647241383558679</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9091578044876201</v>
+        <v>0.9009565986441572</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6961411673453597</v>
+        <v>0.6882326413035997</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.4893307817594419</v>
+        <v>0.4815875783617685</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5516085863805884</v>
+        <v>0.5437459300454393</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3997633881096476</v>
+        <v>0.4106900750397884</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5605074165925501</v>
+        <v>0.5903331056984626</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4991752405775145</v>
+        <v>0.5289054227944021</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3678883193555862</v>
+        <v>0.3978556183377293</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2945252489164218</v>
+        <v>0.3059536223807413</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1569207409142663</v>
+        <v>0.1493285003653426</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.2273736656599894</v>
+        <v>0.2196040516224471</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.1122981439450257</v>
+        <v>0.1239824885423104</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.1266227216696052</v>
+        <v>0.1383213771965259</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.1378537132823752</v>
+        <v>0.149563905219118</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.2764053158496793</v>
+        <v>0.2879401211065584</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.2242243051066595</v>
+        <v>0.2165548142249989</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.0280905188880638</v>
+        <v>-0.01616821120508405</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.02002032076730131</v>
+        <v>-0.008089077143779377</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.113946921703068</v>
+        <v>-0.1019775243800325</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.05585921019522999</v>
+        <v>0.06768073872252245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.003968</t>
+          <t>X &lt; 0.003969</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3142</v>
+        <v>3145</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2474472217001846</v>
+        <v>0.2441813136053099</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2773212384153823</v>
+        <v>0.2739811435104826</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3737874256453182</v>
+        <v>0.3701749911467758</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7222995207491323</v>
+        <v>0.7181706454163219</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7233644698031227</v>
+        <v>0.7166131797082826</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.4535292174163317</v>
+        <v>0.4471348864106943</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2056296332352829</v>
+        <v>0.1994654924422221</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1671128297563413</v>
+        <v>0.1609649800864332</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.1000554735605235</v>
+        <v>0.09399318365263554</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2456874058475336</v>
+        <v>0.2578459863608629</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2848326937046579</v>
+        <v>0.2968976614365531</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2462638883958661</v>
+        <v>0.2584271321276148</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.0923774412567937</v>
+        <v>0.1049290243022156</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.01684483317136909</v>
+        <v>0.0106732296565113</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.1071965612639616</v>
+        <v>0.1008384045858577</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.02813398930518929</v>
+        <v>-0.01538224888478368</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.110806292358788</v>
+        <v>0.1234566645093125</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.00695628171716578</v>
+        <v>0.005830903790098318</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1645932037438342</v>
+        <v>0.1771729946903662</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.08445945945945965</v>
+        <v>0.07821378719253858</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1407759256911163</v>
+        <v>-0.1278063542783272</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.1977178056074891</v>
+        <v>-0.1846753670273387</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.2857181918905383</v>
+        <v>-0.2726483867824214</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.1199556285153776</v>
+        <v>-0.1070253183364756</v>
       </c>
     </row>
     <row r="27">
@@ -7550,79 +7550,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2272518776449601</v>
+        <v>0.2244895449221431</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1274498794799896</v>
+        <v>0.1247814514860721</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2661806292601483</v>
+        <v>0.2632129343837377</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5694804675864447</v>
+        <v>0.5660707264527503</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5344395173015428</v>
+        <v>0.5288734710424023</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3018049743220672</v>
+        <v>0.2965425172471328</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.01557563526665007</v>
+        <v>-0.020511736979266</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.08859440766464388</v>
+        <v>-0.09346643127511101</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1543049627172337</v>
+        <v>-0.1590942134341304</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.02075614319879548</v>
+        <v>-0.007619454959836958</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.0839955745737555</v>
+        <v>0.09697470578698386</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1361271790201073</v>
+        <v>0.1491229954741513</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.06187938622294098</v>
+        <v>-0.04844119195573882</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1393790598946296</v>
+        <v>-0.1443636228453897</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.02760022697987807</v>
+        <v>-0.03278498710161415</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1219792246790874</v>
+        <v>-0.1083945276180671</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.04468479610102349</v>
+        <v>0.058145993544791</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.07293020721954235</v>
+        <v>-0.0593320034780831</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.067818186813696</v>
+        <v>0.08123788663051812</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.02255255726388583</v>
+        <v>0.01737858848196083</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.1441182000239962</v>
+        <v>-0.1303954490113099</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.2013117734917884</v>
+        <v>-0.187515205234277</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.284529434736136</v>
+        <v>-0.270714082920442</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.1219548032560525</v>
+        <v>-0.108272435624869</v>
       </c>
     </row>
     <row r="28">
@@ -7632,161 +7632,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.397439359209109</v>
+        <v>0.3948891773875047</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2332208210426998</v>
+        <v>0.2308475828253052</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.3534717513212087</v>
+        <v>0.3508453252538075</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4287499012758786</v>
+        <v>0.4259777961860536</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3589067810445812</v>
+        <v>0.3543923127740243</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2238245504504306</v>
+        <v>0.2194877120048702</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.06802652584953961</v>
+        <v>-0.07206130862044802</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1125639424729243</v>
+        <v>-0.116566267222872</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1461005203987185</v>
+        <v>-0.150060859511953</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1468994438459461</v>
+        <v>-0.133006182334384</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.04019321213141325</v>
+        <v>-0.02646075410721949</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.03894620231253754</v>
+        <v>0.05267438324639784</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.01523603541580343</v>
+        <v>-0.001188248225055588</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1563332099757133</v>
+        <v>-0.1604242056858709</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.08459895336454792</v>
+        <v>-0.08882871069347686</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1214938136116359</v>
+        <v>-0.1256375637563707</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.04172194251358974</v>
+        <v>0.03736391870469902</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.04475096351195162</v>
+        <v>-0.04901208603742191</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.09687093306173011</v>
+        <v>0.09244740969782583</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.007754342431766759</v>
+        <v>-0.01203732220550791</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.09815697120707512</v>
+        <v>-0.102369768356418</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.1555459053606114</v>
+        <v>-0.1596956138265142</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2347481963267128</v>
+        <v>-0.2387823233180484</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1058806436380806</v>
+        <v>-0.1100826743350112</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006164</t>
+          <t>X &lt; 0.006163</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3251</v>
+        <v>3255</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.3435993397426387</v>
+        <v>0.3414537715237813</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1777446443970447</v>
+        <v>0.1757802396223695</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3443379869647814</v>
+        <v>0.3420822300269251</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3509707702154969</v>
+        <v>0.348662641002889</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2477119247655892</v>
+        <v>0.2439981261767485</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1768519883254527</v>
+        <v>0.1732339900183035</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1195777348341664</v>
+        <v>-0.1228820264135493</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1969706582869222</v>
+        <v>-0.2001991323518979</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2298204903580228</v>
+        <v>-0.2330082544252576</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2379591170539399</v>
+        <v>-0.2234725577692771</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.09905123569964758</v>
+        <v>-0.08475618547827679</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.02333324046470864</v>
+        <v>-0.009035841816100287</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.02639403669897433</v>
+        <v>-0.01181424441220003</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.04559584380472614</v>
+        <v>-0.04912589268114687</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.01145051142636078</v>
+        <v>-0.0150642837968249</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.01162743652529485</v>
+        <v>-0.0152072363227731</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.1487931303484302</v>
+        <v>0.1450063715597736</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.1235831182055023</v>
+        <v>0.1198187252296137</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.1431159095392687</v>
+        <v>0.1393384109194997</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.07200460829493238</v>
+        <v>0.06832349730375853</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.008044213005732104</v>
+        <v>0.004406562338623132</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.08022985750868372</v>
+        <v>-0.08376587424704951</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1560346647020978</v>
+        <v>-0.1594630463243547</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.001663905482971018</v>
+        <v>-0.001964985572158184</v>
       </c>
     </row>
     <row r="30">
@@ -7796,489 +7796,489 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3272</v>
+        <v>3276</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3331645687482876</v>
+        <v>0.3312571922078149</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.257329256343418</v>
+        <v>0.2554952874902909</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3225700517277303</v>
+        <v>0.3205803401581022</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4765286581444812</v>
+        <v>0.4743134901542021</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.371635565933758</v>
+        <v>0.3682136400933871</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2720563954345039</v>
+        <v>0.2687633673668586</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.0882145564902288</v>
+        <v>-0.09111235642807713</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1364602432484503</v>
+        <v>-0.1393158225746021</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.16881640695253</v>
+        <v>-0.1716322073551098</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.18184840932269</v>
+        <v>-0.1670737386648966</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.04205754781353477</v>
+        <v>-0.02747579475395412</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.03140890777919481</v>
+        <v>0.04599733737838818</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.02119145704627812</v>
+        <v>0.03607559218633583</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.06022779965994829</v>
+        <v>-0.0632747389163768</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-4.444227565869596e-05</v>
+        <v>-0.003201091031129977</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.0645686882773262</v>
+        <v>0.06136271361607015</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.1621321025567539</v>
+        <v>0.1587983209831876</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.1669215100261496</v>
+        <v>0.1635744399614154</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.1877273365126158</v>
+        <v>0.184364336353724</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.1182844932844915</v>
+        <v>0.1150140877138028</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.0785431657701281</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.006372935624064269</v>
+        <v>-0.009527686745336439</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.07990580992134966</v>
+        <v>-0.08295819792448356</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.0457541571941249</v>
+        <v>0.04254247829014446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.007627</t>
+          <t>X &lt; 0.007626</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3282</v>
+        <v>3286</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3210359792370951</v>
+        <v>0.3192496217554535</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2141363221116919</v>
+        <v>0.2124619666578909</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2748063708185597</v>
+        <v>0.2729874082132397</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4564156034464517</v>
+        <v>0.4543409925130177</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.4113334566954734</v>
+        <v>0.4080725956233664</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2216988559827655</v>
+        <v>0.218675009407221</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.07919559786456887</v>
+        <v>-0.08189448118328357</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1281370900910801</v>
+        <v>-0.1307919376087554</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1906064074843457</v>
+        <v>-0.1931851225250369</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2059466726227086</v>
+        <v>-0.1909898834081716</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06575472286082373</v>
+        <v>-0.05099148442210577</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.006634227945710336</v>
+        <v>0.0214062030497999</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.006974511082795232</v>
+        <v>0.008099447435732543</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.05845073665639688</v>
+        <v>-0.06128039988464451</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.0004519337847881388</v>
+        <v>-0.003385864325849752</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.06577337357645519</v>
+        <v>0.0627863332781331</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.1322284368680471</v>
+        <v>0.1291523676650641</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.1366748905961686</v>
+        <v>0.1335865017765485</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.127642848736123</v>
+        <v>0.124574218559971</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.05896226415094219</v>
+        <v>0.05598450805630506</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.02091679039321548</v>
+        <v>0.01795694821665705</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.06723707243592969</v>
+        <v>-0.07009515043824877</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1397275415333965</v>
+        <v>-0.1424856601653488</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.04516929129649583</v>
+        <v>-0.04804793488091263</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.008359</t>
+          <t>X &lt; 0.008358</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3298</v>
+        <v>3302</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3620231725624521</v>
+        <v>0.3603562560024471</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.254035408619643</v>
+        <v>0.2524832203277541</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2773437848978872</v>
+        <v>0.2757008080011971</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4244869628622112</v>
+        <v>0.4226351787327474</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.408007068568125</v>
+        <v>0.405082426715289</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2805219281967055</v>
+        <v>0.2777574015681665</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.0226334561814312</v>
+        <v>-0.02506735867291354</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1330350293952733</v>
+        <v>-0.1353492578752196</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1648102440773798</v>
+        <v>-0.167085769525805</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1838147369724155</v>
+        <v>-0.1686237657903717</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.04296775579605594</v>
+        <v>-0.02797136981926229</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.02772906851456725</v>
+        <v>0.04273741534653652</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.008755257007749151</v>
+        <v>0.02407548045482599</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.07738109926990688</v>
+        <v>0.07473573444300996</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.1319523095093373</v>
+        <v>0.1292111853760431</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.2007770603428938</v>
+        <v>0.1979767463151134</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.2360448992979443</v>
+        <v>0.2331945968613738</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.239992847743153</v>
+        <v>0.2371316465781419</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.2320827559993077</v>
+        <v>0.2292388081063592</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.1646729254997013</v>
+        <v>0.1619169841474815</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.09391713114140288</v>
+        <v>0.09122184026730906</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>0.003251025840000921</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.03462734271739265</v>
+        <v>-0.0371615275650754</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.05913560938935092</v>
+        <v>0.05648304341181642</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.009091</t>
+          <t>X &lt; 0.009089</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3312</v>
+        <v>3316</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3750687562168125</v>
+        <v>0.3735327547525671</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2961336226591769</v>
+        <v>0.2946787552844441</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2232715230817703</v>
+        <v>0.2218486459018507</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3667800018152221</v>
+        <v>0.3651571426830174</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3488163941784137</v>
+        <v>0.3462508195427461</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3127538749763872</v>
+        <v>0.3102372991511828</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.00763222902352112</v>
+        <v>0.005451177855626099</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1034678345200604</v>
+        <v>-0.1055273575223623</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1349256574070026</v>
+        <v>-0.1369470662869787</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1571074301728146</v>
+        <v>-0.1417200126307279</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.01569025973030591</v>
+        <v>-0.0004983242317706527</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.02345728880025177</v>
+        <v>0.03869109165388807</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.03026870912770363</v>
+        <v>-0.01468733396879429</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.03712330378096595</v>
+        <v>0.03482909926591304</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.08867455253729872</v>
+        <v>0.08629204820966407</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.1597053324148519</v>
+        <v>0.1572585056339548</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.1942464063227831</v>
+        <v>0.1917515267892966</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.1374448557937455</v>
+        <v>0.1350129799920339</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.130449421141698</v>
+        <v>0.1280327763907607</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.1243968636911887</v>
+        <v>0.1219932237702253</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.05163367848319211</v>
+        <v>0.04929571830596302</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.03640048576307464</v>
+        <v>-0.03863657236598783</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.07555295134286411</v>
+        <v>-0.07773271512161273</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.01271294177472981</v>
+        <v>-0.01497271794640653</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.009823</t>
+          <t>X &lt; 0.00982</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2454016941001669</v>
+        <v>0.2442377332485961</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2244538249835273</v>
+        <v>0.2233040215118436</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1131857351131274</v>
+        <v>0.1121240931044127</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2512904479103071</v>
+        <v>0.2500418755251772</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2609577208228728</v>
+        <v>0.2589240226070544</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2561190556814594</v>
+        <v>0.2540957279278686</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.03762647242568562</v>
+        <v>0.03583911591184119</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1342521311352272</v>
+        <v>-0.1358439251817671</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1353837910853741</v>
+        <v>-0.1369739508259542</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.144958766471909</v>
+        <v>-0.1465621282765923</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.06253382604519686</v>
+        <v>-0.06422824073957401</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.05520794994479417</v>
+        <v>-0.05692067823578384</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1452767446570533</v>
+        <v>-0.146917289766975</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.01980274028051809</v>
+        <v>-0.0216010841968739</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.02747835708404267</v>
+        <v>0.02560220701474236</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.0716885948057282</v>
+        <v>0.06977671451356571</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.1351423036047237</v>
+        <v>0.1331492795056377</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.1079924183201371</v>
+        <v>0.1060275354050333</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.1023253982662879</v>
+        <v>0.100372817061448</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.09742206235011963</v>
+        <v>0.09547998518715417</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.05181458350579504</v>
+        <v>0.04990931815097355</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.03614706632022546</v>
+        <v>-0.03795037210601748</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.07341570169879219</v>
+        <v>-0.0751669513899671</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.04142007680265891</v>
+        <v>-0.04321309307694321</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01056</t>
+          <t>X &lt; 0.01055</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3350</v>
+        <v>3354</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1058963825682042</v>
+        <v>0.1050812253302524</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1128857605064226</v>
+        <v>0.1120538133367077</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.0351735933213746</v>
+        <v>-0.03586518303499275</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.0389897177558538</v>
+        <v>0.03819258702367989</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1356379441344231</v>
+        <v>0.1341141777931227</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1317882158190145</v>
+        <v>0.1302726834725263</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.02768196278305624</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.08393875065107181</v>
+        <v>-0.08522531226277863</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.08482732815545546</v>
+        <v>-0.08611261652110613</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.09847665888502632</v>
+        <v>-0.09976523388866809</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01501059446545128</v>
+        <v>-0.01639248075093036</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.009204061851285417</v>
+        <v>-0.01060042318687948</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.04529296954773798</v>
+        <v>-0.04667449621607744</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.04069484936831458</v>
+        <v>-0.04208803757902047</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.002795621570427897</v>
+        <v>0.001333890102529267</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.02017161684978674</v>
+        <v>0.01870279234942984</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.08255074410841701</v>
+        <v>0.08100356663707231</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.05496772559554586</v>
+        <v>0.05344995140913511</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.05047483329163782</v>
+        <v>0.0489667877552904</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.01677101967799643</v>
+        <v>0.01530679969392423</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.001707715887306449</v>
+        <v>-0.003163996088808574</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.059787922874456</v>
+        <v>-0.06117768699985504</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09538746019961764</v>
+        <v>-0.09672892621319562</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.06397835384480999</v>
+        <v>-0.06535995519369209</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_1.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_1.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01029</t>
+          <t>X ≈ -0.01016</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-53.27373987298473</v>
+        <v>-24.80057889249156</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.60931146728728</v>
+        <v>17.52703209658186</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.18413415735737</v>
+        <v>16.28537332205946</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>27.04593095798985</v>
+        <v>29.90203428189803</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.14762051504819</v>
+        <v>15.43151776896676</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.3362152999258</v>
+        <v>1.381788227638445</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.011776612957917</v>
+        <v>0.5905647911750265</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.290862235945262</v>
+        <v>0.2871487861698512</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.340471638469481</v>
+        <v>14.63688732764218</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.573636386286879</v>
+        <v>-0.3780939643887677</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>25.45149344533183</v>
+        <v>28.35475330606967</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.032945724951823</v>
+        <v>-0.382523921694542</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.457345441790416</v>
+        <v>12.74542419225003</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.238624463994299</v>
+        <v>12.50118011344703</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-10.03741773518378</v>
+        <v>11.82478118662116</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-9.447362230807329</v>
+        <v>-1.863570538054873</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-9.583718140364006</v>
+        <v>-16.22381425805716</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-26.3278964154084</v>
+        <v>-16.36109502651196</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-9.478423869941132</v>
+        <v>-1.88730868938913</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-9.294594678771894</v>
+        <v>-1.673514057583034</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>23.46398824715811</v>
+        <v>12.03195207371941</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.738477197103684</v>
+        <v>11.96041828204303</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>7.014925285582265</v>
+        <v>-2.073918548615659</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.941199376943253</v>
+        <v>-2.236673155776892</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.009562</t>
+          <t>X ≈ -0.009435</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.614152334797048</v>
+        <v>-3.516808956501471</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-23.81766503089773</v>
+        <v>-28.6002886717562</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.31614436783351</v>
+        <v>-17.43309159250808</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.08963769983189</v>
+        <v>-18.0279959222504</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.42498594087364</v>
+        <v>-18.30682454301113</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.1876863135857</v>
+        <v>-18.15652315632368</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.937722490879224</v>
+        <v>-6.516379856913659</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.290696610858113</v>
+        <v>-31.70351423365504</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.251835831379324</v>
+        <v>-31.58580836704221</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-17.98182592265827</v>
+        <v>-32.38769039508396</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.752997423338464</v>
+        <v>-32.12622527120678</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-8.032808392756309</v>
+        <v>-32.41108937108525</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.154695372014821</v>
+        <v>-33.53196426221658</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.5917645598459629</v>
+        <v>-21.32696954431679</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.06418001229010173</v>
+        <v>-22.01337494144015</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-9.447255429908601</v>
+        <v>-21.45979256203228</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-19.56269621645986</v>
+        <v>-21.56967984717161</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.69090809772095</v>
+        <v>-21.70856697226679</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.5066871779037072</v>
+        <v>-9.019549182487694</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.6934896919858176</v>
+        <v>-8.807876355743147</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>10.14252641912412</v>
+        <v>3.111290441045355</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>20.06380695492734</v>
+        <v>3.037121811134291</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>10.34725022273058</v>
+        <v>3.281634561598757</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>10.27453271028038</v>
+        <v>3.120469701365558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.008831</t>
+          <t>X ≈ -0.00871</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.49705419702738</v>
+        <v>-17.7049136871939</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-10.85207640665586</v>
+        <v>-17.95469856651322</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.499819281805387</v>
+        <v>2.088080978717848</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1249821480785016</v>
+        <v>-5.601499054721884</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.395337664446686</v>
+        <v>1.225902466365085</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.03500103446524605</v>
+        <v>-5.722709646572987</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.481284754442228</v>
+        <v>-13.62294656138025</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-7.779393285894834</v>
+        <v>-6.821399423052668</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.733884263942286</v>
+        <v>-6.696363827594233</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.560521161599205</v>
+        <v>-7.4908830329084</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-14.91217077581012</v>
+        <v>-14.33732055676533</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.927862537583103</v>
+        <v>-0.3822370695066297</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.17049902001424</v>
+        <v>12.74532684118933</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.951336366904243</v>
+        <v>12.50100578780248</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2.598476644089168</v>
+        <v>4.700933291688791</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>3.229102247931252</v>
+        <v>5.262422859709048</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.08340846961179</v>
+        <v>5.160458716463403</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.966657905736206</v>
+        <v>5.029499481712222</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>9.862406945941807</v>
+        <v>12.37716570926396</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>3.402189506773112</v>
+        <v>5.460864794234112</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>6.812130474597545</v>
+        <v>4.89538785286625</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>13.40105946147386</v>
+        <v>11.96035217863471</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.014896271111184</v>
+        <v>5.066809400975636</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>-2.236673155781766</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.0081</t>
+          <t>X ≈ -0.007985</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>23.13062035592474</v>
+        <v>24.85971626924687</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.516865530866419</v>
+        <v>10.43048512893871</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.089204602458807</v>
+        <v>9.186145702638264</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.381531657679865</v>
+        <v>8.599339337391442</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.049362685340377</v>
+        <v>8.328248055105405</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.236820947903787</v>
+        <v>8.486577676990201</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.185645183825358</v>
+        <v>0.5908947448966728</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.194073620888574</v>
+        <v>7.396379493962954</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.236376839636236</v>
+        <v>7.525635019611578</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.467974618396774</v>
+        <v>6.735375265761292</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.742046991023635</v>
+        <v>-0.1066108162743689</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>11.13219626535626</v>
+        <v>6.735024439943061</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>10.01559169195429</v>
+        <v>12.74497850570925</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.126135559457701</v>
+        <v>5.379186792967083</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>16.81807413922332</v>
+        <v>18.94809222390845</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>9.740324721482295</v>
+        <v>12.3880812782815</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>17.28811372073581</v>
+        <v>19.41616138559917</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>24.86949434253793</v>
+        <v>26.41951468316576</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>17.40942705259014</v>
+        <v>19.50917569644945</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>25.28676188304037</v>
+        <v>26.86371165076947</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>17.05920029693791</v>
+        <v>19.16822553238734</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>24.67622889026085</v>
+        <v>26.23744409531604</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>17.26819079199815</v>
+        <v>19.34822869432501</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>24.88991732566499</v>
+        <v>26.33475541564842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.007369</t>
+          <t>X ≈ -0.007259</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.9001431350142965</v>
+        <v>-10.61034271795942</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>18.6345717903762</v>
+        <v>10.42992650596806</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>17.21033547816869</v>
+        <v>2.087699826780103</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>25.54490393411255</v>
+        <v>8.59891405683085</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>34.26041641464266</v>
+        <v>15.43008421710657</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>34.4566873622324</v>
+        <v>15.59055248069071</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.489606960870525</v>
+        <v>0.5908727174400923</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.7674174552998</v>
+        <v>-6.821133039785224</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.727209590055345</v>
+        <v>-6.696128223753441</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.497681637233974</v>
+        <v>-7.490603748062327</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.2836740310337</v>
+        <v>-7.221610705410697</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.56528022930167</v>
+        <v>-7.499457444221122</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.625562954937799</v>
+        <v>-8.613203066380969</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.218283616213846</v>
+        <v>5.379046625401806</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.563205924434854</v>
+        <v>4.700556378188004</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.15761389362725</v>
+        <v>5.262138768872092</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.0252938989059</v>
+        <v>-1.967680219613719</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.92194934832245</v>
+        <v>5.029190001809326</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>13.21855084413209</v>
+        <v>12.37681024064455</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>13.40928434167449</v>
+        <v>12.59491240530855</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-5.298204588562371</v>
+        <v>-2.241152093331323</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.709809225548099</v>
+        <v>-9.455479678490953</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.98546559226223</v>
+        <v>-9.214648164724458</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.180012744267145</v>
+        <v>-16.52238744149605</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.006637</t>
+          <t>X ≈ -0.006533</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.191380299384825</v>
+        <v>2.69055209963981</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.551689155109635</v>
+        <v>-6.866036338989602</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.983105329242328</v>
+        <v>-5.0100058852342</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.340988782798306</v>
+        <v>9.92939362090641</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.009648469045089</v>
+        <v>9.65863252663182</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.779821719315564</v>
+        <v>6.709414108193478</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.432646747269551</v>
+        <v>2.811500681288379</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.475339610083559</v>
+        <v>-3.710800605448142</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7769870334659643</v>
+        <v>-0.4740824649269726</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.007614294128977406</v>
+        <v>-1.266652285203648</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.147274065038566</v>
+        <v>-7.221213203556744</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.212060532147447</v>
+        <v>-4.385437640818466</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.314871968796218</v>
+        <v>6.960109694165475</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.772310975667096</v>
+        <v>-8.86359895822735</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-14.8668675462229</v>
+        <v>-15.77930087778585</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-14.2780868104683</v>
+        <v>-15.22392626755413</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-14.41601725745862</v>
+        <v>-12.2136741602103</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-14.52497698454999</v>
+        <v>-15.46925640201775</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-11.09207680553675</v>
+        <v>-15.26000949326566</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-10.90872555952802</v>
+        <v>-11.92904674452656</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-8.228007192401513</v>
+        <v>-9.377474042725964</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-14.75399574853002</v>
+        <v>-9.455402157643356</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-17.70879201545643</v>
+        <v>-12.33865996277184</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-11.33837051552607</v>
+        <v>-6.254530298636574</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005905</t>
+          <t>X ≈ -0.005808</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.582010156386062</v>
+        <v>9.356211988840002</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.108584369804767</v>
+        <v>5.436112272451432</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-7.219815825188533</v>
+        <v>0.5106101084496188</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.250341846438261</v>
+        <v>-3.760901282693354</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.585466517791502</v>
+        <v>-4.035748713205919</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.33692179610236</v>
+        <v>7.169182896940747</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.484551027795284</v>
+        <v>-0.9883966622139226</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.761590730079341</v>
+        <v>-1.29177646240457</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.721243517010137</v>
+        <v>-1.165307760771015</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.491320847687568</v>
+        <v>-1.958025873621779</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.471281341015526</v>
+        <v>2.001812947824455</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.497444480910751</v>
+        <v>-1.963497122243503</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-11.00305389261842</v>
+        <v>-10.45842491550412</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.53365416711901</v>
+        <v>-7.016933401027053</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-8.192138821788006</v>
+        <v>-7.698970581717802</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-11.29712475283864</v>
+        <v>-10.83587456056801</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-11.43420882160976</v>
+        <v>-10.9427846219803</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-11.54232353789195</v>
+        <v>-11.07867387129194</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-18.72876811312469</v>
+        <v>-14.56621257708992</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-7.446997713266221</v>
+        <v>-6.958030611634754</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-7.989148070194076</v>
+        <v>-7.527172142261705</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-11.76882214816762</v>
+        <v>-11.30601764368936</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-11.49794816812793</v>
+        <v>-11.0658345234774</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-7.873615437866931</v>
+        <v>-7.527678446785437</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.005174</t>
+          <t>X ≈ -0.005082</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8.697323848736438</v>
+        <v>12.08684054738458</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.835204033641212</v>
+        <v>3.333380459013881</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.394422939704533</v>
+        <v>-0.7510537709293601</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.879313957181736</v>
+        <v>1.497950713405004</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3017107832991357</v>
+        <v>6.90557491443559</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.797286707886343</v>
+        <v>-1.460688311952474</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.012367843511221</v>
+        <v>-2.251480496309291</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-12.8207769720651</v>
+        <v>-8.241313446039044</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.01819093529475</v>
+        <v>-5.273092761025985</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-16.32390334590229</v>
+        <v>-11.75661652500192</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.753537642258159</v>
+        <v>-2.951916171488968</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.80210407594575</v>
+        <v>-6.075044515964606</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.387164772057062</v>
+        <v>-4.341038027672361</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.609920510982569</v>
+        <v>-4.590186336763537</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-7.268124360123892</v>
+        <v>-5.271471350105337</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.638066720583467</v>
+        <v>3.83725684565438</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.50494891614413</v>
+        <v>3.73482584828794</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.372650187312907</v>
+        <v>0.7515785078936403</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.93196726558763</v>
+        <v>-1.887015991214511</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-6.521802800540698</v>
+        <v>-4.527017512021686</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-7.063945384372275</v>
+        <v>-5.0954389815711</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.589848557883997</v>
+        <v>0.5386250462427</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-9.646604398768964</v>
+        <v>-7.786362013826974</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-12.5032450674974</v>
+        <v>-10.80810172720872</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004443</t>
+          <t>X ≈ -0.004357</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6.3178226807022</v>
+        <v>5.87488826587429</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.148792436371671</v>
+        <v>2.949455136379427</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>18.76119607344672</v>
+        <v>17.81413473863365</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.37457288588784</v>
+        <v>11.85750159880935</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>20.56995488166679</v>
+        <v>19.64730515300697</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12.23415868000137</v>
+        <v>9.059279168457884</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.623781203535735</v>
+        <v>8.271863608700613</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8.350237905138002</v>
+        <v>5.282525987112983</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.3935372760143</v>
+        <v>8.100870375366078</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.626982488910969</v>
+        <v>7.311440231798869</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.902142436070129</v>
+        <v>7.584578162943657</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.779584676249229</v>
+        <v>4.618840053517395</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.357265189195793</v>
+        <v>8.895507531320639</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>9.139424635147492</v>
+        <v>11.34473182890297</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>11.33612572720541</v>
+        <v>13.36354657621131</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.231024172641185</v>
+        <v>5.8397496605903</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>11.80286084689992</v>
+        <v>13.8283326499324</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>5.996733910072777</v>
+        <v>8.304917634515036</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.5069888692847186</v>
+        <v>3.124504672680771</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>9.257052776454316</v>
+        <v>11.43764844053666</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>8.714919223341859</v>
+        <v>10.87420483639431</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.786470775508938</v>
+        <v>8.10144315423819</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.505931955333438</v>
+        <v>0.2420647441144439</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>2.782631863524877</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.003711</t>
+          <t>X ≈ -0.003631</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-6.720342234674071</v>
+        <v>-8.029042980166594</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.396445863177746</v>
+        <v>-0.7515539390389563</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.59237359737546</v>
+        <v>-12.5344001175834</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.985082285264426</v>
+        <v>-5.600751581793851</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.895313430579094</v>
+        <v>1.652964095576252</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.528407508730254</v>
+        <v>1.810247247756088</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.347860932924625</v>
+        <v>-1.99312694109458</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4852091952570419</v>
+        <v>3.733521104533438</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.584932338352871</v>
+        <v>-2.170463645648866</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.313157394706124</v>
+        <v>3.070617363915808</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.526645741809709</v>
+        <v>-1.184184718474867</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.361730918478912</v>
+        <v>-4.478620816384151</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.925551886430576</v>
+        <v>-4.081914018794919</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.589247086758348</v>
+        <v>-2.820764864434899</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.245867103978036</v>
+        <v>-3.501467288530677</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.653424693789859</v>
+        <v>-1.431213186245607</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.331313479236528</v>
+        <v>-0.02368377852649672</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.7873247069397</v>
+        <v>1.356255799151988</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.443268829925493</v>
+        <v>0.05800618139188884</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-4.613754332654707</v>
+        <v>-5.78074048951332</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.033890185904021</v>
+        <v>-3.322162868789846</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.5488536267960953</v>
+        <v>-1.884142121723784</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.411510742503779</v>
+        <v>2.902965532589405</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.212032710280376</v>
+        <v>-0.2886212077281911</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.002979</t>
+          <t>X ≈ -0.002906</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.063788195360615</v>
+        <v>1.00528462771986</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.684921872712891</v>
+        <v>0.7586727110861631</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.792194977046371</v>
+        <v>-2.528090113462397</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.644954548154573</v>
+        <v>3.975924605730242</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2354462475254735</v>
+        <v>0.6584875192060551</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.600680726711417</v>
+        <v>7.918897119672287</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.706609058825052</v>
+        <v>2.619759773137183</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.430790563737062</v>
+        <v>1.302588516839307</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.498355022133737</v>
+        <v>3.460813159819828</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.756405712802263</v>
+        <v>1.654075936562194</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.137591905526428</v>
+        <v>5.989984542827365</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.780994679568707</v>
+        <v>3.684160213292756</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.772098873988575</v>
+        <v>7.657260550549758</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.497796553474963</v>
+        <v>5.377709601003126</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.899663776266458</v>
+        <v>6.73455142719633</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>5.466168059406101</v>
+        <v>6.278970129688886</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.334147724194509</v>
+        <v>5.159131571146766</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>2.143838257872737</v>
+        <v>1.973334756964988</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.330571677025027</v>
+        <v>2.188072823048216</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5.63721777770931</v>
+        <v>5.460211325436774</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>5.095056048187367</v>
+        <v>4.894966533869237</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>5.020911614946705</v>
+        <v>4.821443638990807</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>7.358268247146242</v>
+        <v>8.126919476852656</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.161130648424468</v>
+        <v>3.885775823811699</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002249</t>
+          <t>X ≈ -0.00218</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8359471266808498</v>
+        <v>7.01053986535188</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.919353267942249</v>
+        <v>-1.653722327922573</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.607449159117301</v>
+        <v>-1.695201955718147</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.162635126647331</v>
+        <v>3.732409104817741</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.942608955817583</v>
+        <v>8.277107022046422</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2723194634804713</v>
+        <v>0.0006614130978022104</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.307748633362621</v>
+        <v>4.032412925312357</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.974848857279767</v>
+        <v>3.128521612519449</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.388882297997277</v>
+        <v>3.256246779447061</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.93443737467765</v>
+        <v>3.068876367710828</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.600006356915465</v>
+        <v>-1.486089975446049</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.503750148686379</v>
+        <v>0.6529520231359882</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.186145682571244</v>
+        <v>2.55990760652417</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.966370923729656</v>
+        <v>2.313159342301915</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3.374291297754475</v>
+        <v>3.446830238251657</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.216692212530525</v>
+        <v>0.9861355120102786</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.771564547692861</v>
+        <v>1.487358553450214</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.9795705674340169</v>
+        <v>1.35586152672289</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.950310617131962</v>
+        <v>3.990422568439932</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.6934763961023762</v>
+        <v>0.5746158251270685</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.218147689072012</v>
+        <v>1.218718699781874</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.52149093519072</v>
+        <v>0.5384251378220384</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.176103804785484</v>
+        <v>3.205701648941996</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.102118917177073</v>
+        <v>1.832590913483919</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001517</t>
+          <t>X ≈ -0.001454</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.247707539605948</v>
+        <v>-1.872373669894131</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.861903376045539</v>
+        <v>3.427881242216586</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.355433976711687</v>
+        <v>8.83329134809199</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.677147339584081</v>
+        <v>3.804120290668862</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.820132955660227</v>
+        <v>3.530001624162765</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.2970014779971</v>
+        <v>4.799313572427884</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8.956218454565381</v>
+        <v>9.002713919169551</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>8.681599634490382</v>
+        <v>8.145691727693091</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9.218996048051082</v>
+        <v>8.83254212247035</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>9.927677987459234</v>
+        <v>9.151112930636387</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.754536314410878</v>
+        <v>6.646071667394217</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.491385741093943</v>
+        <v>3.589518738579471</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.382485184490626</v>
+        <v>1.918136618387393</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.63031138172488</v>
+        <v>4.454346212355709</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6.947843153234935</v>
+        <v>6.000141708960975</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>4.582510349985611</v>
+        <v>3.221676470883885</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.450318296909259</v>
+        <v>4.233828525624993</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.851561722010132</v>
+        <v>3.543507782875487</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.845018221320238</v>
+        <v>4.87643682318545</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>4.550410814278479</v>
+        <v>4.861317925228676</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.513725797825138</v>
+        <v>4.296176930824799</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.944586920579198</v>
+        <v>5.8974868865429</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.715162235196772</v>
+        <v>5.026442972089946</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>5.62106736374573</v>
+        <v>7.659575846614111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007853</t>
+          <t>X ≈ -0.0007284</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4038087371073118</v>
+        <v>-0.6004864199066446</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4329159680047425</v>
+        <v>-0.2584982531681845</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4648878756398958</v>
+        <v>0.2505221329262355</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.124015990522672</v>
+        <v>-1.223367637388989</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2918735923357545</v>
+        <v>-0.3233312705852001</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1041881139069218</v>
+        <v>-0.1660554668555747</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.916950516569379</v>
+        <v>-3.019808469553119</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.60803735027212</v>
+        <v>-2.737368492867255</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.568925632443253</v>
+        <v>-2.610064115555979</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.752810335114837</v>
+        <v>-2.524538569479816</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.033461226765326</v>
+        <v>0.9874599165477136</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1208743595571633</v>
+        <v>-0.1738993509267885</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6552071893236899</v>
+        <v>-0.2347774501945992</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.341905200280912</v>
+        <v>-1.95716141198875</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-4.465111159375788</v>
+        <v>-4.114689025467257</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.992794426426535</v>
+        <v>-2.374304507039774</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.182113974352298</v>
+        <v>-4.84079145385514</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.407250772952885</v>
+        <v>-3.794653280778114</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.604974239268863</v>
+        <v>-2.989962936616287</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.7759092597768529</v>
+        <v>-0.4112883013763664</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.4367568329141633</v>
+        <v>0.2027956771285417</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.07516663584008398</v>
+        <v>0.1280991130632714</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.414030643140769</v>
+        <v>-1.106714172196433</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.01958493677845041</v>
+        <v>0.3837833108301751</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -5.4e-05</t>
+          <t>X ≈ -3.1e-06</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1231</v>
+        <v>1247</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8274133627952835</v>
+        <v>0.7968070727101733</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6153948259389708</v>
+        <v>0.7542634930819645</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.236542134289117</v>
+        <v>1.453272808101737</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.089973769241759</v>
+        <v>1.418799947903054</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.375163980737149</v>
+        <v>-0.049242795419012</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2695143893213228</v>
+        <v>-0.05009661802390752</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.07516481524886842</v>
+        <v>0.03326797571779849</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2568173509666352</v>
+        <v>0.4115119738311961</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1023588696620692</v>
+        <v>0.4237220647473663</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.02112422992021123</v>
+        <v>0.2689696642072477</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4667985394412284</v>
+        <v>-0.2565663704380086</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2138034986338226</v>
+        <v>-0.05278349291000239</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.580076191880963</v>
+        <v>-1.406247508795943</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.559287611397387</v>
+        <v>-1.415474822333195</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5499976054665296</v>
+        <v>-0.3719960049247035</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.7985188968347856</v>
+        <v>-0.5631227365462621</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.9331882179697857</v>
+        <v>-0.7470273804000627</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.313956466679109</v>
+        <v>-1.360805704462372</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.6927686736097201</v>
+        <v>-0.7467888539760636</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.317703851447448</v>
+        <v>-1.333043047516192</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.103944150112703</v>
+        <v>-2.142391980058889</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.131772404313125</v>
+        <v>-2.170436691355384</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.809360461264951</v>
+        <v>-1.799588577804109</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.130016436754552</v>
+        <v>-2.041920034002167</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0006774</t>
+          <t>X ≈ 0.0007224</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.556832209410373</v>
+        <v>1.654585414006071</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2492689716880676</v>
+        <v>0.2562391494762792</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.456887908182019</v>
+        <v>-3.594814080993608</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.878502759036834</v>
+        <v>-4.612905332424425</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.432636918138101</v>
+        <v>-2.577813427706339</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.7605419193292065</v>
+        <v>-1.262865014637519</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9304060443817903</v>
+        <v>-1.187352403827248</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.01943537473019319</v>
+        <v>-0.6237785437887027</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.463676485657814</v>
+        <v>-1.94340378589829</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.449521849367656</v>
+        <v>-1.000928397489218</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.196307740164549</v>
+        <v>1.75114287691018</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.924152618155702</v>
+        <v>1.770959214006844</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.001441804430875</v>
+        <v>2.110198796677508</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.485536366578955</v>
+        <v>0.9931642419970999</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.12472066029094</v>
+        <v>0.6013996525641829</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.016796468697393</v>
+        <v>1.453189659473132</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.48216289514248</v>
+        <v>1.932202728029999</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>4.464499323977975</v>
+        <v>4.594262618347187</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.973282511575128</v>
+        <v>5.100874095293847</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>3.377155413434409</v>
+        <v>3.277106024370596</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>3.730158355493309</v>
+        <v>3.87944285477807</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.951941642994051</v>
+        <v>4.387370711831529</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.033963822894592</v>
+        <v>3.464824439092411</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.259607337146065</v>
+        <v>3.011140255298571</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001409</t>
+          <t>X ≈ 0.001448</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.587880147831001</v>
+        <v>2.313032302554753</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.461243580888201</v>
+        <v>2.042623397644725</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.030790974683313</v>
+        <v>2.372590507033614</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2195073470650399</v>
+        <v>1.787727406442684</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1813981269104374</v>
+        <v>-0.08235878587591827</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1835410746399404</v>
+        <v>0.89253282819395</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1607604874319435</v>
+        <v>0.6152231293501842</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.637552537039248</v>
+        <v>2.982931450101034</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.577490665597672</v>
+        <v>2.044080506927159</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.464814596383427</v>
+        <v>3.141189907639387</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5255983831055744</v>
+        <v>0.7451126108996888</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2592884503241919</v>
+        <v>0.7622154522574647</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2946620805891982</v>
+        <v>-0.8876602787084664</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.172329420371668</v>
+        <v>-1.673739450101756</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.383832401746666</v>
+        <v>-2.891397589035662</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.5787373623598313</v>
+        <v>-0.1871016818930897</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.503743627665557</v>
+        <v>2.169540955884329</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.401641874461149</v>
+        <v>0.9674815229169624</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.267485597724608</v>
+        <v>-2.579578897217601</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.526423727128901</v>
+        <v>-1.290449499913116</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.176552732574777</v>
+        <v>-2.934250364445099</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-3.253543411456192</v>
+        <v>-3.009412886400384</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.978152924996301</v>
+        <v>-3.303412809724172</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-3.058800623052996</v>
+        <v>-2.390282986809325</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.002141</t>
+          <t>X ≈ 0.002174</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.604242374456952</v>
+        <v>-1.743490362250633</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7679717557311179</v>
+        <v>2.327696826941526</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.714065575759101</v>
+        <v>1.07272185319556</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.756970367856695</v>
+        <v>3.35897528934381</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.349467250905704</v>
+        <v>-0.5081262141752063</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.856660433333403</v>
+        <v>-3.236324116497023</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.804942525113489</v>
+        <v>1.733880497270313</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.8680360444483171</v>
+        <v>-2.175644734941876</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.8257122352974662</v>
+        <v>-3.490281579417719</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.796139213474824</v>
+        <v>-0.6817282858334934</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6463678087227862</v>
+        <v>-1.850701827941883</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4367217857627068</v>
+        <v>-0.6896944188930121</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.399736078082661</v>
+        <v>3.237607615980146</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.139241094833721</v>
+        <v>0.823548769856238</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.844618852555016</v>
+        <v>1.587307162442407</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.9682853089055854</v>
+        <v>-1.462725577191428</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.105561745065899</v>
+        <v>-1.567467283347575</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.251651238164591</v>
+        <v>4.80022703559338</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.745104982394345</v>
+        <v>2.552442548543866</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.619450348868504</v>
+        <v>3.491208677296264</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.381289167013911</v>
+        <v>1.483701949720398</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.113279046953316</v>
+        <v>-2.214648978031995</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.473689546123353</v>
+        <v>-0.5217391304347743</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.548505313020101</v>
+        <v>0.7653972375945983</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002871</t>
+          <t>X ≈ 0.002899</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.677827814444747</v>
+        <v>-3.061194012513269</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.05137190077198284</v>
+        <v>-1.401342233205149</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.452815435623705</v>
+        <v>0.2061965919492508</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.722443017853486</v>
+        <v>1.531536356579473</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.272494585731394</v>
+        <v>6.522472790327676</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.477415146245754</v>
+        <v>4.773701441840295</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1819835063380566</v>
+        <v>-1.751198685881207</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.50193105441366</v>
+        <v>0.8123186095746746</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.419243745265895</v>
+        <v>-0.968280380122799</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7703239015954964</v>
+        <v>0.1456074964875356</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9177424617475225</v>
+        <v>-0.5392443834950527</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.726509534938934</v>
+        <v>3.019578602621543</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.562501694656234</v>
+        <v>4.783004531171699</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.306647331399816</v>
+        <v>7.435049293402876</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>4.677473597442336</v>
+        <v>4.834279883854059</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.270277027702761</v>
+        <v>5.396293439559074</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>6.714098871119816</v>
+        <v>6.251720541665883</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.633654574456813</v>
+        <v>4.200221408840534</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.09297845947335759</v>
+        <v>-0.3854016175993991</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.090321984357125</v>
+        <v>0.7892018781766623</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.537874826292082</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.462028864882981</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.736503577365035</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.640869343943741</v>
+        <v>4.082008162901175</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.003603</t>
+          <t>X ≈ 0.003625</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-19.19280283547973</v>
+        <v>-18.74995539784228</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-11.75531410111053</v>
+        <v>-8.854000610848288</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.367846328907014</v>
+        <v>-6.049764557934779</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.047389393606402</v>
+        <v>-6.664021814003192</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-10.3299585776383</v>
+        <v>-8.963581267190087</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-14.05882378433895</v>
+        <v>-10.81972144564934</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-16.81096213445729</v>
+        <v>-13.62132072516146</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-22.92579738535929</v>
+        <v>-24.06154627408981</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-19.00560209369466</v>
+        <v>-17.84631488506091</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-19.76738078481679</v>
+        <v>-18.64892289745837</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-13.65669733650583</v>
+        <v>-14.32431424522696</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-8.113672247024127</v>
+        <v>-8.511408214627473</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-12.06079154573744</v>
+        <v>-13.66774644107517</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.400823004501611</v>
+        <v>-9.880739309916933</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-7.105209889122754</v>
+        <v>-8.529418431194138</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-8.463493250020747</v>
+        <v>-10.00048963558109</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.7823847351604911</v>
+        <v>-1.970469004874694</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-8.702251090819402</v>
+        <v>-10.2372541524677</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-6.538033947527623</v>
+        <v>-7.994816851720429</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-8.325325462740587</v>
+        <v>-9.812605629868003</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-6.907087316981062</v>
+        <v>-10.40627143093622</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-10.90450190584115</v>
+        <v>-12.52225027942212</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-10.6300271933591</v>
+        <v>-12.2786157941438</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-10.70585944658237</v>
+        <v>-12.4407547884332</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.004334</t>
+          <t>X ≈ 0.00435</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.273900334720537</v>
+        <v>-2.263792062179185</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-11.05245464407479</v>
+        <v>-12.68063906882326</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-7.765583737123372</v>
+        <v>-8.846876227419138</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-10.86649293863883</v>
+        <v>-12.01188204721808</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-13.56022658845698</v>
+        <v>-12.28146647166626</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-10.98830642076707</v>
+        <v>-12.10362486088929</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-16.45213185535764</v>
+        <v>-17.95430838033629</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-19.08528527690143</v>
+        <v>-18.25026825026829</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-19.03779569402634</v>
+        <v>-20.66208752549363</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-19.81971497150344</v>
+        <v>-21.46709959418966</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-14.82976897479969</v>
+        <v>-16.11536820976636</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-8.019682844033973</v>
+        <v>-8.757771320381387</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-11.47977968479965</v>
+        <v>-12.3944904757883</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-11.73828226898986</v>
+        <v>-12.6837919805489</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-10.02703173127208</v>
+        <v>-10.81407733303568</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-7.058713974802274</v>
+        <v>-7.696389068538856</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-4.82777427571002</v>
+        <v>-5.252915667144485</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.926565647226298</v>
+        <v>-5.379779483934186</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-7.090654433133892</v>
+        <v>-7.727721790837471</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-4.54381285769837</v>
+        <v>-4.956751100101329</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.324454263759776</v>
+        <v>-0.4115042933119355</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.400300225168877</v>
+        <v>-0.4866668152672204</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.1258255126868235</v>
+        <v>-0.2430323299887789</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2016577659100989</v>
+        <v>-0.4051713242783066</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005066</t>
+          <t>X ≈ 0.005076</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>15.17427893698821</v>
+        <v>15.50508343900251</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>9.424330664643428</v>
+        <v>10.19858213971915</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.995509889516633</v>
+        <v>8.939742100845841</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-11.46818226301732</v>
+        <v>-9.460097271071191</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-14.51155847256207</v>
+        <v>-12.26595264296034</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-6.321412636226121</v>
+        <v>-4.464230160830041</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.514551417777255</v>
+        <v>-2.670971823528447</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.131168495053537</v>
+        <v>-0.4248653502384485</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.5811113282419811</v>
+        <v>2.249944539162406</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-10.92096628283876</v>
+        <v>-8.712901190015273</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.6101135450602</v>
+        <v>-8.457249923338011</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.190475485414836</v>
+        <v>-6.199388709037841</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.049523928537539</v>
+        <v>5.411832198131911</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.600033421063664</v>
+        <v>0.09298190127893946</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-4.938071803602611</v>
+        <v>-3.144638632306538</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.652385987828957</v>
+        <v>-0.02996051199559702</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.729284080445694</v>
+        <v>-0.1443011747666034</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.8229626829471712</v>
+        <v>2.282464972190603</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.095873108232269</v>
+        <v>2.486466948290413</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.548960862846592</v>
+        <v>-2.399418659005548</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.31389837459286</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.238052413183759</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.512527125665812</v>
+        <v>2.321070234113677</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.2660078302601647</v>
+        <v>-0.4051713242783066</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.005798</t>
+          <t>X ≈ 0.005802</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-5.261958012458521</v>
+        <v>-6.868977430737807</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-5.578983331518394</v>
+        <v>-7.079971112911075</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6065232814846979</v>
+        <v>-1.751790116609442</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.735873559755426</v>
+        <v>-8.944523990376204</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-11.26950713213086</v>
+        <v>-12.49697253226777</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.657268947560524</v>
+        <v>-5.728069533467604</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.396673252752713</v>
+        <v>-6.45914409756088</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-8.875686377215573</v>
+        <v>-10.04677380168343</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.831240615419247</v>
+        <v>-9.913026033077621</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-9.601197711574066</v>
+        <v>-10.70325866937522</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.132253549465652</v>
+        <v>-7.159952111900395</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.416920112676998</v>
+        <v>-7.448171784215226</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.114810181060051</v>
+        <v>-1.956913367785674</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.56180134142451</v>
+        <v>11.05720626498648</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>7.677851592231058</v>
+        <v>7.058385216434736</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>11.4980449657869</v>
+        <v>10.93341472545045</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>11.36412782880943</v>
+        <v>10.81482843137251</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>17.71090002821401</v>
+        <v>17.31821883601486</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>5.023565602686766</v>
+        <v>4.26307322002333</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>8.436217864267689</v>
+        <v>7.800208684690261</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>11.11947814791457</v>
+        <v>10.61413673232909</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.817825734892558</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>8.092300447374612</v>
+        <v>7.449275362318893</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>11.24227464576425</v>
+        <v>10.62046970136272</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.006529</t>
+          <t>X ≈ 0.006527</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.297971693633457</v>
+        <v>-1.228508098202475</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.58042918273294</v>
+        <v>12.6676067870627</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.058773298250721</v>
+        <v>-2.705717222932464</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>19.88091941187633</v>
+        <v>20.19394407032281</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>19.56112126301363</v>
+        <v>19.94957501404417</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>15.02635388122356</v>
+        <v>15.42369046353986</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.838924628006531</v>
+        <v>5.317553034988606</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.302437155746674</v>
+        <v>9.734437102858067</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.347922418582471</v>
+        <v>9.870163283497412</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.579004823467216</v>
+        <v>9.081909059233254</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.833074061023318</v>
+        <v>9.315157719061844</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.546328495733007</v>
+        <v>9.022981222680201</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.431162590719204</v>
+        <v>7.915886376184467</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.263083451202327</v>
+        <v>-1.731767848148749</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.840678013121881</v>
+        <v>2.316023439509166</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>11.95887445887446</v>
+        <v>12.33327090953496</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.301147798087534</v>
+        <v>2.749759719323954</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.958211856171104</v>
+        <v>7.350769171585355</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.17410323709543</v>
+        <v>7.561283510851098</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.783765731670059</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>11.58030764100213</v>
+        <v>12.04270816090052</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>11.50446167959303</v>
+        <v>11.96754563894523</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>11.77893639207508</v>
+        <v>12.21118012422361</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.00726</t>
+          <t>X ≈ 0.007253</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.67022431672212</v>
+        <v>-3.590245775729805</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.91784874531106</v>
+        <v>-13.66472404000496</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-15.35586779434205</v>
+        <v>-14.91941814189654</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.160870384094096</v>
+        <v>-5.702296531180949</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.37799640932012</v>
+        <v>13.77452628110062</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-16.20295749858947</v>
+        <v>-15.61139725575833</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.943816888417111</v>
+        <v>3.431615970103941</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.67539784476061</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.205755004659963</v>
+        <v>-6.573946992191715</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.973774480148371</v>
+        <v>-7.360474677887495</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.724195840728243</v>
+        <v>-7.135858710902369</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-8.012737645272964</v>
+        <v>-7.431488284420929</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.126107311032357</v>
+        <v>-8.536856592347853</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>1.108216100623878</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.06408389164010941</v>
+        <v>0.4212333666552368</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.5303030303031733</v>
+        <v>0.9680523292245411</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-9.078370692707601</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-9.708454810495624</v>
+        <v>-9.211254797869202</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-19.4925634295713</v>
+        <v>-18.92967847676367</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-19.30571761960313</v>
+        <v>-18.70543532753778</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-19.84826378756944</v>
+        <v>-19.38586326767091</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-19.9241097489784</v>
+        <v>-19.46102578962634</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-19.64963503649635</v>
+        <v>-19.21739130434782</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-29.72546728971962</v>
+        <v>-29.37953029863728</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.007992</t>
+          <t>X ≈ 0.007978</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.721055951429037</v>
+        <v>12.14770428234238</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.410037765576234</v>
+        <v>11.74790662201598</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7732482247419838</v>
+        <v>4.29402552825448</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.168174552125357</v>
+        <v>-2.266727425489925</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2933152266208197</v>
+        <v>3.57995601396955</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.3268298618287</v>
+        <v>15.90442736677351</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.62021736230516</v>
+        <v>14.68614558682889</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.043655759805887</v>
+        <v>1.90590574736909</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.208481220160458</v>
+        <v>8.156076236611916</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.441505197248333</v>
+        <v>7.321552035237048</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.685866573788964</v>
+        <v>7.786150580619406</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.395237864092508</v>
+        <v>7.586514038459356</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.28395510348485</v>
+        <v>0.2339622229830027</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>28.0940594059406</v>
+        <v>24.8781330529678</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>27.43591610836013</v>
+        <v>24.24094269985992</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>28.03030303030295</v>
+        <v>24.93713880501033</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>21.64638589332547</v>
+        <v>18.67318645083935</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>21.54154518950429</v>
+        <v>18.54030234567774</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>21.75743657042862</v>
+        <v>18.75476457282352</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>21.94428238039673</v>
+        <v>18.87942296032848</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>15.15173621243078</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>15.0758902510216</v>
+        <v>15.53897421037389</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>21.60036496350365</v>
+        <v>22.03260869565218</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>21.52453271028046</v>
+        <v>21.87046970136272</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.008724</t>
+          <t>X ≈ 0.008703</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.375156009128453</v>
+        <v>0.2131297105727583</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.14745701457784</v>
+        <v>7.619164429249444</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-12.51313120784195</v>
+        <v>-8.872893934396721</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-13.25644345436432</v>
+        <v>-9.502251048208549</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-13.58464437014167</v>
+        <v>-9.770418205307323</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.862838773193957</v>
+        <v>13.28321219982676</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.174375213772457</v>
+        <v>12.56943100060221</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.926521996098757</v>
+        <v>12.29407448919652</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.975598734783375</v>
+        <v>12.42939438188125</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.2102726155168</v>
+        <v>11.64073386966253</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.446384473829333</v>
+        <v>11.87601396926348</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.924263619878019</v>
+        <v>3.962272426412973</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.108966149913876</v>
+        <v>-4.760215347413919</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-9.405940594059345</v>
+        <v>-5.043698712389087</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-10.0640838916399</v>
+        <v>-5.7258530942742</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-9.469696969696912</v>
+        <v>-5.164549075454538</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-12.96073717948723</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-23.99416909620986</v>
+        <v>-20.78592897695647</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-23.77827771528553</v>
+        <v>-20.5714667498107</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-9.305717619603321</v>
+        <v>-4.972264920136332</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-9.848263787569245</v>
+        <v>-5.539709421517067</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-9.924109748978303</v>
+        <v>-13.30717963578015</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-9.649635036496349</v>
+        <v>-13.06354515050167</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-16.86832443257682</v>
+        <v>-13.22568414479113</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.009455</t>
+          <t>X ≈ 0.009429</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-20.72418044676525</v>
+        <v>-15.39534329992832</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-11.19784613400403</v>
+        <v>-6.193806193806211</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-17.82105036822025</v>
+        <v>-16.83465720994456</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-18.34881920247769</v>
+        <v>-17.47813193173543</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-13.73090597132126</v>
+        <v>-13.03507535322001</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.590236081520182</v>
+        <v>-8.159527028607265</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.128555975330123</v>
+        <v>0.5745509377581612</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.334840654608072</v>
+        <v>-4.397911701282531</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3396497689896307</v>
+        <v>-4.259768287001833</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.158861741322454</v>
+        <v>-5.04560527762461</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-10.65332061767911</v>
+        <v>-14.24124321403941</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-15.88577372483085</v>
+        <v>-19.23643988712544</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-22.14782468057582</v>
+        <v>-25.02908870480474</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.405940594059473</v>
+        <v>-16.03270970140008</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-10.06408389163996</v>
+        <v>-16.71486408328517</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-14.469696969697</v>
+        <v>-20.9154648263702</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-11.49553571428564</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.708454810495667</v>
+        <v>-11.62841981944732</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.492563429571341</v>
+        <v>-11.41395759230155</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.305717619603314</v>
+        <v>-11.19937114724257</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.1517362124306629</v>
+        <v>-7.004910886718562</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.07589025102152647</v>
+        <v>-2.318168646768989</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>-2.074534161490682</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-4.725467289719667</v>
+        <v>-11.76048267958967</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.01018</t>
+          <t>X ≈ 0.01016</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-25.86306933565419</v>
+        <v>-22.64375032361616</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-20.64229057844841</v>
+        <v>-17.39652357629884</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-27.63586518303496</v>
+        <v>-24.51888309641766</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-39.45993031358893</v>
+        <v>-41.46584209922094</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-23.12905411946954</v>
+        <v>-25.07473357265357</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-22.94208793337216</v>
+        <v>-24.91779996665549</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.491814395040201</v>
+        <v>-4.052457509474941</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.341085271317795</v>
+        <v>0.8860677400003496</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.382572453232498</v>
+        <v>6.507130232705649</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>5.64865676495198</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.883716419358016</v>
+        <v>6.108157697159342</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.60496701591002</v>
+        <v>5.831575742688045</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.59291606016492</v>
+        <v>15.57810684621102</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-3.850385038503845</v>
+        <v>-3.334297002987377</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-4.508528336084446</v>
+        <v>-4.016451384872433</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-3.455147366052735</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-9.114583333333371</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-9.708454810495624</v>
+        <v>-9.247467438494894</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-3.477449655793606</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-14.86127317515883</v>
+        <v>-8.818418766290137</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-9.848263787569302</v>
+        <v>-9.385863267670871</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-4.368554193422845</v>
+        <v>-3.905470234070641</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-4.094079480940756</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-4.169911734164067</v>
+        <v>-3.823974743081727</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01066</t>
+          <t>X &gt; -0.01052</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3354</v>
+        <v>3378</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1643053887889394</v>
+        <v>0.2062706550120126</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1712955194978321</v>
+        <v>0.2114664361855318</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2011718540020411</v>
+        <v>0.2377373239968037</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1271078211671295</v>
+        <v>0.1324690171808456</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1637613761328751</v>
+        <v>0.1971428755747979</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.100616692962447</v>
+        <v>0.1055807015022623</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.001982825113707065</v>
+        <v>0.004419111979444779</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02587813125387584</v>
+        <v>-0.01866463268938645</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.05643021818330851</v>
+        <v>-0.05081954492641927</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.04038281108581998</v>
+        <v>-0.03417189262227538</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01639248075093036</v>
+        <v>-0.01039213972623543</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.01060042318687948</v>
+        <v>-0.004602485853745009</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.0127608678255271</v>
+        <v>0.01875329397898895</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1609941017882903</v>
+        <v>-0.1531347309160154</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1176075312474509</v>
+        <v>-0.07983097349559642</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1002740071746544</v>
+        <v>-0.06209099012575336</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.0677616818008957</v>
+        <v>-0.03038835548990448</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.02368804664723001</v>
+        <v>0.06104319980293837</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.01057474246204038</v>
+        <v>0.0270007005633417</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.01530679969392423</v>
+        <v>0.05207206753595983</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.06274099936555189</v>
+        <v>-0.05430455723021055</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.09097506483060869</v>
+        <v>-0.0527417659575633</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.03711640758427848</v>
+        <v>0.00131245416061887</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.06535995519369209</v>
+        <v>-0.05448589366392298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.009928</t>
+          <t>X &gt; -0.009798</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3348</v>
+        <v>3371</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2600724949928335</v>
+        <v>0.2581982571575239</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1490051683369131</v>
+        <v>0.1755100554015598</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1814891258598337</v>
+        <v>0.204413843727913</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.07886620264235233</v>
+        <v>0.070651468425865</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1458691554538234</v>
+        <v>0.1655081605781348</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08227332628329975</v>
+        <v>0.1029306117120043</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01057952934480255</v>
+        <v>0.003201959871944382</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.01285844647844669</v>
+        <v>-0.01929966500384239</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.07327054409128664</v>
+        <v>-0.08131908456093839</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.05582012147537796</v>
+        <v>-0.03345772635043431</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.06203385337831691</v>
+        <v>-0.06929336135797115</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.003776539719503091</v>
+        <v>-0.003817718707232132</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.000580681590186316</v>
+        <v>-0.007674085519049356</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1742550669599368</v>
+        <v>-0.1794118605245956</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.09983009360599482</v>
+        <v>-0.1045513191262089</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.08352295301043711</v>
+        <v>-0.05835015451746983</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.05070799639128865</v>
+        <v>0.003237862640617095</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.07091310840718279</v>
+        <v>0.09514434711358888</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.006392729092588922</v>
+        <v>0.03097583130485759</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.03199121094565527</v>
+        <v>0.05565530778390126</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1049035965815435</v>
+        <v>-0.07940209398982034</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1032142265903389</v>
+        <v>-0.07768751509313887</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.04975447513475473</v>
+        <v>0.005621744287999775</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.07791651313658576</v>
+        <v>-0.04995450510421051</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.009197</t>
+          <t>X &gt; -0.009073</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3338</v>
+        <v>3363</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.271678920486508</v>
+        <v>0.2671783516295037</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2208046596467881</v>
+        <v>0.2439627434233387</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2279170272789202</v>
+        <v>0.2463704430409948</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.09734584285348546</v>
+        <v>0.1137050453290556</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1655541617340077</v>
+        <v>0.209450670726433</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1310149669060365</v>
+        <v>0.1463667193968945</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.001810377273095298</v>
+        <v>0.01871092642986127</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.008944543828270923</v>
+        <v>0.0560716452992267</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.05176495605267917</v>
+        <v>-0.006375309877668656</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.002117288038633092</v>
+        <v>0.04350744205570578</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.03899321955578472</v>
+        <v>0.006964579551578254</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.02785258804927793</v>
+        <v>0.07327362034094165</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.02684326895033706</v>
+        <v>0.0720744489482712</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1765499130558226</v>
+        <v>-0.1291054491447738</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.09993689432892694</v>
+        <v>-0.0524339866913337</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.05547102827437556</v>
+        <v>-0.007439794939678279</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.007746132488485102</v>
+        <v>0.05455613254203939</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1001576296957651</v>
+        <v>0.1470116354142306</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.004893944045214482</v>
+        <v>0.05250547748694601</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.03000948991198271</v>
+        <v>0.07674012886871395</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1356029075932454</v>
+        <v>-0.08699220409397412</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1636307070622323</v>
+        <v>-0.08509711206304615</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.08090188285753896</v>
+        <v>-0.002171328129030314</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1089304413074004</v>
+        <v>-0.05749640033220516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.008466</t>
+          <t>X &gt; -0.008347</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3323</v>
+        <v>3349</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3202889104843223</v>
+        <v>0.3423080287102849</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2707875714718071</v>
+        <v>0.3200395598876966</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1950917086457977</v>
+        <v>0.2386714440862363</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09722109275466551</v>
+        <v>0.1375966121850496</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.137432960247196</v>
+        <v>0.2052015440799835</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1317643620371101</v>
+        <v>0.1709015265403977</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03558901915565826</v>
+        <v>0.07573786128484983</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.04410104922876457</v>
+        <v>0.08482189760049152</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01708792035651641</v>
+        <v>0.021591199303586</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.03651529038550194</v>
+        <v>0.07500384893820922</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.02814420546491903</v>
+        <v>0.06692874554394734</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.03668067317852319</v>
+        <v>0.07517781552095926</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01894512595364972</v>
+        <v>0.01909578860446715</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2222671246716459</v>
+        <v>-0.1819037642589194</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1121175151764291</v>
+        <v>-0.0723047367353189</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.07029757029756922</v>
+        <v>-0.02946967764050612</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.006137386938789291</v>
+        <v>0.03321166070718817</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.08721826642744901</v>
+        <v>0.1266011159014795</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.03960280438344199</v>
+        <v>0.0009840551982378543</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.01478749164146365</v>
+        <v>0.05423259070355613</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1669649300828269</v>
+        <v>-0.1078203082437028</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.224861628677651</v>
+        <v>-0.1354513342397468</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1129322687466541</v>
+        <v>-0.02336145360155228</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1106613914349381</v>
+        <v>-0.04838667367460658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007734</t>
+          <t>X &gt; -0.007622</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3310</v>
+        <v>3335</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2307015060158193</v>
+        <v>0.2393863749269229</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2423286550149726</v>
+        <v>0.2775969098227051</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1719426247728109</v>
+        <v>0.2011108325061031</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.07646700292262665</v>
+        <v>0.1020750535185115</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1181413933510598</v>
+        <v>0.1711017986064221</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1117142908539535</v>
+        <v>0.1359931409013271</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.04824039215829856</v>
+        <v>0.07357528366249255</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.02780206329777712</v>
+        <v>0.05412870229341848</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.03379337107552516</v>
+        <v>-0.009910034124992251</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02303825979210217</v>
+        <v>0.04704426877763268</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.01355788032526561</v>
+        <v>0.06765724745262247</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.006896880506772618</v>
+        <v>0.047220438386951</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.05835569351643244</v>
+        <v>-0.03432620780916551</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2314904584763866</v>
+        <v>-0.2052486721453235</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1786107150275456</v>
+        <v>-0.1521504810978414</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1088287152501834</v>
+        <v>-0.08159732783028772</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.07406042754295328</v>
+        <v>-0.04815604428485898</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.01011393568415997</v>
+        <v>0.01622606644370705</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1081337373564537</v>
+        <v>-0.08090940296592919</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.08446799690481299</v>
+        <v>-0.0583109495785834</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2346205639049543</v>
+        <v>-0.1887392413078217</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.3226604736160823</v>
+        <v>-0.2461621396411786</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1811964982903689</v>
+        <v>-0.1046814722135281</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2088509755202281</v>
+        <v>-0.1591404935398302</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.007003</t>
+          <t>X &gt; -0.006896</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3299</v>
+        <v>3321</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2284693575105194</v>
+        <v>0.285124468061646</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1810025942423152</v>
+        <v>0.2347987724104783</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.11513076621344</v>
+        <v>0.1931577322592446</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.008453520339898546</v>
+        <v>0.06625579846088669</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.004299312346446982</v>
+        <v>0.1067760672426772</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.002803655125184434</v>
+        <v>0.07084293591577051</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.056702447594283</v>
+        <v>0.07139456578447323</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.0371222860030116</v>
+        <v>0.08311203995950933</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.02481259556513749</v>
+        <v>0.01827637197401089</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.03477755014290551</v>
+        <v>0.07881996050776507</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.05456107857472148</v>
+        <v>0.09838586875346067</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.03497708640342978</v>
+        <v>0.07903419639855258</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.04312705457262211</v>
+        <v>0.001838885843355342</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2463275348090974</v>
+        <v>-0.2287898146221892</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1910872179175485</v>
+        <v>-0.1726075410285901</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1230545014574034</v>
+        <v>-0.1041243694905774</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.0877290839815501</v>
+        <v>-0.04006410256410931</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.02322478628254743</v>
+        <v>-0.004906572850217117</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1525694846727248</v>
+        <v>-0.1334261373864507</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.129460805551183</v>
+        <v>-0.1116518489969494</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.217736834207706</v>
+        <v>-0.1800870943857191</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.3361061137163617</v>
+        <v>-0.2073393616996242</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1950895819508887</v>
+        <v>-0.06627751747244304</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1922754133934603</v>
+        <v>-0.09015962715278647</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.006271</t>
+          <t>X &gt; -0.00617</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3268</v>
+        <v>3289</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2193352573886997</v>
+        <v>0.2617210979763556</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2353824731376406</v>
+        <v>0.3038856448838132</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1824640951483048</v>
+        <v>0.2437813977380543</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.0876556964100601</v>
+        <v>-0.02970662486482212</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.07163882224892149</v>
+        <v>0.01384222513247124</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.01971350414833495</v>
+        <v>0.006253614689590847</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.01326520029125078</v>
+        <v>0.04473497451171227</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06095530888510581</v>
+        <v>0.1200245375736984</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.03241840599964263</v>
+        <v>0.02306672855073799</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.03503521872809756</v>
+        <v>0.09191059956607006</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1133912161059385</v>
+        <v>0.1696011835342262</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.06577823884379086</v>
+        <v>0.1224708333067142</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.09395262670371807</v>
+        <v>-0.06586092135224675</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1749366270163719</v>
+        <v>-0.1447782936141664</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.05187387942994803</v>
+        <v>-0.02076376274454361</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.01121906083737656</v>
+        <v>0.04298224672651685</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.04818797029562205</v>
+        <v>0.0783778317152084</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1143377345700571</v>
+        <v>0.1455522883639375</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.04879814839770091</v>
+        <v>0.01374645835332444</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.02720951810525207</v>
+        <v>0.003324325115826809</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1417520174684128</v>
+        <v>-0.09060202830274733</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.19933910677657</v>
+        <v>-0.1173612499726033</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.02895592973587213</v>
+        <v>0.05312541297740836</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.08654440110272787</v>
+        <v>-0.03018399276923844</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.00554</t>
+          <t>X &gt; -0.005445</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3241</v>
+        <v>3262</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1746600885294214</v>
+        <v>0.1864448091801236</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2549095033009934</v>
+        <v>0.2614055348457001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2441307282396608</v>
+        <v>0.2415728216530724</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.05297734835367152</v>
+        <v>0.001176960592374598</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.03403519750975192</v>
+        <v>0.04736121818432082</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1059921690995154</v>
+        <v>-0.05303488642039866</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.001008268065824325</v>
+        <v>0.05328633999042864</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.07613850637107333</v>
+        <v>0.1317101988242797</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.01834920575363697</v>
+        <v>0.03290305939429317</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.05608169012372599</v>
+        <v>0.1088781914655357</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1020789565031706</v>
+        <v>0.1544357274839996</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.08713183755818221</v>
+        <v>0.1397366624912237</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.003071499218471274</v>
+        <v>0.02015968804141011</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1136329017517141</v>
+        <v>-0.08789656832288983</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.01594073132095275</v>
+        <v>0.04278975782941785</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1054261830123977</v>
+        <v>0.1330279652418298</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1438450864268859</v>
+        <v>0.1696014326501469</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.211446606633146</v>
+        <v>0.2384566741121645</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1068202376089715</v>
+        <v>0.1344266833554641</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.03460297225862519</v>
+        <v>0.06094436904356115</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.07637722776659217</v>
+        <v>-0.02904856629265851</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1029564958177502</v>
+        <v>-0.02475127982227576</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.06658951624887521</v>
+        <v>0.1451584964489925</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.02167216475819345</v>
+        <v>0.03187374795989939</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.004808</t>
+          <t>X &gt; -0.004719</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3205</v>
+        <v>3227</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.07892969995922527</v>
+        <v>0.05737327188940355</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2259264758151147</v>
+        <v>0.228086934800487</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2625356992368495</v>
+        <v>0.252338836757005</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.001234232899932408</v>
+        <v>-0.01505702804983855</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.03780644721619097</v>
+        <v>-0.02702287830430095</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.01960009315681788</v>
+        <v>-0.03776749568794457</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.07774647287521219</v>
+        <v>0.07828381109997196</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2210024555828412</v>
+        <v>0.2225239043000258</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.09397350946117911</v>
+        <v>0.09045182100405924</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2400690415424265</v>
+        <v>0.2375711927287369</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.190316771653066</v>
+        <v>0.1881271797505164</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2094446278502744</v>
+        <v>0.2071420982662318</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.06863750478220965</v>
+        <v>0.06746118170425319</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.04066368055598701</v>
+        <v>-0.03906479209251756</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.09775862314373285</v>
+        <v>0.1004281646400003</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.08821087588211185</v>
+        <v>0.09285194701609356</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1285565566703113</v>
+        <v>0.1309330550401953</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.2292398935542224</v>
+        <v>0.2328913613813413</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1521857134639149</v>
+        <v>0.1563512242944043</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1082474676785239</v>
+        <v>0.1107053438924268</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.002110277268606353</v>
+        <v>0.02590143821144153</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.08625505611902895</v>
+        <v>-0.03086165212232572</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1756924744206785</v>
+        <v>0.2311836646732388</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.1185264700307656</v>
+        <v>0.1494439808792905</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.004077</t>
+          <t>X &gt; -0.003994</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3170</v>
+        <v>3190</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.01004602351569872</v>
+        <v>-0.01010260735117896</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1936550850834209</v>
+        <v>0.196522476036094</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.05829181497901459</v>
+        <v>0.0486440253559266</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1353799162655491</v>
+        <v>-0.1527638209005602</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2653369350745152</v>
+        <v>-0.2552204134637179</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1548939597374286</v>
+        <v>-0.1432818300369689</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.01661037746330862</v>
+        <v>-0.01675144047094079</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1312474900514786</v>
+        <v>0.163834224969591</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.002337947369895232</v>
+        <v>-0.002458989814556389</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1585100602623299</v>
+        <v>0.1555231819307537</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1051704315096558</v>
+        <v>0.1023376228921649</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1589856683253643</v>
+        <v>0.1559719338949748</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.03391832138639472</v>
+        <v>-0.03493308630070402</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1420211225274812</v>
+        <v>-0.171102558542934</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.02632429440899386</v>
+        <v>-0.05340737806474749</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.02038801613871755</v>
+        <v>0.02619513967997023</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.0003395474804861465</v>
+        <v>-0.02793960483786861</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1655609375358722</v>
+        <v>0.139265978276029</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1482683284627342</v>
+        <v>0.1219243661156213</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.007235421682580068</v>
+        <v>-0.02067299296519565</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.0940879287606009</v>
+        <v>-0.09992527831920484</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1510958776038791</v>
+        <v>-0.1251861906287033</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.2053003151277437</v>
+        <v>0.231057457795707</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.1168040036557656</v>
+        <v>0.1189023032435941</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003345</t>
+          <t>X &gt; -0.003268</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3106</v>
+        <v>3124</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1487275587778143</v>
+        <v>0.1593116258773222</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2470248406174491</v>
+        <v>0.2165522594531737</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2983570391872234</v>
+        <v>0.3144829861222505</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.07666100074207094</v>
+        <v>-0.03766548792394531</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3304630211665369</v>
+        <v>-0.2955341706969605</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1895788579930482</v>
+        <v>-0.1845535711171067</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.03142569322231026</v>
+        <v>0.02500297151406272</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.123954009969971</v>
+        <v>0.0884183049788092</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.05564937630945366</v>
+        <v>0.04334392544954824</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1347182285159079</v>
+        <v>0.09393668512824149</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.138794460837552</v>
+        <v>0.1295176723576716</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.231531019759835</v>
+        <v>0.2538858652388996</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.0256645981766539</v>
+        <v>0.05056651086466246</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.112200626162128</v>
+        <v>-0.1151237774325367</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.01941000688283623</v>
+        <v>0.01943895807185214</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.05487739586679652</v>
+        <v>0.05698545642487574</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.02777863109603373</v>
+        <v>-0.02802951666134135</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1115387607033469</v>
+        <v>0.113554925722319</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.1215844803965425</v>
+        <v>0.1232747502999274</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.1024522099239107</v>
+        <v>0.1010185738632785</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.05411775990766898</v>
+        <v>-0.03184983626700699</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1428999677686278</v>
+        <v>-0.08802514983092635</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1186301710993973</v>
+        <v>0.1746086956521822</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.09423650937889505</v>
+        <v>0.1275119548838433</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002614</t>
+          <t>X &gt; -0.002543</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3009</v>
+        <v>3026</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.02251922320169797</v>
+        <v>0.1319139543040961</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2006718954153115</v>
+        <v>0.1989951529561296</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3657493773642386</v>
+        <v>0.4065425247076107</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1966333198656898</v>
+        <v>-0.1676495689477733</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3487060251755594</v>
+        <v>-0.3264311057962601</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4407105229037569</v>
+        <v>-0.4469918287831192</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.02257656216600878</v>
+        <v>-0.05903079139375933</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.08182601205857054</v>
+        <v>0.0490962029423514</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.02309520582578983</v>
+        <v>-0.06733419251750661</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.05020387624745126</v>
+        <v>0.04341003389212261</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.08682313708029454</v>
+        <v>-0.0602793379880211</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1171082962631758</v>
+        <v>0.1427930410124389</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1918176632901947</v>
+        <v>-0.1957837918085445</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2608113694073211</v>
+        <v>-0.2930146138789098</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1701495197473477</v>
+        <v>-0.1980365944642344</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1195643437022653</v>
+        <v>-0.1445196651811642</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2006290320475728</v>
+        <v>-0.1960208539399915</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.04602428704916406</v>
+        <v>0.05332411823329153</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.0826108153673033</v>
+        <v>0.05640422448058757</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.07596994364045173</v>
+        <v>-0.0725441788314356</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2201097371044938</v>
+        <v>-0.1914096526164357</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3093638173942139</v>
+        <v>-0.2470231476182718</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1147513155661173</v>
+        <v>-0.08293474669998346</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.004629802182229525</v>
+        <v>0.005796865936410711</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001883</t>
+          <t>X &gt; -0.001817</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2864</v>
+        <v>2861</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.01866340459314841</v>
+        <v>-0.2647911401813516</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.358634063252893</v>
+        <v>0.3058453397247405</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4656494429333193</v>
+        <v>0.5277546321072037</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3667080142596717</v>
+        <v>-0.3925743089587144</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7178543045903609</v>
+        <v>-0.8226155836340965</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4768101555943005</v>
+        <v>-0.4728089503875808</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2418143950402012</v>
+        <v>-0.2949931168941049</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.01401487919738997</v>
+        <v>-0.1285008584278771</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1958384802861133</v>
+        <v>-0.2590122283001506</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.04519202363815822</v>
+        <v>-0.1310750919660038</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.04041553850493074</v>
+        <v>0.02195021642672401</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.1991699144606969</v>
+        <v>0.1133710794429277</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3122103606190763</v>
+        <v>-0.3547104191153991</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.373570249471868</v>
+        <v>-0.4433182499396651</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.3495992119742226</v>
+        <v>-0.4082438742258958</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1872169975618192</v>
+        <v>-0.2097269718000305</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3004782181726995</v>
+        <v>-0.293104951185498</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.001239752984290021</v>
+        <v>-0.02179600494069689</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.1132049916354489</v>
+        <v>-0.1704790424726781</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1149258512042479</v>
+        <v>-0.1098672828695868</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.3435550327733452</v>
+        <v>-0.2727347760507968</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.5033142151333223</v>
+        <v>-0.2923216331469831</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3826193296900655</v>
+        <v>-0.2725974538935958</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.26317678692633</v>
+        <v>-0.09955826088824438</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001151</t>
+          <t>X &gt; -0.001091</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2662</v>
+        <v>2682</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1906419660988803</v>
+        <v>-0.1574990921505588</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.0169134016510526</v>
+        <v>0.09747679887983196</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.05716666368698498</v>
+        <v>-0.02656716959350547</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7494498555355733</v>
+        <v>-0.6726669015513167</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.213975050860313</v>
+        <v>-1.113114644109721</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9149431195257236</v>
+        <v>-0.8246769338267868</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.939786835168043</v>
+        <v>-0.9155335939468259</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6738624117912835</v>
+        <v>-0.6807307141011307</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9102624377331949</v>
+        <v>-0.8657938199436686</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8019612731654604</v>
+        <v>-0.7505798108496009</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4690707112069461</v>
+        <v>-0.4201518490927327</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.202418213630942</v>
+        <v>-0.1186313183890917</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5925741848535395</v>
+        <v>-0.5064030439151708</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8291615678421707</v>
+        <v>-0.7701944388848077</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.903349534202718</v>
+        <v>-0.8359474608740882</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.5491572395620352</v>
+        <v>-0.4387430852379239</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6609819356958155</v>
+        <v>-0.595238095238102</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.2936010970672598</v>
+        <v>-0.2597487931655706</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5653316216193147</v>
+        <v>-0.5073164548339051</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4689446364888212</v>
+        <v>-0.4416503373996363</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6362562828788683</v>
+        <v>-0.5776695991420482</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.764950589819243</v>
+        <v>-0.7054371160047381</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.6935704476867386</v>
+        <v>-0.6262619715114397</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.7096896789006948</v>
+        <v>-0.6174124761167761</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0004197</t>
+          <t>X &gt; -0.0003659</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2322</v>
+        <v>2344</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1594289160804081</v>
+        <v>-0.0936212266294234</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.04399998015784945</v>
+        <v>0.1488076724260097</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1336087581620617</v>
+        <v>-0.06652287959847314</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6946038237114536</v>
+        <v>-0.5932569831583407</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.348994213607234</v>
+        <v>-1.22699978926812</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.033658322760182</v>
+        <v>-0.9196488006511387</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.6502796639034187</v>
+        <v>-0.6121014659797126</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3906498884995173</v>
+        <v>-0.3841677579479992</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6673918579737403</v>
+        <v>-0.6142736152009363</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.516307233086728</v>
+        <v>-0.4947785905351907</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6890796943725661</v>
+        <v>-0.6231265832166386</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2143583128493205</v>
+        <v>-0.1106617812740112</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5834031161542086</v>
+        <v>-0.5455708982997933</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6076573322568279</v>
+        <v>-0.5990362320123168</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3818168242290483</v>
+        <v>-0.3631596414062983</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.1913464542330487</v>
+        <v>-0.1596390918210986</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.001027062212529017</v>
+        <v>0.01696200510856016</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.3087420940615573</v>
+        <v>0.2499771952358998</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1202504459083542</v>
+        <v>-0.1493239160786004</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.4239971894957364</v>
+        <v>-0.446028480819372</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.6654680886445732</v>
+        <v>-0.6902110937578669</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.8879651706651472</v>
+        <v>-0.8256313333362186</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.5880767067503285</v>
+        <v>-0.5569817480338273</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.8107386075490766</v>
+        <v>-0.7617828583642492</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003117</t>
+          <t>X &gt; 0.0003597</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.272905401227966</v>
+        <v>-1.105803623417458</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.7880100684302391</v>
+        <v>-0.5394360908902769</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.679581030029532</v>
+        <v>-1.794130192781857</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.708183124284687</v>
+        <v>-2.880435645905422</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.447788912656804</v>
+        <v>-2.565799216186846</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.895859222909792</v>
+        <v>-1.908100552461676</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.299194768114006</v>
+        <v>-1.345716501345976</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.121201833305044</v>
+        <v>-1.288645994528352</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.535919030952378</v>
+        <v>-1.794201247740169</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.122703320127556</v>
+        <v>-1.362959149937012</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.9398845538780378</v>
+        <v>-1.039808976411692</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2149843222895385</v>
+        <v>-0.1764541473541499</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5411656796474631</v>
+        <v>0.4327916662295621</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4660886563976376</v>
+        <v>0.3290393578966615</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1920546411829207</v>
+        <v>-0.3531150239883942</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.4937399590050404</v>
+        <v>0.2990155161755013</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.055123313270663</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.139669617683694</v>
+        <v>2.081012998265756</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5257348320938391</v>
+        <v>0.5298363187054775</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.5843922705066191</v>
+        <v>0.5622734012872286</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.9575970182915015</v>
+        <v>0.9605360030674674</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.5154506905820355</v>
+        <v>0.7030580754604046</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.789925403064089</v>
+        <v>0.8555348579128861</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.6778324353032943</v>
+        <v>0.6933958636234223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001043</t>
+          <t>X &gt; 0.001085</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.526823522344159</v>
+        <v>-2.361524365905872</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.026737935372871</v>
+        <v>-0.9013944562029224</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.892017796985769</v>
+        <v>-0.9749861958897768</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.189589106239758</v>
+        <v>-2.092322777900094</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.45450309012211</v>
+        <v>-2.560333865323202</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.398942948702775</v>
+        <v>-2.201622819668145</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.462613051778412</v>
+        <v>-1.417757463479823</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.609418451853436</v>
+        <v>-1.591098959520011</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.567931269938732</v>
+        <v>-1.726327944572745</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.42100463322884</v>
+        <v>-1.5276495320187</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.329599393169403</v>
+        <v>-2.309432962737155</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.162882305158796</v>
+        <v>-1.062346432429507</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1059143491917567</v>
+        <v>-0.3302728506718324</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.01434926101305933</v>
+        <v>0.02692419178730887</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.7755463422328432</v>
+        <v>-0.7873305863989231</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.1811594202898519</v>
+        <v>-0.226026567579261</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.4227711175999644</v>
+        <v>0.4092261904761898</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.10948714201097</v>
+        <v>0.9377177466902467</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.445070025877371</v>
+        <v>-1.549561502739891</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6531416618754022</v>
+        <v>-0.6727234020517656</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.2709850557331066</v>
+        <v>-0.367295628413622</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.00733299864816</v>
+        <v>-0.9729621291487476</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.2044567009613374</v>
+        <v>-0.3314496597854841</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.466208030460372</v>
+        <v>-0.3609626593799931</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001775</t>
+          <t>X &gt; 0.001811</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.812668419273891</v>
+        <v>-3.892277077760944</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.429232159204467</v>
+        <v>-1.865456640737541</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.805395538132359</v>
+        <v>-2.071199693678082</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.942431747897508</v>
+        <v>-3.362902591786998</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.278222220444782</v>
+        <v>-3.371783451198546</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.091256034347403</v>
+        <v>-3.214849845200462</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.969917282781651</v>
+        <v>-2.083487023807962</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.936596885882395</v>
+        <v>-3.088932861262109</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.550875624793854</v>
+        <v>-2.961003951578</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.635323142482669</v>
+        <v>-3.05653005275181</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.221848698255336</v>
+        <v>-3.309689083681626</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.60731066624723</v>
+        <v>-1.659826204527704</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.04693068313005</v>
+        <v>-0.1477480943077154</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6976863489457799</v>
+        <v>0.5838316519833811</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.03954305136522152</v>
+        <v>-0.09832272990167468</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.05691631339298908</v>
+        <v>-0.2387730970469164</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.08496720820445347</v>
+        <v>-0.1672149122807127</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.018188788120291</v>
+        <v>0.9279711579962893</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.188065159675098</v>
+        <v>-1.212267074266556</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3802410164836871</v>
+        <v>-0.4704398559211072</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.637004843279918</v>
+        <v>0.4732916619065506</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.3053922446456525</v>
+        <v>-0.3060962121614139</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.6623233690495809</v>
+        <v>0.6417636252296433</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.3439771547248185</v>
+        <v>0.3035682929120114</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002506</t>
+          <t>X &gt; 0.002536</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>430</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.562506099607084</v>
+        <v>-4.581887698087506</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.514794418694223</v>
+        <v>-3.211166358271747</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.339910241918766</v>
+        <v>-3.080179166860781</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.896182233711727</v>
+        <v>-5.520156423405723</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.849484226996339</v>
+        <v>-4.290817634243233</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.510444308180062</v>
+        <v>-3.207958102319232</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.591148752439075</v>
+        <v>-3.308595670107493</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.638945450648379</v>
+        <v>-3.382034632034639</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.136628775646109</v>
+        <v>-2.791142759387569</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.139959198226379</v>
+        <v>-3.81867573608838</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-4.096314302608242</v>
+        <v>-3.777922202965534</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.301330987162224</v>
+        <v>-1.971170824103496</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.217194281123199</v>
+        <v>-1.23421108970242</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.5477631096443076</v>
+        <v>0.5068991815962747</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.5733431508992126</v>
+        <v>-0.6392923232586227</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.2525252525252526</v>
+        <v>0.1540302570459673</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.489193317919522</v>
+        <v>0.282168406805873</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.07968450887148748</v>
+        <v>-0.3147528213255697</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.183978742796356</v>
+        <v>-2.420476209028976</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.398740875417225</v>
+        <v>-1.741852641000165</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.3842943519655861</v>
+        <v>0.1490204532593182</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.3084483905564852</v>
+        <v>0.306416070838921</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.0480393821083</v>
+        <v>1.015166835187067</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>0.1553534222929471</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003237</t>
+          <t>X &gt; 0.003262</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.448076029094615</v>
+        <v>-5.067016972013036</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.578033550336002</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.811233322258559</v>
+        <v>-4.128593519364586</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.235030715195272</v>
+        <v>-7.769776205977685</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-8.570821187742546</v>
+        <v>-7.740456297296532</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.576626085982511</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.637731396378896</v>
+        <v>-3.805433971823845</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.217147660409069</v>
+        <v>-4.720110512793447</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.970841201385937</v>
+        <v>-3.372669407987381</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-5.647371335253759</v>
+        <v>-5.083355049548189</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.072106873814718</v>
+        <v>-4.811120034943855</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.844832180877177</v>
+        <v>-3.563311745512706</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.991508243292571</v>
+        <v>-3.15381361906104</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.527152715271527</v>
+        <v>-1.703308216035282</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.185296012852085</v>
+        <v>-2.385462597920338</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.287878787878789</v>
+        <v>-1.518348181547168</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.421795924856262</v>
+        <v>-1.622228593272176</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.526636628677444</v>
+        <v>-1.755112698433777</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-2.825896762904634</v>
+        <v>-3.069702459055591</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.162860476746133</v>
+        <v>-2.549305616443085</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.03015566531824021</v>
+        <v>-0.4901577461985198</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.04569029609086073</v>
+        <v>-0.2585718018961316</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.8366871519534982</v>
+        <v>0.5985596158975781</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.7589019401755479</v>
+        <v>-1.09732170968023</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.003969</t>
+          <t>X &gt; 0.003987</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.926561399146259</v>
+        <v>-2.646569380440347</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.261338197496073</v>
+        <v>-2.892476216144217</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.342214389384203</v>
+        <v>-3.788747378967699</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-8.269454123112652</v>
+        <v>-7.965378968456925</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-8.248101738517072</v>
+        <v>-7.524091230420055</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.203992695276838</v>
+        <v>-4.858197050945272</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.40451280773862</v>
+        <v>-2.06904967249698</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.968438538205973</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.212665642005561</v>
+        <v>-0.8123494499491031</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.057009889470613</v>
+        <v>-2.683669762372737</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.497235961594413</v>
+        <v>-3.128280625904601</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.061699650756687</v>
+        <v>-2.6880167022397</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.32771886046995</v>
+        <v>-1.293948246213773</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.266155647822842</v>
+        <v>-0.2567590333630747</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.282721884471499</v>
+        <v>-1.298625645463957</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.02851091560768282</v>
+        <v>-0.01789716621264148</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.539097977642179</v>
+        <v>-1.560626498800964</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.2102469251909724</v>
+        <v>-0.2546616830992505</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.144893178675247</v>
+        <v>-2.198472837248445</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.032336324639239</v>
+        <v>-1.264461931757808</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.302815349121346</v>
+        <v>1.263956226913919</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.946393848143906</v>
+        <v>1.910815365608457</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.940293021057606</v>
+        <v>2.876471511536664</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.065899616755196</v>
+        <v>0.9092783656226473</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.0047</t>
+          <t>X &gt; 0.004713</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.220679046205078</v>
+        <v>-2.709293394777269</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.874783575647321</v>
+        <v>-1.288533563814468</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.732970691905201</v>
+        <v>-2.959894332372713</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.807269249163078</v>
+        <v>-7.302296531180936</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.302723587256573</v>
+        <v>-6.744521337946942</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.174580930570947</v>
+        <v>-3.670921065282187</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.5339969224850876</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.077779949188987</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.959603265557469</v>
+        <v>2.440338722093912</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.07381661215968904</v>
+        <v>0.3942872268745816</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.480429238905337</v>
+        <v>-1.000144425187756</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.179346709580223</v>
+        <v>-1.693393046325717</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.479003828605677</v>
+        <v>0.5250481695568396</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.775494005096711</v>
+        <v>1.779603508402673</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.2734688509760659</v>
+        <v>0.2606290428356033</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.289796701189111</v>
+        <v>1.240343103496279</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.9538250771385748</v>
+        <v>-0.9555875174337487</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.629097932120402</v>
+        <v>0.5851685447686563</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.264715328305478</v>
+        <v>-1.29241943729059</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.4074125348575137</v>
+        <v>-0.6594229503905922</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.592414178532394</v>
+        <v>1.538506480228243</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.364025844241937</v>
+        <v>2.303680092726744</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.485958183842634</v>
+        <v>3.3876507124589</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.291481862822749</v>
+        <v>1.124671382034983</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.005432</t>
+          <t>X &gt; 0.005439</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>199</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-6.640847113431967</v>
+        <v>-6.278945136070796</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.539777344908991</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.913642960812773</v>
+        <v>-5.291983884611518</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.126596980255513</v>
+        <v>-6.879410959041635</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-5.962387452802787</v>
+        <v>-5.662431785708129</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.775421266705408</v>
+        <v>-3.515448428466271</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9526300494042346</v>
+        <v>1.162106375221413</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.674418604651166</v>
+        <v>1.85221080743468</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.21590578656587</v>
+        <v>2.477652154929736</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.942990110529379</v>
+        <v>2.179113097521338</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2170497526912953</v>
+        <v>0.4612983608818979</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.061699650756701</v>
+        <v>-0.810308469211293</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1848617176128116</v>
+        <v>-0.4326632732292239</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.403104632071255</v>
+        <v>2.110147441457066</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.242448771676621</v>
+        <v>0.9279930595720103</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.836835693619612</v>
+        <v>1.489297078391672</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8096442574282108</v>
+        <v>-1.114583333333343</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.5930527271928128</v>
+        <v>0.2525325615050633</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.703618705953211</v>
+        <v>-2.03300521134917</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.00923520754297158</v>
+        <v>-0.3184187662901792</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.458268875747279</v>
+        <v>1.418156832831599</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.387448039966323</v>
+        <v>2.348019436504458</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.666947878076513</v>
+        <v>3.59667904741098</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.581065373596957</v>
+        <v>1.424489801865228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006163</t>
+          <t>X &gt; 0.006164</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.895284983254449</v>
+        <v>-6.174205675479023</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.679765923616102</v>
+        <v>-2.911340581358324</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.892932901641174</v>
+        <v>-5.920420648162192</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.014170944752557</v>
+        <v>-6.512822846970415</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.983097511974385</v>
+        <v>-4.44919970052004</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.612699373214284</v>
+        <v>-3.122675451247105</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.124227682540337</v>
+        <v>2.514991074531878</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.621164166781341</v>
+        <v>3.964456596035532</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>4.677180827357077</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.073167625322277</v>
+        <v>4.465924653775161</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.388647385827397</v>
+        <v>1.814183060192363</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.07353397028332154</v>
+        <v>0.3680104624462146</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.01326408447671668</v>
+        <v>-0.1620863333671352</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.7131070249882114</v>
+        <v>0.521912147339421</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.0549637274076531</v>
+        <v>-0.1602422345456347</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.05411255411255667</v>
+        <v>-0.1871735098436176</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.055995059055398</v>
+        <v>-3.232230392156865</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>-2.776879203200821</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-2.944944381952254</v>
+        <v>-3.150652270172692</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.567622381508038</v>
+        <v>-1.759595236878418</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.324454263759776</v>
+        <v>-0.2142656345348186</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.385414060545408</v>
+        <v>1.485719772503977</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.850364963503651</v>
+        <v>2.912786210445077</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.2016577659100989</v>
+        <v>-0.2079326655011897</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.006895</t>
+          <t>X &gt; 0.00689</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-7.694901167486016</v>
+        <v>-6.875960061443934</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-6.002650938808813</v>
+        <v>-5.121866897147797</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.440669987839804</v>
+        <v>-6.376560999039377</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-10.85632670998525</v>
+        <v>-10.30229653118094</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-8.489414479829819</v>
+        <v>-7.911188004613606</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-6.275421266705408</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.736413833188024</v>
+        <v>2.117330255818423</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.809553739786296</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.526716597376684</v>
+        <v>3.940338722093919</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.429476597015871</v>
+        <v>3.810953893541239</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3251578607994077</v>
+        <v>0.7498555748122371</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.304942893999936</v>
+        <v>-0.8600597129923884</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.076753609504706</v>
+        <v>-1.308285163776489</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.138277093015432</v>
+        <v>0.8416910656181429</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.2001383134086652</v>
+        <v>-0.5116042558642278</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.646567717996291</v>
+        <v>-1.963723055836518</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-3.821301181504381</v>
+        <v>-4.08102628635347</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.926141885325563</v>
+        <v>-4.213910391515071</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-4.390522613244777</v>
+        <v>-4.670589103966613</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-2.843132585589672</v>
+        <v>-3.113720779712999</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-2.025134535868624</v>
+        <v>-1.953430835238478</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.06016417074710745</v>
+        <v>-0.001566330166738794</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.574854759422017</v>
+        <v>1.593419506462993</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.222065929175407</v>
+        <v>-1.271422190529179</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.007626</t>
+          <t>X &gt; 0.007615</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-7.98867320038849</v>
+        <v>-7.114055299539167</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.424899274100625</v>
+        <v>-4.502819278100176</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.862918323131616</v>
+        <v>-5.757513379991757</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.19906074837146</v>
+        <v>-10.63562986451427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-10.08557585859989</v>
+        <v>-9.482616576042176</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-5.550783585545986</v>
+        <v>-5.039968684329814</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.648282223317288</v>
+        <v>2.022092160580335</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.819346140883049</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.310108685116589</v>
+        <v>4.702243483998679</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.26183069023952</v>
+        <v>4.620477703065056</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.912701926604349</v>
+        <v>1.321284146240821</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8153228391624907</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.489209543699765</v>
+        <v>-0.7844756399669635</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.178001011780019</v>
+        <v>0.8223776572843988</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.2100692930998065</v>
+        <v>-0.5792011850323036</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.805463393054637</v>
+        <v>-2.17617054750761</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-3.399234544630652</v>
+        <v>-3.718899880095925</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.504075248451834</v>
+        <v>-3.851783985257526</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-3.288183867527508</v>
+        <v>-3.637321758111753</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.64148404296094</v>
+        <v>-1.983886392189461</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.7241761963284219</v>
+        <v>-0.6902110937578669</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.389758864160285</v>
+        <v>1.408539427765113</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.12408759124088</v>
+        <v>3.10144927536232</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.8584743161197963</v>
+        <v>0.7653972375945983</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.008358</t>
+          <t>X &gt; 0.008341</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-10.1982241626123</v>
+        <v>-9.64018770372035</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-7.25431243637194</v>
+        <v>-6.634062019099019</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-7.872659354255397</v>
+        <v>-7.075747990909299</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-11.8643018982883</v>
+        <v>-11.73319084012402</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-11.38042023968804</v>
+        <v>-11.19574085014207</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.914765529000491</v>
+        <v>-7.786774723818773</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3296792297321076</v>
+        <v>0.361232694842812</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.330156309569198</v>
+        <v>3.308344771759408</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.191315622631443</v>
+        <v>4.24928181152481</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.238072077742494</v>
+        <v>4.266238446386772</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4137710641667098</v>
+        <v>0.4734328105846046</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.504322601576369</v>
+        <v>-1.429165404049293</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9881404061374042</v>
+        <v>-0.9180412613374642</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.381147205629652</v>
+        <v>-2.33247550936261</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-3.865736784201943</v>
+        <v>-3.834302022395207</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.750688705234161</v>
+        <v>-5.732014397018162</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-6.711052123203366</v>
+        <v>-6.655566939890711</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-6.815892827024548</v>
+        <v>-6.788451045052312</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-6.600001446100222</v>
+        <v>-6.573988817906539</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-4.760263074148732</v>
+        <v>-4.720058110552472</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.823470399139552</v>
+        <v>-2.828486218490589</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.419977517573443</v>
+        <v>-0.4446323470032496</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.6809434759003423</v>
+        <v>0.6186742694226695</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-1.874227620298143</v>
+        <v>-2.002481118309419</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.009089</t>
+          <t>X &gt; 0.009066</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-11.9741804467653</v>
+        <v>-10.81535400083787</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-9.531179467337338</v>
+        <v>-8.333988109269015</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-7.265494812664627</v>
+        <v>-6.861409483887869</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.68215253581107</v>
+        <v>-11.99926622815064</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.09201708243241</v>
+        <v>-11.36573345915906</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-9.97912497040911</v>
+        <v>-10.29970894407007</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-1.094790956302788</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.859603789836349</v>
+        <v>2.236652236652233</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.827016897676984</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.980027147566418</v>
+        <v>3.386711469298824</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3755428399012928</v>
+        <v>-0.8865080615513961</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.58021816927522</v>
+        <v>-2.072180925113599</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.07439754164644086</v>
+        <v>-0.4598003152916448</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.462015360414547</v>
+        <v>-2.009118613588804</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-3.054738097247444</v>
+        <v>-3.608704188134418</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.264089493061462</v>
+        <v>-5.799693747296395</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-6.332586069291267</v>
+        <v>-5.903574159021403</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.568267894607779</v>
+        <v>-5.11902707152246</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.352376513683453</v>
+        <v>-4.904564844376686</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.165530703715426</v>
+        <v>-4.689978399317702</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-1.904338553924447</v>
+        <v>-2.505129322716783</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.8235538024234614</v>
+        <v>1.089432925970137</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.032607954157854</v>
+        <v>2.250498603909058</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.08761682242990076</v>
+        <v>-0.663933968362052</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.00982</t>
+          <t>X &gt; 0.009792</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-9.962686193891734</v>
+        <v>-9.722402009009471</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-9.148037704885226</v>
+        <v>-8.844713339095371</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.838930317134604</v>
+        <v>-4.481429912897056</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-10.14958548600264</v>
+        <v>-10.69180963979517</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.48537595854992</v>
+        <v>-10.96736777989451</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.29840977245254</v>
+        <v>-10.81043417389643</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.874956157492313</v>
+        <v>-1.493156635567338</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.743384121892547</v>
+        <v>3.819900449113931</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.78487130380725</v>
+        <v>5.071424864416009</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.161380915127083</v>
+        <v>5.398968874814649</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.987164695220045</v>
+        <v>2.300417372565057</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.708415291772049</v>
+        <v>2.023835418093761</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.182954374341215</v>
+        <v>5.403325323114892</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3641743484693407</v>
+        <v>1.337420168729793</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-1.443394236467554</v>
+        <v>-0.4810978495188962</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-3.147857889237201</v>
+        <v>-2.192521103426508</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-5.580625600927313</v>
+        <v>-4.569128787878796</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-4.536041017392179</v>
+        <v>-3.565649256676757</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.320149636467853</v>
+        <v>-3.351187029530983</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.133303826499827</v>
+        <v>-3.136600584471999</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-2.376999419753211</v>
+        <v>-1.431317813125453</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.9954304809066556</v>
+        <v>1.902610574010168</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>2.419330480745032</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.194072940165434</v>
+        <v>1.984106064999082</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01055</t>
+          <t>X &gt; 0.01052</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-5.814760156910225</v>
+        <v>-6.399769585253459</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-6.645676420957329</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>0.6710580485796669</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.503408574458405</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.187025133962202</v>
+        <v>-7.339759433185037</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.000058947864822</v>
+        <v>-7.182825827186953</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.974906182479813</v>
+        <v>-0.8350506965625257</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.543983822042478</v>
+        <v>4.57431457431457</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3.585471003957181</v>
+        <v>4.702243483998679</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4.26183069023952</v>
+        <v>5.334763417350764</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1880642454449273</v>
+        <v>1.321284146240821</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.09068515800306898</v>
+        <v>1.044702191769524</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.6847034997785</v>
+        <v>2.786952931461606</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.46362462333191</v>
+        <v>2.538718870028497</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.643794036567499</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-1.498682476943344</v>
+        <v>-1.867845778751189</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-4.531150338558497</v>
+        <v>-3.40029761904762</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.186715680060843</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-2.970824299136517</v>
+        <v>-3.318719497063448</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-1.334703126849647</v>
+        <v>-1.67556162343304</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>2.394730830731739</v>
+        <v>3.396117067516656</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.118480905532628</v>
+        <v>5.068322981366471</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>2.593373289990517</v>
+        <v>3.477612558505569</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01066</t>
+          <t>X &lt; -0.01052</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.713310881547912</v>
+        <v>-10.68548387096774</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.048087679897726</v>
+        <v>-9.502819278100183</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.48610672892872</v>
+        <v>-12.18608480856319</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.851234661414928</v>
+        <v>-7.064201293085702</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.636300496281045</v>
+        <v>-8.768330861756468</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-5.550783585545986</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>-0.8350506965625257</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.6454330974047906</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.136195641638331</v>
+        <v>1.845100626855825</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.363279965601841</v>
+        <v>1.049049131636487</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1880642454449273</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.09068515800306898</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.213847224859187</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>6.824433155742774</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.153307412707868</v>
+        <v>3.285135916714864</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.298418972332009</v>
+        <v>2.417868506963103</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.715226473035699</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.737440317741999</v>
+        <v>-3.533181724209221</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.07227357449883698</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.334703126849647</v>
+        <v>-3.104133052004464</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>2.470576792140839</v>
+        <v>2.042708160900517</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>3.844006193050575</v>
+        <v>3.396117067516656</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>1.219930180894963</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.593373289990517</v>
+        <v>3.477612558505569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.009928</t>
+          <t>X &lt; -0.009798</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-12.30751378009863</v>
+        <v>-11.98418516966904</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.308957245115117</v>
+        <v>-7.035286810567719</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.746976294146108</v>
+        <v>-9.588682211160595</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.126596980255513</v>
+        <v>-3.687577916462331</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.129054119469451</v>
+        <v>-6.560538653964258</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.275421266705408</v>
+        <v>-5.104903749264878</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.047369950595751</v>
+        <v>-0.7051805666923983</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.007751937984501467</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>3.013931795686986</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.942990110529379</v>
+        <v>0.9191790017663521</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.217049752691302</v>
+        <v>2.490115315071982</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.7283663174233581</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.5181950509461473</v>
+        <v>-0.2000600555513827</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>7.343913675223298</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.93591610836004</v>
+        <v>4.064356695935643</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>3.196969696969703</v>
+        <v>2.028258117352706</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.729719226658887</v>
+        <v>-0.6730248917748938</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-3.708454810495617</v>
+        <v>-4.702012893040397</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.8258967629046339</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.972384286269936</v>
+        <v>-2.974262922134336</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.151736212430698</v>
+        <v>2.951799069991424</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>4.075890251021598</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.68369829683698</v>
+        <v>0.5228684359119171</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>2.941199376947047</v>
+        <v>2.958132039025053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.009197</t>
+          <t>X &lt; -0.009073</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>85</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-11.28790593696138</v>
+        <v>-11.18968555164001</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-9.2697415588406</v>
+        <v>-9.082651210873287</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.531290019636302</v>
+        <v>-10.33734531276487</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.361891097902564</v>
+        <v>-5.047394570396627</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.050622746920432</v>
+        <v>-7.675893886966549</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.687185972587763</v>
+        <v>-6.342489692733167</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5767817153016424</v>
+        <v>-1.255218763789415</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.8549931600547183</v>
+        <v>-2.736609795433331</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.53943519833058</v>
+        <v>-0.255739709278636</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.4099510659412147</v>
+        <v>-2.228261792733264</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.040579164456013</v>
+        <v>-0.7795561898936398</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.591111415462578</v>
+        <v>-3.409079320835524</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.537802894083406</v>
+        <v>-3.347500850050999</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.476412347117062</v>
+        <v>4.639559206162943</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3.465327873065917</v>
+        <v>1.604463647807307</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.706773618538328</v>
+        <v>-0.1871735098436176</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.780084694909732</v>
+        <v>-2.64399509803922</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.414337163436798</v>
+        <v>-6.306290967906698</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.6690340178065881</v>
+        <v>-2.562416976055047</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.658658796073865</v>
+        <v>-3.524301119231353</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>4.857618565371872</v>
+        <v>2.967077908799673</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.958243192198061</v>
+        <v>4.068385975079678</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.703306139974238</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.803944474986253</v>
+        <v>2.973410877833302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.008466</t>
+          <t>X &lt; -0.008347</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.06658968768939</v>
+        <v>-12.12848531396919</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-9.421168466237226</v>
+        <v>-10.35419012947103</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.898791475664261</v>
+        <v>-8.578581201059585</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.651349455503038</v>
+        <v>-5.130579359463766</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.977238937951299</v>
+        <v>-6.416238509664112</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.790272751853919</v>
+        <v>-6.259304903666028</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.601825396140306</v>
+        <v>-3.013982875494705</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.880036840893382</v>
+        <v>-3.318903318903324</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1416483608232895</v>
+        <v>-1.170772389017195</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.621366325114188</v>
+        <v>-2.97692489433755</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.347306682952265</v>
+        <v>-2.704689879733216</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.626056086400261</v>
+        <v>-2.981271834204513</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2210788764465903</v>
+        <v>-1.065860921352247</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.93069306930694</v>
+        <v>5.756612087921717</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>3.302252742023406</v>
+        <v>2.044154675733623</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.916441644164415</v>
+        <v>0.5852566743512639</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1976735126150402</v>
+        <v>-1.538825757575758</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.272811246139192</v>
+        <v>-4.702012893040397</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.9034761743890982</v>
+        <v>-0.4471466254905749</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.8898760354448569</v>
+        <v>-2.252762200633619</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>5.151736212430698</v>
+        <v>3.240399358591716</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7.075890251021598</v>
+        <v>5.185438856838452</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.350364963503651</v>
+        <v>1.388669301712788</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>3.274532710280376</v>
+        <v>2.236631317524328</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007734</t>
+          <t>X &lt; -0.007622</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>113</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.149619043256529</v>
+        <v>-7.524927613066353</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.484395841606343</v>
+        <v>-7.770834448770223</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-6.370661294024636</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.617825050430952</v>
+        <v>-3.423240483983292</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.830808505434369</v>
+        <v>-4.583754376295019</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.64384231933699</v>
+        <v>-4.426820770296935</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.784212055858909</v>
+        <v>-2.567035525892493</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.185230518155855</v>
+        <v>-1.98700021708872</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>-0.08915980297982884</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.039466029821497</v>
+        <v>-1.770167050411558</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.7654063876595742</v>
+        <v>-2.382887788019616</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1669628086514265</v>
+        <v>-1.774513990278521</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.341454071860873</v>
+        <v>0.6504169011202663</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.383533090151133</v>
+        <v>5.711917352961486</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.848196810114423</v>
+        <v>4.144807218864045</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>2.811004784689004</v>
+        <v>2.051243981046532</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.799894665255387</v>
+        <v>1.062407817109147</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.0593320034780831</v>
+        <v>-0.8403877924772374</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.788138324814675</v>
+        <v>2.028941691305697</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.097791152326558</v>
+        <v>1.358572384152303</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>6.523417628359901</v>
+        <v>5.215906643833506</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>9.102438923587961</v>
+        <v>7.795611378515396</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>4.95213487500807</v>
+        <v>3.614467102731822</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>5.761258373997187</v>
+        <v>5.222239612867135</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.007003</t>
+          <t>X &lt; -0.006896</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.440847113431971</v>
+        <v>-7.873335389527917</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.175623911781784</v>
+        <v>-5.757037500822342</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.413642960812773</v>
+        <v>-5.436928453107619</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1265969802555063</v>
+        <v>-2.092322777900094</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4623874528027798</v>
+        <v>-2.367880917999429</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2754212667054006</v>
+        <v>-2.210947312001345</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.847369950595755</v>
+        <v>-2.218627749430915</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.325581395348827</v>
+        <v>-2.523548192839534</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3159057865658639</v>
+        <v>-0.8208161335491297</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.257009889470623</v>
+        <v>-2.404269203571616</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.78295024730869</v>
+        <v>-2.91943576377043</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.261699650756697</v>
+        <v>-2.408616143438579</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>-0.3739019616767578</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>6.194059405940607</v>
+        <v>5.677076575315333</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>4.735916108360037</v>
+        <v>4.207520618627129</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.93030303030303</v>
+        <v>2.406619913037346</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.996385893325559</v>
+        <v>0.7279363517060418</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.2915451895043759</v>
+        <v>-0.1923493282587216</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.707436570428705</v>
+        <v>3.171719198099659</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.094282380396727</v>
+        <v>2.598904068355495</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.47431685759198</v>
+        <v>4.393664291384205</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>8.62427734779579</v>
+        <v>5.893304919035209</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.866493995761715</v>
+        <v>2.199931530297853</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.79066174253844</v>
+        <v>2.825194110811537</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.006271</t>
+          <t>X &lt; -0.00617</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.922898395483251</v>
+        <v>-5.743884589745818</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.257675193833066</v>
+        <v>-5.989791425449688</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.131591678761495</v>
+        <v>-5.357693074511083</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.565710712052173</v>
+        <v>0.3392129027813269</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.229920239504899</v>
+        <v>0.06365476268199188</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1348351435510011</v>
+        <v>-0.4083424489299858</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.003912100686292774</v>
+        <v>-1.203424461162705</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.556350626118061</v>
+        <v>-2.766206539791455</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4082134788735559</v>
+        <v>-0.7514851772771536</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.005727838188569</v>
+        <v>-2.176467490106553</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.654745119103566</v>
+        <v>-3.791024928332412</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.651443240500285</v>
+        <v>-2.809745247583585</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.712574179823079</v>
+        <v>1.106809175846145</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.414572226453416</v>
+        <v>2.745367567243228</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.8333520057959305</v>
+        <v>0.1764207325279799</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.4953379953379908</v>
+        <v>-1.149067701482544</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.270280773341106</v>
+        <v>-1.881878930817614</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.657172759213573</v>
+        <v>-3.272624671199338</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.7638468268389573</v>
+        <v>-0.5424391736133174</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.3096669957813418</v>
+        <v>-0.3278527285543333</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.732381373721026</v>
+        <v>1.620426040505187</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.946857992957078</v>
+        <v>2.803125153770026</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>-0.726825266611975</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.564855290925536</v>
+        <v>0.9978281919287539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.00554</t>
+          <t>X &lt; -0.005445</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.367623069716117</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.795296042929323</v>
+        <v>-4.32616797241662</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.593970829665231</v>
+        <v>-4.505593257103897</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7040041126406607</v>
+        <v>-0.2592857784927673</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3682136400933871</v>
+        <v>-0.5348439185921023</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.64807600105415</v>
+        <v>0.6973585046102926</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2167688576995843</v>
+        <v>-1.172992324826737</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.587876477316051</v>
+        <v>-2.55318158543966</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.0929549668937355</v>
+        <v>-0.8123494499491031</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.226408796574447</v>
+        <v>-2.146035353770586</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.045245329275915</v>
+        <v>-2.949069156370555</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.777546645292219</v>
+        <v>-2.6880167022397</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1684682749898627</v>
+        <v>-0.5771023680775613</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.796245198290329</v>
+        <v>1.32520120489793</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.5012423615853194</v>
+        <v>-0.9698564027935745</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.092647789369103</v>
+        <v>-2.559090018382513</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.773013013778268</v>
+        <v>-3.200604838709687</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.970749892462841</v>
+        <v>-4.408757761075584</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.115514249243432</v>
+        <v>-2.581392308123348</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.8357722644120145</v>
+        <v>-1.291537045860068</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.140747201441691</v>
+        <v>0.2915560871677982</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.614351789483138</v>
+        <v>0.7540279738146651</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.407876794738101</v>
+        <v>-2.228143992519861</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.1646426003902661</v>
+        <v>-0.2397453524007247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.004808</t>
+          <t>X &lt; -0.004719</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.368119840704694</v>
+        <v>-1.053938945305163</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.521078457236328</v>
+        <v>-3.109800532140262</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.050006597176406</v>
+        <v>-3.912005946249039</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2175060711646069</v>
+        <v>0.02047873277079759</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3557943653790332</v>
+        <v>0.6498979682370702</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.08821509693095209</v>
+        <v>0.3543428864523506</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.339607393518136</v>
+        <v>-1.345716501345976</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.444302856536055</v>
+        <v>-3.460591695885817</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.576331656356508</v>
+        <v>-1.522708035070487</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.719110346091625</v>
+        <v>-3.676225593638243</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.988429699363493</v>
+        <v>-2.951501891251105</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.26717910281149</v>
+        <v>-3.228083845722402</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.193994137704131</v>
+        <v>-1.17555514869354</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4114110041141146</v>
+        <v>0.3861655410045799</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.616595307165078</v>
+        <v>-1.653454904228887</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.478829389788288</v>
+        <v>-1.544639573192043</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.069367531331977</v>
+        <v>-2.101008672699855</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.544071248851786</v>
+        <v>-3.591358841209868</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.414937858795042</v>
+        <v>-2.471919238498486</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.771471044260807</v>
+        <v>-1.804844105656699</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2152362646335249</v>
+        <v>-0.5623338559062034</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.085064562948205</v>
+        <v>0.7199696854869231</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.768901091542219</v>
+        <v>-3.108794019279948</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.92730215210495</v>
+        <v>-1.913466950221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.004077</t>
+          <t>X &lt; -0.003994</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.3075137800986312</v>
+        <v>-0.05425463508734651</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.603074892173943</v>
+        <v>-2.238145966915241</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9038390392441471</v>
+        <v>-0.7796617742331833</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.520461843273893</v>
+        <v>1.728711220757049</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.145455684452116</v>
+        <v>3.391137576781745</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.763794419569109</v>
+        <v>1.610086686655798</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.03924422263258975</v>
+        <v>0.03981087597346544</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.813770371726783</v>
+        <v>-2.203094063559192</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1974800402057824</v>
+        <v>-0.1371806577510455</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.151498078446998</v>
+        <v>-2.096022850644808</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.483737648883498</v>
+        <v>-1.436190936815663</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.156187839733072</v>
+        <v>-2.10036979051177</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.2639571800249882</v>
+        <v>0.2731101850607232</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.617681453184694</v>
+        <v>1.962860619751638</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1721365808009878</v>
+        <v>0.5055124394169681</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.4145788594607538</v>
+        <v>-0.4835711386625903</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.1547952090366422</v>
+        <v>0.1877422480620154</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.228139849865705</v>
+        <v>-1.883126353223616</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.01224846894138</v>
+        <v>-1.668664126077843</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2505995093670563</v>
+        <v>0.09630991588036864</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.02130142982201</v>
+        <v>1.079253011398848</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.735969302404996</v>
+        <v>1.779284287893176</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.732638989065514</v>
+        <v>-2.628244017526114</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.622700491300655</v>
+        <v>-1.239995414916351</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003345</t>
+          <t>X &lt; -0.003268</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.603229558573027</v>
+        <v>-1.69077487625875</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.564965604571746</v>
+        <v>-1.936681711962621</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.062545782129391</v>
+        <v>-3.191375813854201</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6132149319701909</v>
+        <v>0.2285676663499316</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.09874107384298</v>
+        <v>3.039429279337007</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.718309140818107</v>
+        <v>1.653153008791882</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4435963656900981</v>
+        <v>-0.376496904675399</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.350738628053236</v>
+        <v>-0.9900593233926571</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6803206285284702</v>
+        <v>-0.5534884383999099</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.45323630456496</v>
+        <v>-1.040897958310616</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.493642071208072</v>
+        <v>-1.385946894323553</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.40132229226613</v>
+        <v>-2.58845477472078</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3798302710719312</v>
+        <v>-0.6169271390851279</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9714178965066367</v>
+        <v>0.9866906513336104</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.3156562186839906</v>
+        <v>-0.3127476811687373</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.6646655231560885</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.1448135662815275</v>
+        <v>0.1446759259259167</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.217888772759778</v>
+        <v>-1.22277608047024</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.31646280064048</v>
+        <v>-1.316955828633112</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.129616990672453</v>
+        <v>-1.102369383574128</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.4041021430300731</v>
+        <v>0.1820379668969849</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.274628421368597</v>
+        <v>1.032801370867631</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.290013585392245</v>
+        <v>-1.50134192163177</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.050388425366307</v>
+        <v>-1.046196965303949</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002614</t>
+          <t>X &lt; -0.002543</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2754624980473537</v>
+        <v>-1.060357224564498</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.571777757935628</v>
+        <v>-1.306264060268369</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.769412191581999</v>
+        <v>-3.03377140093064</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.32532609666756</v>
+        <v>1.101958787968002</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.431843316427987</v>
+        <v>2.481246983566059</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.099578733294592</v>
+        <v>3.110993828334827</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.06106378434400028</v>
+        <v>0.3227015038437031</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6990753712524409</v>
+        <v>-0.4561525888540103</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.06530337692731791</v>
+        <v>0.3826767947637393</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4666484436874896</v>
+        <v>-0.4133747004555985</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5303027647394956</v>
+        <v>0.3327939634378367</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.9532659158169352</v>
+        <v>-1.128622114256203</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.297065993230561</v>
+        <v>1.310988137961267</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.798878683049033</v>
+        <v>2.010621375106354</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.140735385468474</v>
+        <v>1.328466993221298</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7712668857247209</v>
+        <v>0.9419037134627644</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.36024131501231</v>
+        <v>1.311956951026851</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.4313463767606862</v>
+        <v>-0.4796949266466015</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.6973827066797256</v>
+        <v>-0.5021995241453752</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.453318524975046</v>
+        <v>0.4232873948472644</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.504393217261608</v>
+        <v>1.277643841333827</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.153184937011936</v>
+        <v>1.913381793312183</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.7368383934553435</v>
+        <v>0.7352153307232712</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.06363154092735357</v>
+        <v>0.09914268714470609</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001883</t>
+          <t>X &lt; -0.001817</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.01334183487462326</v>
+        <v>1.219278033794168</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.925713038341499</v>
+        <v>-1.407581182862081</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.472466490224534</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.805666834361247</v>
+        <v>1.847363332764637</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.608913794969048</v>
+        <v>4.122825600828563</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.369855025629704</v>
+        <v>2.238942880296044</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.166915763689957</v>
+        <v>1.372299023564025</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.004152823920264836</v>
+        <v>0.5563053263223594</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9301915008515849</v>
+        <v>1.195307489839514</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1572758248150947</v>
+        <v>0.5696137458978612</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2829502473087047</v>
+        <v>-0.1802977471639053</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.097413936470986</v>
+        <v>-0.6272374529128868</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.529423996672897</v>
+        <v>1.665025455190005</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.844059405940605</v>
+        <v>2.098222398867634</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.721630394074332</v>
+        <v>1.927141270815625</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.8874458874458853</v>
+        <v>0.9552255281361397</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.467814464754134</v>
+        <v>1.362418370244178</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.06559766763848529</v>
+        <v>0.03703000613879226</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>0.7625654871176195</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.515710951825298</v>
+        <v>0.4660786783435498</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>1.261496187184285</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.508806172309612</v>
+        <v>1.527049167784369</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>1.429968150507378</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.27632161904603</v>
+        <v>0.5863981511071827</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001151</t>
+          <t>X &lt; -0.001091</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6075188996399277</v>
+        <v>0.4938316052227378</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1194147614549834</v>
+        <v>-0.2729085638144682</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>0.03489733429395159</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.566213477260831</v>
+        <v>2.307078468819064</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.191207318439041</v>
+        <v>3.984645328719729</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.148662502928097</v>
+        <v>2.839495601384478</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.240965567097554</v>
+        <v>3.163831776896217</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.307446127586942</v>
+        <v>2.337398947568431</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.135302903210693</v>
+        <v>2.986840243171706</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.755572024028723</v>
+        <v>2.581923037391746</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.587954077724071</v>
+        <v>1.419998990718369</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6538966795185388</v>
+        <v>0.3611484573683228</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.020904992741059</v>
+        <v>1.723440173033588</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.848318907906524</v>
+        <v>2.648608979918606</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>3.10760680298651</v>
+        <v>2.879101273392095</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.867131339608399</v>
+        <v>1.484733845014887</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.257460598436964</v>
+        <v>2.032743915688833</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.973065504052208</v>
+        <v>0.8568350386888994</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.924759405074376</v>
+        <v>1.723187748233627</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.586670831840294</v>
+        <v>1.494897160602775</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.175389300472752</v>
+        <v>1.971839082198535</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.625167517775864</v>
+        <v>2.549418074603572</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.374018051545704</v>
+        <v>2.270859348393692</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.42959184300048</v>
+        <v>2.239268656976286</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0004197</t>
+          <t>X &lt; -0.0003659</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2958044702784406</v>
+        <v>0.1577342827197228</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.05152540948518691</v>
+        <v>-0.2686779681466049</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2424656364722964</v>
+        <v>0.1011766664239104</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.429964105717332</v>
+        <v>1.223575911659012</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.813630646744727</v>
+        <v>2.662819215603001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.14849177677285</v>
+        <v>1.917225745788805</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.338849451036154</v>
+        <v>1.264575061599814</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7886525121760997</v>
+        <v>0.7789861448397986</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.374110682304767</v>
+        <v>1.268252001226713</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.054504163113236</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.419225636644157</v>
+        <v>1.286440940665898</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.415181582244216</v>
+        <v>0.1968508561133078</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.195917974136961</v>
+        <v>1.123300128568296</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.246824591797349</v>
+        <v>1.236729719938076</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.7700049569547787</v>
+        <v>0.7354071644544717</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.367111733838847</v>
+        <v>0.3021361380661745</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.03879089724561169</v>
+        <v>-0.07299201326100757</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6876025892807576</v>
+        <v>-0.5675397712254977</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.2170554452018436</v>
+        <v>0.2798338483253389</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.8576217633368373</v>
+        <v>0.9100880210401385</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.368811598443422</v>
+        <v>1.428616370338133</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.837924765099707</v>
+        <v>1.805942536165659</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.204134264139434</v>
+        <v>1.235097383434983</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.673261138981552</v>
+        <v>1.671194339043879</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003117</t>
+          <t>X &lt; 0.0003597</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2332</v>
+        <v>2351</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5755072306906825</v>
+        <v>0.4988459760789894</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.34904587944105</v>
+        <v>0.2758186800466689</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7670902020175845</v>
+        <v>0.8229307417484222</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.247657069190346</v>
+        <v>1.331756836036341</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.124995326395847</v>
+        <v>1.225618433336408</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>0.87429282713628</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5891488207352964</v>
+        <v>0.6116805383042987</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5062581266315291</v>
+        <v>0.5853361936447925</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7005343091961009</v>
+        <v>0.8224421996172353</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.50770604389119</v>
+        <v>0.6201141988847496</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4221779578195139</v>
+        <v>0.4682610031413361</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.08280654847374791</v>
+        <v>0.06445258556571076</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2707958775102099</v>
+        <v>-0.2198959684717252</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2353548736660684</v>
+        <v>-0.1711423336808195</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.07278522726508641</v>
+        <v>0.147857236142471</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2484731785116878</v>
+        <v>-0.1571997368949525</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5107600202388412</v>
+        <v>-0.4309315286624269</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.018386317344941</v>
+        <v>-0.9884440839301831</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.2634413738967751</v>
+        <v>-0.2644277166570177</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.2907283262413856</v>
+        <v>-0.2797611622120115</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4652303685461661</v>
+        <v>-0.46487771117134</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.2584432251892821</v>
+        <v>-0.3025047526521192</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.3871993589663347</v>
+        <v>-0.3738538893818344</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.3343866722239071</v>
+        <v>-0.2982882739669321</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001043</t>
+          <t>X &lt; 0.001085</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2667</v>
+        <v>2694</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7013071914506313</v>
+        <v>0.6471111825575449</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2749353723345465</v>
+        <v>0.2735048409122598</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2372335777922245</v>
+        <v>0.2578436309322996</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6059654964322831</v>
+        <v>0.5727958561065734</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>0.7406966960515859</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6648772407572778</v>
+        <v>0.601990982020105</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3994385600425474</v>
+        <v>0.3822717222386345</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4414088959132982</v>
+        <v>0.4312461043230229</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4297645837268718</v>
+        <v>0.4693805274953249</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3884310671810951</v>
+        <v>0.4132476412289989</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6469562947473761</v>
+        <v>0.6329051677063973</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3152637000286447</v>
+        <v>0.2823039682314032</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.01483910512465769</v>
+        <v>0.07737446845847984</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.01925398224189223</v>
+        <v>-0.0227662941964013</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2052763777203097</v>
+        <v>0.2057708373497817</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.03629105425512336</v>
+        <v>0.04820778606118381</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1350512324229456</v>
+        <v>-0.1297741447449781</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.3299448891178614</v>
+        <v>-0.2778603221124314</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.3950770198669105</v>
+        <v>0.4184403038472837</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.1699378111083476</v>
+        <v>0.1730532396423428</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.06181489358468895</v>
+        <v>0.08762579424973183</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.2707927997472339</v>
+        <v>0.2941670887120793</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.04290339619956995</v>
+        <v>0.1147051706058022</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1170523953197531</v>
+        <v>0.1230680681036276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001775</t>
+          <t>X &lt; 0.001811</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2847</v>
+        <v>2880</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.7585942273501516</v>
+        <v>0.7519576113167901</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4777466785081259</v>
+        <v>0.3867597419136217</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3515562006127979</v>
+        <v>0.3934309466515629</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5819984075851536</v>
+        <v>0.6489005222260573</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6505101354530609</v>
+        <v>0.684115862789703</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.612690621406486</v>
+        <v>0.6188025962031247</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3852988147067933</v>
+        <v>0.3960678738787777</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5820463163376601</v>
+        <v>0.5947580092066715</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5037951810355992</v>
+        <v>0.5696609904203314</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5214214830783988</v>
+        <v>0.589000705486356</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6408676160888547</v>
+        <v>0.6391289312136266</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3125119820393891</v>
+        <v>0.3133566940688794</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.004763609694101945</v>
+        <v>0.01489119818103291</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1557654013474163</v>
+        <v>-0.1294647469085817</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.02202290320672518</v>
+        <v>0.005409062343055382</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.002656296485191945</v>
+        <v>0.03295612205072018</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.03138409264920483</v>
+        <v>0.01886554015020181</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.2205558276825741</v>
+        <v>-0.1975367866225426</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.2267348160427431</v>
+        <v>0.2249698233248978</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.06270343302831094</v>
+        <v>0.07856354380346886</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.1431040824096002</v>
+        <v>-0.1073339579241193</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.04780036338114968</v>
+        <v>0.08095894319822605</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.1484056722532898</v>
+        <v>-0.1059716583915531</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.0837391548407993</v>
+        <v>-0.03925252085951314</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002506</t>
+          <t>X &lt; 0.002536</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2993</v>
+        <v>3018</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6420214124644446</v>
+        <v>0.6377551020408134</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4913305883842725</v>
+        <v>0.475542827361032</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4667557102835715</v>
+        <v>0.4244930194059364</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8358490150917746</v>
+        <v>0.7729368570672719</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6852189301759353</v>
+        <v>0.6291744336071545</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4921211343587757</v>
+        <v>0.4421859441662832</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5041935889917326</v>
+        <v>0.4569280138138012</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.511357040591264</v>
+        <v>0.4676428818908889</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4389417386297865</v>
+        <v>0.3835367865390964</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5843487518880224</v>
+        <v>0.5304258407359654</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5781423576213456</v>
+        <v>0.5246987573807473</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.318840169303293</v>
+        <v>0.2671970021110894</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1620226542632324</v>
+        <v>0.1624779680371873</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.09237844810805029</v>
+        <v>-0.08575609339592205</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.06924944169337977</v>
+        <v>0.07769563723228856</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.04989036749623921</v>
+        <v>-0.03549631003807718</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.08377416002556259</v>
+        <v>-0.05373677248677922</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.001983829841854856</v>
+        <v>0.03139461906377505</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.3005630302218236</v>
+        <v>0.33165395476599</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1871085398895573</v>
+        <v>0.2348748450967832</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.06855751253592501</v>
+        <v>-0.03465505846865824</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.05766567552264235</v>
+        <v>-0.02393969691096487</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.1639970939445732</v>
+        <v>-0.1249765974912407</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.05289796128661095</v>
+        <v>-0.002459390751262447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003237</t>
+          <t>X &lt; 0.003262</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3094</v>
+        <v>3122</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5659608506014351</v>
+        <v>0.5140070612626104</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4734605726383947</v>
+        <v>0.4126122032129018</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4989534402155087</v>
+        <v>0.4168169060863747</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8647241383558679</v>
+        <v>0.797491154594006</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9009565986441572</v>
+        <v>0.8266265860203532</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6882326413035997</v>
+        <v>0.5873644669039138</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.4815875783617685</v>
+        <v>0.3840394259384965</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5437459300454393</v>
+        <v>0.4799268192125226</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4106900750397884</v>
+        <v>0.3390628050285258</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5903331056984626</v>
+        <v>0.5184629341708984</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5289054227944021</v>
+        <v>0.4900407008894803</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3978556183377293</v>
+        <v>0.3596082308134925</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3059536223807413</v>
+        <v>0.3171806086071953</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1493285003653426</v>
+        <v>0.1647625803903168</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.2196040516224471</v>
+        <v>0.2362997688371919</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.1239824885423104</v>
+        <v>0.145577040040763</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.1383213771965259</v>
+        <v>0.1565164109121895</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.149563905219118</v>
+        <v>0.1705050591065955</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.2879401211065584</v>
+        <v>0.3080056651703558</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.2165548142249989</v>
+        <v>0.2535812337098236</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.01616821120508405</v>
+        <v>0.03813673232908599</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.008089077143779377</v>
+        <v>0.04601646389492942</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.1019775243800325</v>
+        <v>-0.04352002673014965</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.06768073872252245</v>
+        <v>0.1336023086657221</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.003969</t>
+          <t>X &lt; 0.003987</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3145</v>
+        <v>3171</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2441813136053099</v>
+        <v>0.216771768130009</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2739811435104826</v>
+        <v>0.2697553738226333</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3701749911467758</v>
+        <v>0.3172739016920758</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7181706454163219</v>
+        <v>0.6829653063856966</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7166131797082826</v>
+        <v>0.67601400291462</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.4471348864106943</v>
+        <v>0.4114186481369089</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1994654924422221</v>
+        <v>0.1675499670550877</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1609649800864332</v>
+        <v>0.1002172430743826</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.09399318365263554</v>
+        <v>0.05759165341719807</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2578459863608629</v>
+        <v>0.2218869755393555</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2968976614365531</v>
+        <v>0.26085494627673</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2584271321276148</v>
+        <v>0.2224091123245984</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1049290243022156</v>
+        <v>0.1005198676700445</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.0106732296565113</v>
+        <v>0.009518510639459521</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.1008384045858577</v>
+        <v>0.1008461580306417</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.01538224888478368</v>
+        <v>-0.01133224822884671</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.1234566645093125</v>
+        <v>0.1236917689644272</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.005830903790098318</v>
+        <v>0.009459513646113749</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1771729946903662</v>
+        <v>0.1795932138476886</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.07821378719253858</v>
+        <v>0.09777531058442435</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1278063542783272</v>
+        <v>-0.1231033432852797</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.1846753670273387</v>
+        <v>-0.148072748340347</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.2726483867824214</v>
+        <v>-0.2325237129228483</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.1070253183364756</v>
+        <v>-0.06070343014153678</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.0047</t>
+          <t>X &lt; 0.004713</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3187</v>
+        <v>3210</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2244895449221431</v>
+        <v>0.1868687841147221</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1247814514860721</v>
+        <v>0.1123952287551901</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2632129343837377</v>
+        <v>0.2060755241360113</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5660707264527503</v>
+        <v>0.5291780660929106</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5288734710424023</v>
+        <v>0.5189328506699411</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.2965425172471328</v>
+        <v>0.2593847830335747</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.020511736979266</v>
+        <v>-0.05321237984048821</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.09346643127511101</v>
+        <v>-0.1234876234876339</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1590942134341304</v>
+        <v>-0.1951458161209985</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.007619454959836958</v>
+        <v>-0.04255324488210022</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.09697470578698386</v>
+        <v>0.06124955183801717</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1491229954741513</v>
+        <v>0.1130251731359735</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.04844119195573882</v>
+        <v>-0.05199439024433161</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1443636228453897</v>
+        <v>-0.1449007101428066</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.03278498710161415</v>
+        <v>-0.03191992986241843</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1083945276180671</v>
+        <v>-0.1048900524755965</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.058145993544791</v>
+        <v>0.05830223880596463</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.0593320034780831</v>
+        <v>-0.05617661423365661</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.08123788663051812</v>
+        <v>0.08336068784187489</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.01737858848196083</v>
+        <v>0.03623420600985838</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.1303954490113099</v>
+        <v>-0.1266040084116611</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.187515205234277</v>
+        <v>-0.1521839465377752</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.270714082920442</v>
+        <v>-0.2326513479479431</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.108272435624869</v>
+        <v>-0.06488855408899497</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.005432</t>
+          <t>X &lt; 0.005439</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3224</v>
+        <v>3249</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3948891773875047</v>
+        <v>0.37174636057442</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2308475828253052</v>
+        <v>0.2341033282014422</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.3508453252538075</v>
+        <v>0.3117294946366727</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4259777961860536</v>
+        <v>0.4096716353326855</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3543923127740243</v>
+        <v>0.3656031772602475</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2194877120048702</v>
+        <v>0.2028665814763571</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.07206130862044802</v>
+        <v>-0.08487562653451164</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.116566267222872</v>
+        <v>-0.1273184540116858</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.150060859511953</v>
+        <v>-0.1659355472704789</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.133006182334384</v>
+        <v>-0.1473411079920268</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.02646075410721949</v>
+        <v>-0.04155546813253608</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.05267438324639784</v>
+        <v>0.03694345771437924</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.001188248225055588</v>
+        <v>0.0139984457999347</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1604242056858709</v>
+        <v>-0.1421545843256169</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.08882871069347686</v>
+        <v>-0.06939717684186775</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1256375637563707</v>
+        <v>-0.1040690149744208</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.03736391870469902</v>
+        <v>0.05592357910906287</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.04901208603742191</v>
+        <v>-0.02804518895590036</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.09244740969782583</v>
+        <v>0.112399030888767</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.01203732220550791</v>
+        <v>0.006919487092353904</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.102369768356418</v>
+        <v>-0.09927040174225965</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.1596956138265142</v>
+        <v>-0.1254367401029768</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2387823233180484</v>
+        <v>-0.2020066889632091</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1100826743350112</v>
+        <v>-0.06897320414667263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006163</t>
+          <t>X &lt; 0.006164</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3255</v>
+        <v>3279</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.3414537715237813</v>
+        <v>0.3058581203742463</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1757802396223695</v>
+        <v>0.1672106010839869</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3420822300269251</v>
+        <v>0.2933399510313706</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.348662641002889</v>
+        <v>0.3243337387614389</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2439981261767485</v>
+        <v>0.2477925779106727</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1732339900183035</v>
+        <v>0.1486287576818981</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1228820264135493</v>
+        <v>-0.1437504970656107</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2001991323518979</v>
+        <v>-0.2189698818912333</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2330082544252576</v>
+        <v>-0.2560970818753034</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2234725577692771</v>
+        <v>-0.2449561641919615</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.08475618547827679</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.009035841816100287</v>
+        <v>-0.03204714584938984</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.01181424441220003</v>
+        <v>-0.004148910735132461</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.04912589268114687</v>
+        <v>-0.03948759503928301</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.0150642837968249</v>
+        <v>-0.004011808088463908</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.0152072363227731</v>
+        <v>-0.002790566160967956</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.1450063715597736</v>
+        <v>0.15482305936073</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.1198187252296137</v>
+        <v>0.1313388952444043</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.1393384109194997</v>
+        <v>0.1506682580385927</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.06832349730375853</v>
+        <v>0.07859524955381403</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.004406562338623132</v>
+        <v>-0.001341634520393598</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.08376587424704951</v>
+        <v>-0.05840463753842329</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1594630463243547</v>
+        <v>-0.1320254506892908</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.001964985572158184</v>
+        <v>0.02882590752313519</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.006895</t>
+          <t>X &lt; 0.00689</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3276</v>
+        <v>3300</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3312571922078149</v>
+        <v>0.2965783306066569</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2554952874902909</v>
+        <v>0.24761101449878</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3205803401581022</v>
+        <v>0.2746391616515922</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4743134901542021</v>
+        <v>0.4523749576677645</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3682136400933871</v>
+        <v>0.3746124174545287</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2687633673668586</v>
+        <v>0.246951874002086</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.09111235642807713</v>
+        <v>-0.1089140880729786</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1393158225746021</v>
+        <v>-0.1554035048301898</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1716322073551098</v>
+        <v>-0.1914652823330911</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1670737386648966</v>
+        <v>-0.1854229180529572</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.02747579475395412</v>
+        <v>-0.04688257076310975</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.04599733737838818</v>
+        <v>0.02614371097538992</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.03607559218633583</v>
+        <v>0.04680700908540558</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.0632747389163768</v>
+        <v>-0.05032400006604831</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.003201091031129977</v>
+        <v>0.01082256380416879</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.06136271361607015</v>
+        <v>0.07608268468136714</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.1587983209831876</v>
+        <v>0.171563067150629</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.1635744399614154</v>
+        <v>0.1776460259528747</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.184364336353724</v>
+        <v>0.1982296554789258</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.1150140877138028</v>
+        <v>0.1279935861167303</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.0785431657701281</v>
+        <v>0.07523270568664486</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.009527686745336439</v>
+        <v>0.01807778396556614</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.08295819792448356</v>
+        <v>-0.0535015739630893</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.04254247829014446</v>
+        <v>0.07501515590817576</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.007626</t>
+          <t>X &lt; 0.007615</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3286</v>
+        <v>3310</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3192496217554535</v>
+        <v>0.2850526474522965</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2124619666578909</v>
+        <v>0.205460430179528</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2729874082132397</v>
+        <v>0.2286257437262122</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4543409925130177</v>
+        <v>0.4340816739472686</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.4080725956233664</v>
+        <v>0.4158333359334279</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.218675009407221</v>
+        <v>0.1988424143730541</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.08189448118328357</v>
+        <v>-0.09820859129936821</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1307919376087554</v>
+        <v>-0.1454722573856202</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1931851225250369</v>
+        <v>-0.2111308335285145</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1909898834081716</v>
+        <v>-0.2075088798884153</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.05099148442210577</v>
+        <v>-0.06857260946959798</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.0214062030497999</v>
+        <v>0.003394102268664767</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.008099447435732543</v>
+        <v>0.0206291678494992</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.06128039988464451</v>
+        <v>-0.04682755101054425</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.003385864325849752</v>
+        <v>0.01207985884867924</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.0627863332781331</v>
+        <v>0.07883581821681673</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.1291523676650641</v>
+        <v>0.1435590068355381</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.1335865017765485</v>
+        <v>0.1492143111279916</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.124574218559971</v>
+        <v>0.1401993752531254</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.05598450805630506</v>
+        <v>0.07080550174483591</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.01795694821665705</v>
+        <v>0.01649109393487436</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.07009515043824877</v>
+        <v>-0.04073593455373725</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1424856601653488</v>
+        <v>-0.1113810355468559</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.04804793488091263</v>
+        <v>-0.01397138625058147</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.008358</t>
+          <t>X &lt; 0.008341</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3302</v>
+        <v>3326</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3603562560024471</v>
+        <v>0.3402884451271575</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2524832203277541</v>
+        <v>0.2598679898156533</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2757008080011971</v>
+        <v>0.2466707204266498</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4226351787327474</v>
+        <v>0.4181817946785458</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.405082426715289</v>
+        <v>0.4285249140466831</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2777574015681665</v>
+        <v>0.2732657928292923</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.02506735867291354</v>
+        <v>-0.02629631509719843</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1353492578752196</v>
+        <v>-0.1347118078635674</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.167085769525805</v>
+        <v>-0.1694417170278442</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1686237657903717</v>
+        <v>-0.1698786910649233</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.02797136981926229</v>
+        <v>-0.03025227419914245</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.04273741534653652</v>
+        <v>0.03995027601969525</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.02407548045482599</v>
+        <v>0.02145104725468627</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.07473573444300996</v>
+        <v>0.07297717766810052</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.1292111853760431</v>
+        <v>0.1281429846094895</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.1979767463151134</v>
+        <v>0.1974554467180099</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.2331945968613738</v>
+        <v>0.2313512601260115</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.2371316465781419</v>
+        <v>0.2363260789120218</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.2292388081063592</v>
+        <v>0.2284778267775209</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.1619169841474815</v>
+        <v>0.1605602126888002</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.09122184026730906</v>
+        <v>0.09145724900076146</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.003251025840000921</v>
+        <v>0.03416651806611526</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.0371615275650754</v>
+        <v>-0.004887547209250442</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.05648304341181642</v>
+        <v>0.09130554020817527</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.009089</t>
+          <t>X &lt; 0.009066</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3316</v>
+        <v>3339</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3735327547525671</v>
+        <v>0.3401462561202919</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2946787552844441</v>
+        <v>0.2888473885664808</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2218486459018507</v>
+        <v>0.2113123759730158</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3651571426830174</v>
+        <v>0.3798555434666611</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3462508195427461</v>
+        <v>0.3890800919011426</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3102372991511828</v>
+        <v>0.3244106788576531</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.005451177855626099</v>
+        <v>0.02294376798931097</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1055273575223623</v>
+        <v>-0.08621869086985612</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1369470662869787</v>
+        <v>-0.1203034888614525</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1417200126307279</v>
+        <v>-0.1238114206990133</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.0004983242317706527</v>
+        <v>0.01634319044936206</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.03869109165388807</v>
+        <v>0.05536317257974588</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.01468733396879429</v>
+        <v>0.002752957055598415</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.03482909926591304</v>
+        <v>0.05311549162129126</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.08629204820966407</v>
+        <v>0.105412414410722</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.1572585056339548</v>
+        <v>0.176629017441563</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.1917515267892966</v>
+        <v>0.1800968818489679</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.1350129799920339</v>
+        <v>0.1546252371403369</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.1280327763907607</v>
+        <v>0.1476167982202128</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.1219932237702253</v>
+        <v>0.1406000790583093</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.04929571830596302</v>
+        <v>0.06955265094069318</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.03863657236598783</v>
+        <v>-0.01774533467258976</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.07773271512161273</v>
+        <v>-0.05571465764123928</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.01497271794640653</v>
+        <v>0.03945742223723414</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.00982</t>
+          <t>X &lt; 0.009792</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2442377332485961</v>
+        <v>0.2421160276552285</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2233040215118436</v>
+        <v>0.2487335169308764</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1121240931044127</v>
+        <v>0.104701328376791</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2500418755251772</v>
+        <v>0.2684837785754013</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2589240226070544</v>
+        <v>0.3055082653686298</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2540957279278686</v>
+        <v>0.2718042333063053</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.03583911591184119</v>
+        <v>0.02649297303801745</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1358439251817671</v>
+        <v>-0.1135161135161269</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1369739508259542</v>
+        <v>-0.1466006179574606</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1465621282765923</v>
+        <v>-0.1550506523625046</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.06422824073957401</v>
+        <v>-0.07339472174765405</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.05692067823578384</v>
+        <v>-0.06603222362226546</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.146917289766975</v>
+        <v>-0.1549716128368246</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.0216010841968739</v>
+        <v>-0.04712258821652426</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.02560220701474236</v>
+        <v>0.0005665235078922137</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.06977671451356571</v>
+        <v>0.04511655582635399</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.1331492795056377</v>
+        <v>0.1072758885258835</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.1060275354050333</v>
+        <v>0.08111247832027857</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.100372817061448</v>
+        <v>0.07546432802676861</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.09547998518715417</v>
+        <v>0.06980953335310858</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.04990931815097355</v>
+        <v>0.02537669664665998</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.03795037210601748</v>
+        <v>-0.03211442734184544</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.0751669513899671</v>
+        <v>-0.06832852541298706</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.04321309307694321</v>
+        <v>-0.0342922033991897</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01055</t>
+          <t>X &lt; 0.01052</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3354</v>
+        <v>3378</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1050812253302524</v>
+        <v>0.1180613048208912</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1120538133367077</v>
+        <v>0.1526429067737709</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.03586518303499275</v>
+        <v>-0.02704643593258282</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.03819258702367989</v>
+        <v>0.04418178939980066</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1341141777931227</v>
+        <v>0.1677051363931596</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1302726834725263</v>
+        <v>0.1350271090405428</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02768196278305624</v>
+        <v>0.004419111979444779</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.08522531226277863</v>
+        <v>-0.107055911416559</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.08611261652110613</v>
+        <v>-0.1097644314575135</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.09976523388866809</v>
+        <v>-0.1226152888486922</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01639248075093036</v>
+        <v>-0.03988196573627079</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.01060042318687948</v>
+        <v>-0.03410101092748619</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.04667449621607744</v>
+        <v>-0.06976839383452216</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.04208803757902047</v>
+        <v>-0.0645869150954681</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.001333890102529267</v>
+        <v>-0.0207816673249539</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.01870279234942984</v>
+        <v>0.02650912800773142</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.08100356663707231</v>
+        <v>0.05823793697685886</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.05344995140913511</v>
+        <v>0.03149237237977331</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.0489667877552904</v>
+        <v>0.05656026308182049</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.01530679969392423</v>
+        <v>0.02250376475653582</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.003163996088808574</v>
+        <v>-0.02472750901962684</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.06117768699985504</v>
+        <v>-0.0527417659575633</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09672892621319562</v>
+        <v>-0.08747120964525124</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.06535995519369209</v>
+        <v>-0.05448589366392298</v>
       </c>
     </row>
   </sheetData>
